--- a/cw71012026.xlsx
+++ b/cw71012026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Library/Mobile Documents/com~apple~CloudDocs/Git/course-master/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6821CE31-1F7D-D94D-A27F-431425718EA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C611FD02-BC06-244A-968E-20F635D3BC83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="27040" windowHeight="15620" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="91">
   <si>
     <t>Surname</t>
   </si>
@@ -245,13 +245,76 @@
   </si>
   <si>
     <t>H265709O</t>
+  </si>
+  <si>
+    <t>Ndebele</t>
+  </si>
+  <si>
+    <t>H250828v</t>
+  </si>
+  <si>
+    <t>EIA</t>
+  </si>
+  <si>
+    <t>Mujokeri</t>
+  </si>
+  <si>
+    <t>H240595Y</t>
+  </si>
+  <si>
+    <t>Chipuka</t>
+  </si>
+  <si>
+    <t>H261999S</t>
+  </si>
+  <si>
+    <t>ICC</t>
+  </si>
+  <si>
+    <t>Chiyangwa</t>
+  </si>
+  <si>
+    <t>H261400N</t>
+  </si>
+  <si>
+    <t>H266680G</t>
+  </si>
+  <si>
+    <t>Karomo</t>
+  </si>
+  <si>
+    <t>H262811j</t>
+  </si>
+  <si>
+    <t>Kashiri</t>
+  </si>
+  <si>
+    <t>H267804G</t>
+  </si>
+  <si>
+    <t>MUDIWA</t>
+  </si>
+  <si>
+    <t>H260393B</t>
+  </si>
+  <si>
+    <t>Muzungu</t>
+  </si>
+  <si>
+    <t>H263848C</t>
+  </si>
+  <si>
+    <t>SAMANIKA</t>
+  </si>
+  <si>
+    <t>H262827Z</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="14"/>
       <color theme="1"/>
@@ -294,13 +357,6 @@
     <font>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -315,14 +371,23 @@
       <name val="Times"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF333333"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Latin Modern Roman"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Latin Modern Roman"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="LMRoman10-Regular"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="LMRoman10-Regular"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="LMRoman10-Regular"/>
     </font>
   </fonts>
   <fills count="3">
@@ -396,7 +461,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -406,20 +471,33 @@
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -466,7 +544,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}" name="Table1" displayName="Table1" ref="A1:M228" totalsRowShown="0">
   <autoFilter ref="A1:M228" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M228">
-    <sortCondition ref="A1:A228"/>
+    <sortCondition ref="C1:C228"/>
   </sortState>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{1B9A59CC-67BA-3D4E-8BF2-E846FAA4CCF7}" name="Surname"/>
@@ -853,531 +931,525 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="16" t="s">
+    <row r="2" spans="1:13" ht="20">
+      <c r="A2" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="D2" s="19">
+        <v>0.85</v>
+      </c>
+      <c r="H2" s="5"/>
+      <c r="M2" s="24"/>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B3" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C3" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="16">
+      <c r="D3" s="12">
         <v>0.83</v>
       </c>
-      <c r="G2">
+      <c r="G3">
         <v>0.6</v>
       </c>
-      <c r="H2" s="5"/>
-      <c r="M2" s="15"/>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="16" t="s">
+      <c r="H3" s="5"/>
+      <c r="M3" s="11"/>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B4" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C4" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="16">
+      <c r="D4" s="12">
         <v>0.87</v>
       </c>
-      <c r="G3">
+      <c r="G4">
         <v>0.44</v>
       </c>
-      <c r="H3" s="5"/>
-      <c r="M3" s="15"/>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="16" t="s">
+      <c r="H4" s="5"/>
+      <c r="M4" s="11"/>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B5" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C5" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="16">
+      <c r="D5" s="12">
         <v>0.88</v>
-      </c>
-      <c r="G4">
-        <v>0.21</v>
-      </c>
-      <c r="H4" s="5"/>
-      <c r="M4" s="15"/>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="16">
-        <v>0.71</v>
       </c>
       <c r="G5">
         <v>0.21</v>
       </c>
       <c r="H5" s="5"/>
-      <c r="M5" s="15"/>
+      <c r="M5" s="11"/>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="12">
+        <v>0.71</v>
+      </c>
+      <c r="G6">
+        <v>0.21</v>
+      </c>
+      <c r="H6" s="5"/>
+      <c r="M6" s="25"/>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B7" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C7" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D7" s="12">
         <v>0.88</v>
       </c>
-      <c r="G6">
+      <c r="G7">
         <v>0.67</v>
-      </c>
-      <c r="H6" s="5"/>
-      <c r="M6" s="6"/>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="16">
-        <v>0.76</v>
-      </c>
-      <c r="G7">
-        <v>0.32</v>
       </c>
       <c r="H7" s="5"/>
       <c r="M7" s="6"/>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="16" t="s">
+      <c r="A8" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="16">
-        <v>0.6</v>
+      <c r="D8" s="12">
+        <v>0.76</v>
       </c>
       <c r="G8">
-        <v>0.16</v>
+        <v>0.32</v>
       </c>
       <c r="H8" s="5"/>
       <c r="M8" s="6"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="16" t="s">
+      <c r="A9" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="16">
-        <v>0.75</v>
+      <c r="D9" s="12">
+        <v>0.6</v>
       </c>
       <c r="G9">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="H9" s="5"/>
       <c r="M9" s="6"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="16" t="s">
+      <c r="A10" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="16">
-        <v>0.61</v>
+      <c r="D10" s="12">
+        <v>0.75</v>
       </c>
       <c r="G10">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="H10" s="5"/>
       <c r="M10" s="6"/>
     </row>
     <row r="11" spans="1:13">
-      <c r="A11" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="16" t="s">
+      <c r="A11" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="16">
-        <v>0.83</v>
+      <c r="D11" s="12">
+        <v>0.61</v>
       </c>
       <c r="G11">
-        <v>0.23</v>
+        <v>0.18</v>
       </c>
       <c r="H11" s="5"/>
       <c r="M11" s="6"/>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="16" t="s">
+      <c r="A12" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="16">
-        <v>0.9</v>
+      <c r="D12" s="12">
+        <v>0.83</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="H12" s="5"/>
       <c r="M12" s="6"/>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" s="16" t="s">
+      <c r="A13" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="16">
-        <v>0.72</v>
+      <c r="D13" s="12">
+        <v>0.9</v>
       </c>
       <c r="G13">
-        <v>0.49</v>
+        <v>0</v>
       </c>
       <c r="H13" s="5"/>
       <c r="M13" s="6"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="16" t="s">
+      <c r="A14" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="16">
-        <v>0.87</v>
+      <c r="D14" s="12">
+        <v>0.72</v>
       </c>
       <c r="G14">
-        <v>0.39</v>
+        <v>0.49</v>
       </c>
       <c r="H14" s="5"/>
       <c r="M14" s="6"/>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="16" t="s">
+      <c r="A15" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="16">
-        <v>0.86</v>
+      <c r="D15" s="12">
+        <v>0.87</v>
       </c>
       <c r="G15">
-        <v>0.37</v>
+        <v>0.39</v>
       </c>
       <c r="H15" s="5"/>
       <c r="M15" s="6"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" s="16" t="s">
+      <c r="A16" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="16">
-        <v>0.96</v>
+      <c r="D16" s="12">
+        <v>0.86</v>
       </c>
       <c r="G16">
-        <v>0.51</v>
+        <v>0.37</v>
       </c>
       <c r="H16" s="5"/>
       <c r="M16" s="6"/>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="16" t="s">
+      <c r="A17" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="16">
-        <v>0.81</v>
+      <c r="D17" s="12">
+        <v>0.96</v>
       </c>
       <c r="G17">
-        <v>0.72</v>
+        <v>0.51</v>
       </c>
       <c r="H17" s="5"/>
       <c r="M17" s="6"/>
     </row>
     <row r="18" spans="1:13">
-      <c r="A18" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="C18" s="16" t="s">
+      <c r="A18" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="16">
-        <v>0.91</v>
+      <c r="D18" s="12">
+        <v>0.81</v>
       </c>
       <c r="G18">
-        <v>0.47</v>
+        <v>0.72</v>
       </c>
       <c r="H18" s="5"/>
       <c r="M18" s="6"/>
     </row>
     <row r="19" spans="1:13">
-      <c r="A19" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="C19" s="16" t="s">
+      <c r="A19" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D19" s="16">
-        <v>0.89</v>
+      <c r="D19" s="12">
+        <v>0.91</v>
       </c>
       <c r="G19">
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
       <c r="H19" s="5"/>
       <c r="M19" s="6"/>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" s="16" t="s">
+      <c r="A20" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="16">
-        <v>0.9</v>
+      <c r="D20" s="12">
+        <v>0.89</v>
       </c>
       <c r="G20">
-        <v>0.49</v>
+        <v>0.33</v>
       </c>
       <c r="H20" s="5"/>
       <c r="M20" s="6"/>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21" s="16" t="s">
+      <c r="A21" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="16">
-        <v>0.8</v>
+      <c r="D21" s="12">
+        <v>0.9</v>
       </c>
       <c r="G21">
-        <v>0.39</v>
+        <v>0.49</v>
       </c>
       <c r="H21" s="5"/>
       <c r="M21" s="6"/>
     </row>
     <row r="22" spans="1:13">
-      <c r="A22" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="C22" s="16" t="s">
+      <c r="A22" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="16">
-        <v>0.95</v>
+      <c r="D22" s="12">
+        <v>0.8</v>
       </c>
       <c r="G22">
-        <v>0.72</v>
+        <v>0.39</v>
       </c>
       <c r="H22" s="5"/>
       <c r="M22" s="6"/>
     </row>
     <row r="23" spans="1:13">
-      <c r="A23" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="B23" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="C23" s="16" t="s">
+      <c r="A23" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D23" s="16">
-        <v>0.85</v>
+      <c r="D23" s="12">
+        <v>0.95</v>
       </c>
       <c r="G23">
-        <v>0.54</v>
+        <v>0.72</v>
       </c>
       <c r="H23" s="5"/>
       <c r="M23" s="6"/>
     </row>
-    <row r="24" spans="1:13">
-      <c r="A24" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="B24" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="C24" s="16" t="s">
+    <row r="24" spans="1:13" ht="20">
+      <c r="A24" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="C24" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D24" s="16">
-        <v>0.89</v>
-      </c>
-      <c r="G24">
-        <v>0.54</v>
+      <c r="D24" s="19">
+        <v>0.87</v>
       </c>
       <c r="H24" s="5"/>
       <c r="M24" s="6"/>
     </row>
     <row r="25" spans="1:13">
-      <c r="A25" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="B25" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C25" s="16" t="s">
+      <c r="A25" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D25" s="16">
-        <v>0.83</v>
+      <c r="D25" s="12">
+        <v>0.85</v>
       </c>
       <c r="G25">
-        <v>0.18</v>
+        <v>0.54</v>
       </c>
       <c r="H25" s="5"/>
       <c r="M25" s="6"/>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="B26" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="C26" s="16" t="s">
+      <c r="A26" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D26" s="16">
-        <v>0.7</v>
+      <c r="D26" s="12">
+        <v>0.89</v>
       </c>
       <c r="G26">
-        <v>0.68</v>
+        <v>0.54</v>
       </c>
       <c r="H26" s="5"/>
       <c r="M26" s="6"/>
     </row>
     <row r="27" spans="1:13">
-      <c r="A27" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="B27" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="C27" s="16" t="s">
+      <c r="A27" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D27" s="16">
-        <v>0.93</v>
+      <c r="D27" s="12">
+        <v>0.83</v>
       </c>
       <c r="G27">
-        <v>0.46</v>
+        <v>0.18</v>
       </c>
       <c r="H27" s="5"/>
       <c r="M27" s="6"/>
     </row>
     <row r="28" spans="1:13">
-      <c r="A28" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="B28" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="C28" s="16" t="s">
+      <c r="A28" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="B28" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D28" s="16">
-        <v>0.82</v>
+      <c r="D28" s="12">
+        <v>0.7</v>
       </c>
       <c r="G28">
-        <v>0.25</v>
+        <v>0.68</v>
       </c>
       <c r="H28" s="5"/>
       <c r="M28" s="6"/>
     </row>
     <row r="29" spans="1:13">
-      <c r="A29" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="B29" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="C29" s="16" t="s">
+      <c r="A29" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="B29" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="C29" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D29" s="16">
-        <v>0.62</v>
+      <c r="D29" s="12">
+        <v>0.93</v>
       </c>
       <c r="G29">
         <v>0.46</v>
@@ -1386,72 +1458,166 @@
       <c r="M29" s="6"/>
     </row>
     <row r="30" spans="1:13">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
-      <c r="D30" s="4"/>
+      <c r="A30" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D30" s="12">
+        <v>0.82</v>
+      </c>
+      <c r="G30">
+        <v>0.25</v>
+      </c>
       <c r="H30" s="5"/>
       <c r="M30" s="6"/>
     </row>
     <row r="31" spans="1:13">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="D31" s="4"/>
+      <c r="A31" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="B31" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31" s="12">
+        <v>0.62</v>
+      </c>
+      <c r="G31">
+        <v>0.46</v>
+      </c>
       <c r="H31" s="5"/>
       <c r="M31" s="6"/>
     </row>
-    <row r="32" spans="1:13">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7"/>
-      <c r="D32" s="4"/>
+    <row r="32" spans="1:13" ht="20">
+      <c r="A32" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="D32" s="19">
+        <v>0.93</v>
+      </c>
       <c r="H32" s="5"/>
       <c r="M32" s="6"/>
     </row>
-    <row r="33" spans="1:13">
-      <c r="A33" s="7"/>
-      <c r="B33" s="7"/>
-      <c r="D33" s="4"/>
+    <row r="33" spans="1:13" ht="20">
+      <c r="A33" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="D33" s="19">
+        <v>0.93</v>
+      </c>
       <c r="H33" s="5"/>
       <c r="M33" s="6"/>
     </row>
-    <row r="34" spans="1:13">
-      <c r="A34" s="14"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="4"/>
+    <row r="34" spans="1:13" ht="20">
+      <c r="A34" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D34" s="19">
+        <v>0.91</v>
+      </c>
       <c r="M34" s="6"/>
     </row>
-    <row r="35" spans="1:13">
-      <c r="A35" s="9"/>
-      <c r="B35" s="9"/>
-      <c r="D35" s="4"/>
+    <row r="35" spans="1:13" ht="20">
+      <c r="A35" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="D35" s="19">
+        <v>0.75</v>
+      </c>
       <c r="H35" s="5"/>
       <c r="M35" s="6"/>
     </row>
-    <row r="36" spans="1:13">
-      <c r="A36" s="8"/>
-      <c r="B36" s="8"/>
-      <c r="D36" s="4"/>
+    <row r="36" spans="1:13" ht="20">
+      <c r="A36" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="D36" s="19">
+        <v>0.87</v>
+      </c>
       <c r="H36" s="5"/>
       <c r="M36" s="6"/>
     </row>
-    <row r="37" spans="1:13">
-      <c r="A37" s="14"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="4"/>
+    <row r="37" spans="1:13" ht="20">
+      <c r="A37" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D37" s="19">
+        <v>0.89</v>
+      </c>
       <c r="M37" s="6"/>
     </row>
-    <row r="38" spans="1:13">
-      <c r="A38" s="10"/>
-      <c r="B38" s="10"/>
-      <c r="D38" s="4"/>
+    <row r="38" spans="1:13" ht="21">
+      <c r="A38" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="D38" s="19">
+        <v>0.47</v>
+      </c>
       <c r="H38" s="5"/>
       <c r="M38" s="6"/>
     </row>
-    <row r="39" spans="1:13">
-      <c r="A39" s="8"/>
-      <c r="B39" s="8"/>
-      <c r="D39" s="4"/>
+    <row r="39" spans="1:13" ht="20">
+      <c r="A39" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="D39" s="19">
+        <v>0.94</v>
+      </c>
       <c r="H39" s="5"/>
       <c r="M39" s="6"/>
     </row>
@@ -1491,262 +1657,262 @@
       <c r="M44" s="6"/>
     </row>
     <row r="45" spans="1:13">
-      <c r="A45" s="12"/>
-      <c r="B45" s="12"/>
+      <c r="A45" s="10"/>
+      <c r="B45" s="10"/>
       <c r="D45" s="4"/>
       <c r="H45" s="5"/>
       <c r="M45" s="6"/>
     </row>
     <row r="46" spans="1:13">
-      <c r="A46" s="12"/>
-      <c r="B46" s="12"/>
+      <c r="A46" s="10"/>
+      <c r="B46" s="10"/>
       <c r="D46" s="4"/>
       <c r="H46" s="5"/>
       <c r="M46" s="6"/>
     </row>
     <row r="47" spans="1:13">
-      <c r="A47" s="11"/>
-      <c r="B47" s="11"/>
-      <c r="C47" s="11"/>
-      <c r="D47" s="11"/>
+      <c r="A47" s="9"/>
+      <c r="B47" s="9"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
       <c r="H47" s="5"/>
       <c r="M47" s="6"/>
     </row>
     <row r="48" spans="1:13">
-      <c r="A48" s="11"/>
-      <c r="B48" s="11"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="11"/>
+      <c r="A48" s="9"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
       <c r="H48" s="5"/>
       <c r="M48" s="6"/>
     </row>
     <row r="49" spans="1:13">
-      <c r="A49" s="11"/>
-      <c r="B49" s="11"/>
-      <c r="C49" s="11"/>
-      <c r="D49" s="11"/>
+      <c r="A49" s="9"/>
+      <c r="B49" s="9"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
       <c r="H49" s="5"/>
       <c r="M49" s="6"/>
     </row>
     <row r="50" spans="1:13">
-      <c r="A50" s="11"/>
-      <c r="B50" s="11"/>
-      <c r="C50" s="11"/>
-      <c r="D50" s="11"/>
+      <c r="A50" s="9"/>
+      <c r="B50" s="9"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
       <c r="H50" s="5"/>
       <c r="M50" s="6"/>
     </row>
     <row r="51" spans="1:13">
-      <c r="A51" s="11"/>
-      <c r="B51" s="11"/>
-      <c r="C51" s="11"/>
-      <c r="D51" s="11"/>
+      <c r="A51" s="9"/>
+      <c r="B51" s="9"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
       <c r="H51" s="5"/>
       <c r="M51" s="6"/>
     </row>
     <row r="52" spans="1:13">
-      <c r="A52" s="11"/>
-      <c r="B52" s="11"/>
-      <c r="C52" s="11"/>
-      <c r="D52" s="11"/>
+      <c r="A52" s="9"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="9"/>
       <c r="H52" s="5"/>
       <c r="M52" s="6"/>
     </row>
     <row r="53" spans="1:13">
-      <c r="A53" s="11"/>
-      <c r="B53" s="11"/>
-      <c r="C53" s="11"/>
-      <c r="D53" s="11"/>
+      <c r="A53" s="9"/>
+      <c r="B53" s="9"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="9"/>
       <c r="H53" s="5"/>
       <c r="M53" s="6"/>
     </row>
     <row r="54" spans="1:13">
-      <c r="A54" s="11"/>
-      <c r="B54" s="11"/>
-      <c r="C54" s="11"/>
-      <c r="D54" s="11"/>
+      <c r="A54" s="9"/>
+      <c r="B54" s="9"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="9"/>
       <c r="M54" s="6"/>
     </row>
     <row r="55" spans="1:13">
-      <c r="A55" s="11"/>
-      <c r="B55" s="11"/>
-      <c r="C55" s="11"/>
-      <c r="D55" s="11"/>
+      <c r="A55" s="9"/>
+      <c r="B55" s="9"/>
+      <c r="C55" s="9"/>
+      <c r="D55" s="9"/>
       <c r="M55" s="6"/>
     </row>
     <row r="56" spans="1:13">
-      <c r="A56" s="11"/>
-      <c r="B56" s="11"/>
-      <c r="C56" s="11"/>
-      <c r="D56" s="11"/>
+      <c r="A56" s="9"/>
+      <c r="B56" s="9"/>
+      <c r="C56" s="9"/>
+      <c r="D56" s="9"/>
       <c r="M56" s="6"/>
     </row>
     <row r="57" spans="1:13">
-      <c r="A57" s="11"/>
-      <c r="B57" s="11"/>
-      <c r="C57" s="11"/>
-      <c r="D57" s="11"/>
+      <c r="A57" s="9"/>
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
       <c r="M57" s="6"/>
     </row>
     <row r="58" spans="1:13">
-      <c r="A58" s="11"/>
-      <c r="B58" s="11"/>
-      <c r="C58" s="11"/>
-      <c r="D58" s="11"/>
+      <c r="A58" s="9"/>
+      <c r="B58" s="9"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
       <c r="M58" s="6"/>
     </row>
     <row r="59" spans="1:13">
-      <c r="A59" s="11"/>
-      <c r="B59" s="11"/>
-      <c r="C59" s="11"/>
-      <c r="D59" s="11"/>
+      <c r="A59" s="9"/>
+      <c r="B59" s="9"/>
+      <c r="C59" s="9"/>
+      <c r="D59" s="9"/>
       <c r="M59" s="6"/>
     </row>
     <row r="60" spans="1:13">
-      <c r="A60" s="11"/>
-      <c r="B60" s="11"/>
-      <c r="C60" s="11"/>
-      <c r="D60" s="11"/>
+      <c r="A60" s="9"/>
+      <c r="B60" s="9"/>
+      <c r="C60" s="9"/>
+      <c r="D60" s="9"/>
       <c r="M60" s="6"/>
     </row>
     <row r="61" spans="1:13">
-      <c r="A61" s="11"/>
-      <c r="B61" s="11"/>
-      <c r="C61" s="11"/>
-      <c r="D61" s="11"/>
+      <c r="A61" s="9"/>
+      <c r="B61" s="9"/>
+      <c r="C61" s="9"/>
+      <c r="D61" s="9"/>
       <c r="M61" s="6"/>
     </row>
     <row r="62" spans="1:13">
-      <c r="A62" s="11"/>
-      <c r="B62" s="11"/>
-      <c r="C62" s="11"/>
-      <c r="D62" s="11"/>
+      <c r="A62" s="9"/>
+      <c r="B62" s="9"/>
+      <c r="C62" s="9"/>
+      <c r="D62" s="9"/>
       <c r="M62" s="6"/>
     </row>
     <row r="63" spans="1:13">
-      <c r="A63" s="11"/>
-      <c r="B63" s="11"/>
-      <c r="C63" s="11"/>
-      <c r="D63" s="11"/>
+      <c r="A63" s="9"/>
+      <c r="B63" s="9"/>
+      <c r="C63" s="9"/>
+      <c r="D63" s="9"/>
       <c r="M63" s="6"/>
     </row>
     <row r="64" spans="1:13">
-      <c r="A64" s="11"/>
-      <c r="B64" s="11"/>
-      <c r="C64" s="11"/>
-      <c r="D64" s="11"/>
+      <c r="A64" s="9"/>
+      <c r="B64" s="9"/>
+      <c r="C64" s="9"/>
+      <c r="D64" s="9"/>
       <c r="M64" s="6"/>
     </row>
     <row r="65" spans="1:13">
-      <c r="A65" s="11"/>
-      <c r="B65" s="11"/>
-      <c r="C65" s="11"/>
-      <c r="D65" s="11"/>
+      <c r="A65" s="9"/>
+      <c r="B65" s="9"/>
+      <c r="C65" s="9"/>
+      <c r="D65" s="9"/>
       <c r="M65" s="6"/>
     </row>
     <row r="66" spans="1:13">
-      <c r="A66" s="11"/>
-      <c r="B66" s="11"/>
-      <c r="C66" s="11"/>
-      <c r="D66" s="11"/>
+      <c r="A66" s="9"/>
+      <c r="B66" s="9"/>
+      <c r="C66" s="9"/>
+      <c r="D66" s="9"/>
       <c r="M66" s="6"/>
     </row>
     <row r="67" spans="1:13">
-      <c r="A67" s="11"/>
-      <c r="B67" s="11"/>
-      <c r="C67" s="11"/>
-      <c r="D67" s="11"/>
+      <c r="A67" s="9"/>
+      <c r="B67" s="9"/>
+      <c r="C67" s="9"/>
+      <c r="D67" s="9"/>
       <c r="M67" s="6"/>
     </row>
     <row r="68" spans="1:13">
-      <c r="A68" s="11"/>
-      <c r="B68" s="11"/>
-      <c r="C68" s="11"/>
-      <c r="D68" s="11"/>
+      <c r="A68" s="9"/>
+      <c r="B68" s="9"/>
+      <c r="C68" s="9"/>
+      <c r="D68" s="9"/>
       <c r="M68" s="6"/>
     </row>
     <row r="69" spans="1:13">
-      <c r="A69" s="11"/>
-      <c r="B69" s="11"/>
-      <c r="C69" s="11"/>
-      <c r="D69" s="11"/>
+      <c r="A69" s="9"/>
+      <c r="B69" s="9"/>
+      <c r="C69" s="9"/>
+      <c r="D69" s="9"/>
       <c r="M69" s="6"/>
     </row>
     <row r="70" spans="1:13">
-      <c r="A70" s="11"/>
-      <c r="B70" s="11"/>
-      <c r="C70" s="11"/>
-      <c r="D70" s="11"/>
+      <c r="A70" s="9"/>
+      <c r="B70" s="9"/>
+      <c r="C70" s="9"/>
+      <c r="D70" s="9"/>
       <c r="M70" s="6"/>
     </row>
     <row r="71" spans="1:13">
-      <c r="A71" s="11"/>
-      <c r="B71" s="11"/>
-      <c r="C71" s="11"/>
-      <c r="D71" s="11"/>
+      <c r="A71" s="9"/>
+      <c r="B71" s="9"/>
+      <c r="C71" s="9"/>
+      <c r="D71" s="9"/>
       <c r="M71" s="6"/>
     </row>
     <row r="72" spans="1:13">
-      <c r="A72" s="11"/>
-      <c r="B72" s="11"/>
-      <c r="C72" s="11"/>
-      <c r="D72" s="11"/>
+      <c r="A72" s="9"/>
+      <c r="B72" s="9"/>
+      <c r="C72" s="9"/>
+      <c r="D72" s="9"/>
       <c r="M72" s="6"/>
     </row>
     <row r="73" spans="1:13">
-      <c r="A73" s="11"/>
-      <c r="B73" s="11"/>
-      <c r="C73" s="11"/>
-      <c r="D73" s="11"/>
+      <c r="A73" s="9"/>
+      <c r="B73" s="9"/>
+      <c r="C73" s="9"/>
+      <c r="D73" s="9"/>
       <c r="M73" s="6"/>
     </row>
     <row r="74" spans="1:13">
-      <c r="A74" s="11"/>
-      <c r="B74" s="11"/>
-      <c r="C74" s="11"/>
-      <c r="D74" s="11"/>
+      <c r="A74" s="9"/>
+      <c r="B74" s="9"/>
+      <c r="C74" s="9"/>
+      <c r="D74" s="9"/>
       <c r="M74" s="6"/>
     </row>
     <row r="75" spans="1:13">
-      <c r="A75" s="11"/>
-      <c r="B75" s="11"/>
-      <c r="C75" s="11"/>
-      <c r="D75" s="11"/>
+      <c r="A75" s="9"/>
+      <c r="B75" s="9"/>
+      <c r="C75" s="9"/>
+      <c r="D75" s="9"/>
       <c r="M75" s="6"/>
     </row>
     <row r="76" spans="1:13">
-      <c r="A76" s="11"/>
-      <c r="B76" s="11"/>
-      <c r="C76" s="11"/>
-      <c r="D76" s="11"/>
+      <c r="A76" s="9"/>
+      <c r="B76" s="9"/>
+      <c r="C76" s="9"/>
+      <c r="D76" s="9"/>
       <c r="M76" s="6"/>
     </row>
     <row r="77" spans="1:13">
-      <c r="A77" s="11"/>
-      <c r="B77" s="11"/>
-      <c r="C77" s="11"/>
-      <c r="D77" s="11"/>
+      <c r="A77" s="9"/>
+      <c r="B77" s="9"/>
+      <c r="C77" s="9"/>
+      <c r="D77" s="9"/>
       <c r="M77" s="6"/>
     </row>
     <row r="78" spans="1:13">
-      <c r="A78" s="11"/>
-      <c r="B78" s="11"/>
-      <c r="C78" s="11"/>
-      <c r="D78" s="11"/>
+      <c r="A78" s="9"/>
+      <c r="B78" s="9"/>
+      <c r="C78" s="9"/>
+      <c r="D78" s="9"/>
       <c r="M78" s="6"/>
     </row>
     <row r="79" spans="1:13">
-      <c r="A79" s="11"/>
-      <c r="B79" s="11"/>
-      <c r="C79" s="11"/>
-      <c r="D79" s="11"/>
+      <c r="A79" s="9"/>
+      <c r="B79" s="9"/>
+      <c r="C79" s="9"/>
+      <c r="D79" s="9"/>
       <c r="M79" s="6"/>
     </row>
     <row r="80" spans="1:13">
-      <c r="A80" s="11"/>
-      <c r="B80" s="11"/>
-      <c r="C80" s="11"/>
-      <c r="D80" s="11"/>
+      <c r="A80" s="9"/>
+      <c r="B80" s="9"/>
+      <c r="C80" s="9"/>
+      <c r="D80" s="9"/>
       <c r="M80" s="6"/>
     </row>
     <row r="81" spans="1:13">
@@ -1755,598 +1921,598 @@
       <c r="M81" s="6"/>
     </row>
     <row r="82" spans="1:13">
-      <c r="A82" s="11"/>
-      <c r="B82" s="11"/>
-      <c r="C82" s="11"/>
-      <c r="D82" s="11"/>
+      <c r="A82" s="9"/>
+      <c r="B82" s="9"/>
+      <c r="C82" s="9"/>
+      <c r="D82" s="9"/>
       <c r="M82" s="6"/>
     </row>
     <row r="83" spans="1:13">
-      <c r="A83" s="11"/>
-      <c r="B83" s="11"/>
-      <c r="C83" s="11"/>
-      <c r="D83" s="11"/>
+      <c r="A83" s="9"/>
+      <c r="B83" s="9"/>
+      <c r="C83" s="9"/>
+      <c r="D83" s="9"/>
       <c r="M83" s="6"/>
     </row>
     <row r="84" spans="1:13">
-      <c r="A84" s="11"/>
-      <c r="B84" s="11"/>
-      <c r="C84" s="11"/>
-      <c r="D84" s="11"/>
+      <c r="A84" s="9"/>
+      <c r="B84" s="9"/>
+      <c r="C84" s="9"/>
+      <c r="D84" s="9"/>
       <c r="M84" s="6"/>
     </row>
     <row r="85" spans="1:13">
-      <c r="A85" s="11"/>
-      <c r="B85" s="11"/>
-      <c r="C85" s="11"/>
-      <c r="D85" s="11"/>
+      <c r="A85" s="9"/>
+      <c r="B85" s="9"/>
+      <c r="C85" s="9"/>
+      <c r="D85" s="9"/>
       <c r="M85" s="6"/>
     </row>
     <row r="86" spans="1:13">
-      <c r="A86" s="11"/>
-      <c r="B86" s="11"/>
-      <c r="C86" s="11"/>
-      <c r="D86" s="11"/>
+      <c r="A86" s="9"/>
+      <c r="B86" s="9"/>
+      <c r="C86" s="9"/>
+      <c r="D86" s="9"/>
       <c r="M86" s="6"/>
     </row>
     <row r="87" spans="1:13">
-      <c r="A87" s="11"/>
-      <c r="B87" s="11"/>
-      <c r="C87" s="11"/>
-      <c r="D87" s="11"/>
+      <c r="A87" s="9"/>
+      <c r="B87" s="9"/>
+      <c r="C87" s="9"/>
+      <c r="D87" s="9"/>
       <c r="M87" s="6"/>
     </row>
     <row r="88" spans="1:13">
-      <c r="A88" s="11"/>
-      <c r="B88" s="11"/>
-      <c r="C88" s="11"/>
-      <c r="D88" s="11"/>
+      <c r="A88" s="9"/>
+      <c r="B88" s="9"/>
+      <c r="C88" s="9"/>
+      <c r="D88" s="9"/>
       <c r="M88" s="6"/>
     </row>
     <row r="89" spans="1:13">
-      <c r="A89" s="11"/>
-      <c r="B89" s="11"/>
-      <c r="C89" s="11"/>
-      <c r="D89" s="11"/>
+      <c r="A89" s="9"/>
+      <c r="B89" s="9"/>
+      <c r="C89" s="9"/>
+      <c r="D89" s="9"/>
       <c r="M89" s="6"/>
     </row>
     <row r="90" spans="1:13">
-      <c r="A90" s="11"/>
-      <c r="B90" s="11"/>
-      <c r="C90" s="11"/>
-      <c r="D90" s="11"/>
+      <c r="A90" s="9"/>
+      <c r="B90" s="9"/>
+      <c r="C90" s="9"/>
+      <c r="D90" s="9"/>
       <c r="M90" s="6"/>
     </row>
     <row r="91" spans="1:13">
-      <c r="A91" s="11"/>
-      <c r="B91" s="11"/>
-      <c r="C91" s="11"/>
-      <c r="D91" s="11"/>
+      <c r="A91" s="9"/>
+      <c r="B91" s="9"/>
+      <c r="C91" s="9"/>
+      <c r="D91" s="9"/>
       <c r="M91" s="6"/>
     </row>
     <row r="92" spans="1:13">
-      <c r="A92" s="11"/>
-      <c r="B92" s="11"/>
-      <c r="C92" s="11"/>
-      <c r="D92" s="11"/>
+      <c r="A92" s="9"/>
+      <c r="B92" s="9"/>
+      <c r="C92" s="9"/>
+      <c r="D92" s="9"/>
       <c r="M92" s="6"/>
     </row>
     <row r="93" spans="1:13">
-      <c r="A93" s="11"/>
-      <c r="B93" s="11"/>
-      <c r="C93" s="11"/>
-      <c r="D93" s="11"/>
+      <c r="A93" s="9"/>
+      <c r="B93" s="9"/>
+      <c r="C93" s="9"/>
+      <c r="D93" s="9"/>
       <c r="M93" s="6"/>
     </row>
     <row r="94" spans="1:13">
-      <c r="A94" s="11"/>
-      <c r="B94" s="11"/>
-      <c r="C94" s="11"/>
-      <c r="D94" s="11"/>
+      <c r="A94" s="9"/>
+      <c r="B94" s="9"/>
+      <c r="C94" s="9"/>
+      <c r="D94" s="9"/>
       <c r="M94" s="6"/>
     </row>
     <row r="95" spans="1:13">
-      <c r="A95" s="11"/>
-      <c r="B95" s="11"/>
-      <c r="C95" s="11"/>
-      <c r="D95" s="11"/>
+      <c r="A95" s="9"/>
+      <c r="B95" s="9"/>
+      <c r="C95" s="9"/>
+      <c r="D95" s="9"/>
       <c r="M95" s="6"/>
     </row>
     <row r="96" spans="1:13">
-      <c r="A96" s="11"/>
-      <c r="B96" s="11"/>
-      <c r="C96" s="11"/>
-      <c r="D96" s="11"/>
+      <c r="A96" s="9"/>
+      <c r="B96" s="9"/>
+      <c r="C96" s="9"/>
+      <c r="D96" s="9"/>
       <c r="M96" s="6"/>
     </row>
     <row r="97" spans="1:13">
-      <c r="A97" s="11"/>
-      <c r="B97" s="11"/>
-      <c r="C97" s="11"/>
-      <c r="D97" s="11"/>
+      <c r="A97" s="9"/>
+      <c r="B97" s="9"/>
+      <c r="C97" s="9"/>
+      <c r="D97" s="9"/>
       <c r="M97" s="6"/>
     </row>
     <row r="98" spans="1:13">
-      <c r="A98" s="11"/>
-      <c r="B98" s="11"/>
-      <c r="C98" s="11"/>
-      <c r="D98" s="11"/>
+      <c r="A98" s="9"/>
+      <c r="B98" s="9"/>
+      <c r="C98" s="9"/>
+      <c r="D98" s="9"/>
       <c r="M98" s="6"/>
     </row>
     <row r="99" spans="1:13">
-      <c r="A99" s="11"/>
-      <c r="B99" s="11"/>
-      <c r="C99" s="11"/>
-      <c r="D99" s="11"/>
+      <c r="A99" s="9"/>
+      <c r="B99" s="9"/>
+      <c r="C99" s="9"/>
+      <c r="D99" s="9"/>
       <c r="M99" s="6"/>
     </row>
     <row r="100" spans="1:13">
-      <c r="A100" s="11"/>
-      <c r="B100" s="11"/>
-      <c r="C100" s="11"/>
-      <c r="D100" s="11"/>
+      <c r="A100" s="9"/>
+      <c r="B100" s="9"/>
+      <c r="C100" s="9"/>
+      <c r="D100" s="9"/>
       <c r="M100" s="6"/>
     </row>
     <row r="101" spans="1:13">
-      <c r="A101" s="11"/>
-      <c r="B101" s="11"/>
-      <c r="C101" s="11"/>
-      <c r="D101" s="11"/>
+      <c r="A101" s="9"/>
+      <c r="B101" s="9"/>
+      <c r="C101" s="9"/>
+      <c r="D101" s="9"/>
       <c r="M101" s="6"/>
     </row>
     <row r="102" spans="1:13">
-      <c r="A102" s="11"/>
-      <c r="B102" s="11"/>
-      <c r="C102" s="11"/>
-      <c r="D102" s="11"/>
+      <c r="A102" s="9"/>
+      <c r="B102" s="9"/>
+      <c r="C102" s="9"/>
+      <c r="D102" s="9"/>
       <c r="M102" s="6"/>
     </row>
     <row r="103" spans="1:13">
-      <c r="A103" s="11"/>
-      <c r="B103" s="11"/>
-      <c r="C103" s="11"/>
-      <c r="D103" s="11"/>
+      <c r="A103" s="9"/>
+      <c r="B103" s="9"/>
+      <c r="C103" s="9"/>
+      <c r="D103" s="9"/>
       <c r="M103" s="6"/>
     </row>
     <row r="104" spans="1:13">
-      <c r="A104" s="11"/>
-      <c r="B104" s="11"/>
-      <c r="C104" s="11"/>
-      <c r="D104" s="11"/>
+      <c r="A104" s="9"/>
+      <c r="B104" s="9"/>
+      <c r="C104" s="9"/>
+      <c r="D104" s="9"/>
       <c r="M104" s="6"/>
     </row>
     <row r="105" spans="1:13">
-      <c r="A105" s="11"/>
-      <c r="B105" s="11"/>
-      <c r="C105" s="11"/>
-      <c r="D105" s="11"/>
+      <c r="A105" s="9"/>
+      <c r="B105" s="9"/>
+      <c r="C105" s="9"/>
+      <c r="D105" s="9"/>
       <c r="M105" s="6"/>
     </row>
     <row r="106" spans="1:13">
-      <c r="A106" s="11"/>
-      <c r="B106" s="11"/>
-      <c r="C106" s="11"/>
-      <c r="D106" s="11"/>
+      <c r="A106" s="9"/>
+      <c r="B106" s="9"/>
+      <c r="C106" s="9"/>
+      <c r="D106" s="9"/>
       <c r="M106" s="6"/>
     </row>
     <row r="107" spans="1:13">
-      <c r="A107" s="11"/>
-      <c r="B107" s="11"/>
-      <c r="C107" s="11"/>
-      <c r="D107" s="11"/>
+      <c r="A107" s="9"/>
+      <c r="B107" s="9"/>
+      <c r="C107" s="9"/>
+      <c r="D107" s="9"/>
       <c r="M107" s="6"/>
     </row>
     <row r="108" spans="1:13">
-      <c r="A108" s="11"/>
-      <c r="B108" s="11"/>
-      <c r="C108" s="11"/>
-      <c r="D108" s="11"/>
+      <c r="A108" s="9"/>
+      <c r="B108" s="9"/>
+      <c r="C108" s="9"/>
+      <c r="D108" s="9"/>
       <c r="M108" s="6"/>
     </row>
     <row r="109" spans="1:13">
-      <c r="A109" s="11"/>
-      <c r="B109" s="11"/>
-      <c r="C109" s="11"/>
-      <c r="D109" s="11"/>
+      <c r="A109" s="9"/>
+      <c r="B109" s="9"/>
+      <c r="C109" s="9"/>
+      <c r="D109" s="9"/>
       <c r="M109" s="6"/>
     </row>
     <row r="110" spans="1:13">
-      <c r="A110" s="11"/>
-      <c r="B110" s="11"/>
-      <c r="C110" s="11"/>
-      <c r="D110" s="11"/>
+      <c r="A110" s="9"/>
+      <c r="B110" s="9"/>
+      <c r="C110" s="9"/>
+      <c r="D110" s="9"/>
       <c r="M110" s="6"/>
     </row>
     <row r="111" spans="1:13">
-      <c r="A111" s="11"/>
-      <c r="B111" s="11"/>
-      <c r="C111" s="11"/>
-      <c r="D111" s="11"/>
+      <c r="A111" s="9"/>
+      <c r="B111" s="9"/>
+      <c r="C111" s="9"/>
+      <c r="D111" s="9"/>
       <c r="M111" s="6"/>
     </row>
     <row r="112" spans="1:13">
-      <c r="A112" s="11"/>
-      <c r="B112" s="11"/>
-      <c r="C112" s="11"/>
-      <c r="D112" s="11"/>
+      <c r="A112" s="9"/>
+      <c r="B112" s="9"/>
+      <c r="C112" s="9"/>
+      <c r="D112" s="9"/>
       <c r="M112" s="6"/>
     </row>
     <row r="113" spans="1:13">
-      <c r="A113" s="11"/>
-      <c r="B113" s="11"/>
-      <c r="C113" s="11"/>
-      <c r="D113" s="11"/>
+      <c r="A113" s="9"/>
+      <c r="B113" s="9"/>
+      <c r="C113" s="9"/>
+      <c r="D113" s="9"/>
       <c r="M113" s="6"/>
     </row>
     <row r="114" spans="1:13">
-      <c r="A114" s="11"/>
-      <c r="B114" s="11"/>
-      <c r="C114" s="11"/>
-      <c r="D114" s="11"/>
+      <c r="A114" s="9"/>
+      <c r="B114" s="9"/>
+      <c r="C114" s="9"/>
+      <c r="D114" s="9"/>
       <c r="M114" s="6"/>
     </row>
     <row r="115" spans="1:13">
-      <c r="A115" s="11"/>
-      <c r="B115" s="11"/>
-      <c r="C115" s="11"/>
-      <c r="D115" s="11"/>
+      <c r="A115" s="9"/>
+      <c r="B115" s="9"/>
+      <c r="C115" s="9"/>
+      <c r="D115" s="9"/>
       <c r="M115" s="6"/>
     </row>
     <row r="116" spans="1:13">
-      <c r="A116" s="11"/>
-      <c r="B116" s="11"/>
-      <c r="C116" s="11"/>
-      <c r="D116" s="11"/>
+      <c r="A116" s="9"/>
+      <c r="B116" s="9"/>
+      <c r="C116" s="9"/>
+      <c r="D116" s="9"/>
       <c r="M116" s="6"/>
     </row>
     <row r="117" spans="1:13">
-      <c r="A117" s="11"/>
-      <c r="B117" s="11"/>
-      <c r="C117" s="11"/>
-      <c r="D117" s="11"/>
+      <c r="A117" s="9"/>
+      <c r="B117" s="9"/>
+      <c r="C117" s="9"/>
+      <c r="D117" s="9"/>
       <c r="M117" s="6"/>
     </row>
     <row r="118" spans="1:13">
-      <c r="A118" s="11"/>
-      <c r="B118" s="11"/>
-      <c r="C118" s="11"/>
-      <c r="D118" s="11"/>
+      <c r="A118" s="9"/>
+      <c r="B118" s="9"/>
+      <c r="C118" s="9"/>
+      <c r="D118" s="9"/>
       <c r="M118" s="6"/>
     </row>
     <row r="119" spans="1:13">
-      <c r="A119" s="11"/>
-      <c r="B119" s="11"/>
-      <c r="C119" s="11"/>
-      <c r="D119" s="11"/>
+      <c r="A119" s="9"/>
+      <c r="B119" s="9"/>
+      <c r="C119" s="9"/>
+      <c r="D119" s="9"/>
       <c r="M119" s="6"/>
     </row>
     <row r="120" spans="1:13">
-      <c r="A120" s="11"/>
-      <c r="B120" s="11"/>
-      <c r="C120" s="11"/>
-      <c r="D120" s="11"/>
+      <c r="A120" s="9"/>
+      <c r="B120" s="9"/>
+      <c r="C120" s="9"/>
+      <c r="D120" s="9"/>
       <c r="M120" s="6"/>
     </row>
     <row r="121" spans="1:13">
-      <c r="A121" s="11"/>
-      <c r="B121" s="11"/>
-      <c r="C121" s="11"/>
-      <c r="D121" s="11"/>
+      <c r="A121" s="9"/>
+      <c r="B121" s="9"/>
+      <c r="C121" s="9"/>
+      <c r="D121" s="9"/>
       <c r="M121" s="6"/>
     </row>
     <row r="122" spans="1:13">
-      <c r="A122" s="11"/>
-      <c r="B122" s="11"/>
-      <c r="C122" s="11"/>
-      <c r="D122" s="11"/>
+      <c r="A122" s="9"/>
+      <c r="B122" s="9"/>
+      <c r="C122" s="9"/>
+      <c r="D122" s="9"/>
       <c r="M122" s="6"/>
     </row>
     <row r="123" spans="1:13">
-      <c r="A123" s="11"/>
-      <c r="B123" s="11"/>
-      <c r="C123" s="11"/>
-      <c r="D123" s="11"/>
+      <c r="A123" s="9"/>
+      <c r="B123" s="9"/>
+      <c r="C123" s="9"/>
+      <c r="D123" s="9"/>
       <c r="M123" s="6"/>
     </row>
     <row r="124" spans="1:13">
-      <c r="A124" s="11"/>
-      <c r="B124" s="11"/>
-      <c r="C124" s="11"/>
-      <c r="D124" s="11"/>
+      <c r="A124" s="9"/>
+      <c r="B124" s="9"/>
+      <c r="C124" s="9"/>
+      <c r="D124" s="9"/>
       <c r="M124" s="6"/>
     </row>
     <row r="125" spans="1:13">
-      <c r="A125" s="11"/>
-      <c r="B125" s="11"/>
-      <c r="C125" s="11"/>
-      <c r="D125" s="11"/>
+      <c r="A125" s="9"/>
+      <c r="B125" s="9"/>
+      <c r="C125" s="9"/>
+      <c r="D125" s="9"/>
       <c r="M125" s="6"/>
     </row>
     <row r="126" spans="1:13">
-      <c r="A126" s="11"/>
-      <c r="B126" s="11"/>
-      <c r="C126" s="11"/>
-      <c r="D126" s="11"/>
+      <c r="A126" s="9"/>
+      <c r="B126" s="9"/>
+      <c r="C126" s="9"/>
+      <c r="D126" s="9"/>
       <c r="M126" s="6"/>
     </row>
     <row r="127" spans="1:13">
-      <c r="A127" s="11"/>
-      <c r="B127" s="11"/>
-      <c r="C127" s="11"/>
-      <c r="D127" s="11"/>
+      <c r="A127" s="9"/>
+      <c r="B127" s="9"/>
+      <c r="C127" s="9"/>
+      <c r="D127" s="9"/>
       <c r="M127" s="6"/>
     </row>
     <row r="128" spans="1:13">
-      <c r="A128" s="11"/>
-      <c r="B128" s="11"/>
-      <c r="C128" s="11"/>
-      <c r="D128" s="11"/>
+      <c r="A128" s="9"/>
+      <c r="B128" s="9"/>
+      <c r="C128" s="9"/>
+      <c r="D128" s="9"/>
       <c r="M128" s="6"/>
     </row>
     <row r="129" spans="1:13">
-      <c r="A129" s="11"/>
-      <c r="B129" s="11"/>
-      <c r="C129" s="11"/>
-      <c r="D129" s="11"/>
+      <c r="A129" s="9"/>
+      <c r="B129" s="9"/>
+      <c r="C129" s="9"/>
+      <c r="D129" s="9"/>
       <c r="M129" s="6"/>
     </row>
     <row r="130" spans="1:13">
-      <c r="A130" s="11"/>
-      <c r="B130" s="11"/>
-      <c r="C130" s="11"/>
-      <c r="D130" s="11"/>
+      <c r="A130" s="9"/>
+      <c r="B130" s="9"/>
+      <c r="C130" s="9"/>
+      <c r="D130" s="9"/>
       <c r="M130" s="6"/>
     </row>
     <row r="131" spans="1:13">
-      <c r="A131" s="11"/>
-      <c r="B131" s="11"/>
-      <c r="C131" s="11"/>
-      <c r="D131" s="11"/>
+      <c r="A131" s="9"/>
+      <c r="B131" s="9"/>
+      <c r="C131" s="9"/>
+      <c r="D131" s="9"/>
       <c r="M131" s="6"/>
     </row>
     <row r="132" spans="1:13">
-      <c r="A132" s="11"/>
-      <c r="B132" s="11"/>
-      <c r="C132" s="11"/>
-      <c r="D132" s="11"/>
+      <c r="A132" s="9"/>
+      <c r="B132" s="9"/>
+      <c r="C132" s="9"/>
+      <c r="D132" s="9"/>
       <c r="M132" s="6"/>
     </row>
     <row r="133" spans="1:13">
-      <c r="A133" s="11"/>
-      <c r="B133" s="11"/>
-      <c r="C133" s="11"/>
-      <c r="D133" s="11"/>
+      <c r="A133" s="9"/>
+      <c r="B133" s="9"/>
+      <c r="C133" s="9"/>
+      <c r="D133" s="9"/>
       <c r="M133" s="6"/>
     </row>
     <row r="134" spans="1:13">
-      <c r="A134" s="11"/>
-      <c r="B134" s="11"/>
-      <c r="C134" s="11"/>
-      <c r="D134" s="11"/>
+      <c r="A134" s="9"/>
+      <c r="B134" s="9"/>
+      <c r="C134" s="9"/>
+      <c r="D134" s="9"/>
       <c r="M134" s="6"/>
     </row>
     <row r="135" spans="1:13">
-      <c r="A135" s="11"/>
-      <c r="B135" s="11"/>
-      <c r="C135" s="11"/>
-      <c r="D135" s="11"/>
+      <c r="A135" s="9"/>
+      <c r="B135" s="9"/>
+      <c r="C135" s="9"/>
+      <c r="D135" s="9"/>
       <c r="M135" s="6"/>
     </row>
     <row r="136" spans="1:13">
-      <c r="A136" s="11"/>
-      <c r="B136" s="11"/>
-      <c r="C136" s="11"/>
-      <c r="D136" s="11"/>
+      <c r="A136" s="9"/>
+      <c r="B136" s="9"/>
+      <c r="C136" s="9"/>
+      <c r="D136" s="9"/>
       <c r="M136" s="6"/>
     </row>
     <row r="137" spans="1:13">
-      <c r="A137" s="11"/>
-      <c r="B137" s="11"/>
-      <c r="C137" s="11"/>
-      <c r="D137" s="11"/>
+      <c r="A137" s="9"/>
+      <c r="B137" s="9"/>
+      <c r="C137" s="9"/>
+      <c r="D137" s="9"/>
       <c r="M137" s="6"/>
     </row>
     <row r="138" spans="1:13">
-      <c r="A138" s="11"/>
-      <c r="B138" s="11"/>
-      <c r="C138" s="11"/>
-      <c r="D138" s="11"/>
+      <c r="A138" s="9"/>
+      <c r="B138" s="9"/>
+      <c r="C138" s="9"/>
+      <c r="D138" s="9"/>
       <c r="M138" s="6"/>
     </row>
     <row r="139" spans="1:13">
-      <c r="A139" s="11"/>
-      <c r="B139" s="11"/>
-      <c r="C139" s="11"/>
-      <c r="D139" s="11"/>
+      <c r="A139" s="9"/>
+      <c r="B139" s="9"/>
+      <c r="C139" s="9"/>
+      <c r="D139" s="9"/>
       <c r="M139" s="6"/>
     </row>
     <row r="140" spans="1:13">
-      <c r="A140" s="11"/>
-      <c r="B140" s="11"/>
-      <c r="C140" s="11"/>
-      <c r="D140" s="11"/>
+      <c r="A140" s="9"/>
+      <c r="B140" s="9"/>
+      <c r="C140" s="9"/>
+      <c r="D140" s="9"/>
       <c r="M140" s="6"/>
     </row>
     <row r="141" spans="1:13">
-      <c r="A141" s="11"/>
-      <c r="B141" s="11"/>
-      <c r="C141" s="11"/>
-      <c r="D141" s="11"/>
+      <c r="A141" s="9"/>
+      <c r="B141" s="9"/>
+      <c r="C141" s="9"/>
+      <c r="D141" s="9"/>
       <c r="M141" s="6"/>
     </row>
     <row r="142" spans="1:13">
-      <c r="A142" s="11"/>
-      <c r="B142" s="11"/>
-      <c r="C142" s="11"/>
-      <c r="D142" s="11"/>
+      <c r="A142" s="9"/>
+      <c r="B142" s="9"/>
+      <c r="C142" s="9"/>
+      <c r="D142" s="9"/>
       <c r="M142" s="6"/>
     </row>
     <row r="143" spans="1:13">
-      <c r="A143" s="11"/>
-      <c r="B143" s="11"/>
-      <c r="C143" s="11"/>
-      <c r="D143" s="11"/>
+      <c r="A143" s="9"/>
+      <c r="B143" s="9"/>
+      <c r="C143" s="9"/>
+      <c r="D143" s="9"/>
       <c r="M143" s="6"/>
     </row>
     <row r="144" spans="1:13">
-      <c r="A144" s="11"/>
-      <c r="B144" s="11"/>
-      <c r="C144" s="11"/>
-      <c r="D144" s="11"/>
+      <c r="A144" s="9"/>
+      <c r="B144" s="9"/>
+      <c r="C144" s="9"/>
+      <c r="D144" s="9"/>
       <c r="M144" s="6"/>
     </row>
     <row r="145" spans="1:13">
-      <c r="A145" s="11"/>
-      <c r="B145" s="11"/>
-      <c r="C145" s="11"/>
-      <c r="D145" s="11"/>
+      <c r="A145" s="9"/>
+      <c r="B145" s="9"/>
+      <c r="C145" s="9"/>
+      <c r="D145" s="9"/>
       <c r="M145" s="6"/>
     </row>
     <row r="146" spans="1:13">
-      <c r="A146" s="11"/>
-      <c r="B146" s="11"/>
-      <c r="C146" s="11"/>
-      <c r="D146" s="11"/>
+      <c r="A146" s="9"/>
+      <c r="B146" s="9"/>
+      <c r="C146" s="9"/>
+      <c r="D146" s="9"/>
       <c r="M146" s="6"/>
     </row>
     <row r="147" spans="1:13">
-      <c r="A147" s="11"/>
-      <c r="B147" s="11"/>
-      <c r="C147" s="11"/>
-      <c r="D147" s="11"/>
+      <c r="A147" s="9"/>
+      <c r="B147" s="9"/>
+      <c r="C147" s="9"/>
+      <c r="D147" s="9"/>
       <c r="M147" s="6"/>
     </row>
     <row r="148" spans="1:13">
-      <c r="A148" s="11"/>
-      <c r="B148" s="11"/>
-      <c r="C148" s="11"/>
-      <c r="D148" s="11"/>
+      <c r="A148" s="9"/>
+      <c r="B148" s="9"/>
+      <c r="C148" s="9"/>
+      <c r="D148" s="9"/>
       <c r="M148" s="6"/>
     </row>
     <row r="149" spans="1:13">
-      <c r="A149" s="11"/>
-      <c r="B149" s="11"/>
-      <c r="C149" s="11"/>
-      <c r="D149" s="11"/>
+      <c r="A149" s="9"/>
+      <c r="B149" s="9"/>
+      <c r="C149" s="9"/>
+      <c r="D149" s="9"/>
       <c r="M149" s="6"/>
     </row>
     <row r="150" spans="1:13">
-      <c r="A150" s="11"/>
-      <c r="B150" s="11"/>
-      <c r="C150" s="11"/>
-      <c r="D150" s="11"/>
+      <c r="A150" s="9"/>
+      <c r="B150" s="9"/>
+      <c r="C150" s="9"/>
+      <c r="D150" s="9"/>
       <c r="M150" s="6"/>
     </row>
     <row r="151" spans="1:13">
-      <c r="A151" s="11"/>
-      <c r="B151" s="11"/>
-      <c r="C151" s="11"/>
-      <c r="D151" s="11"/>
+      <c r="A151" s="9"/>
+      <c r="B151" s="9"/>
+      <c r="C151" s="9"/>
+      <c r="D151" s="9"/>
       <c r="M151" s="6"/>
     </row>
     <row r="152" spans="1:13">
-      <c r="A152" s="11"/>
-      <c r="B152" s="11"/>
-      <c r="C152" s="11"/>
-      <c r="D152" s="11"/>
+      <c r="A152" s="9"/>
+      <c r="B152" s="9"/>
+      <c r="C152" s="9"/>
+      <c r="D152" s="9"/>
       <c r="M152" s="6"/>
     </row>
     <row r="153" spans="1:13">
-      <c r="A153" s="11"/>
-      <c r="B153" s="11"/>
-      <c r="C153" s="11"/>
-      <c r="D153" s="11"/>
+      <c r="A153" s="9"/>
+      <c r="B153" s="9"/>
+      <c r="C153" s="9"/>
+      <c r="D153" s="9"/>
       <c r="M153" s="6"/>
     </row>
     <row r="154" spans="1:13">
-      <c r="A154" s="11"/>
-      <c r="B154" s="11"/>
-      <c r="C154" s="11"/>
-      <c r="D154" s="11"/>
+      <c r="A154" s="9"/>
+      <c r="B154" s="9"/>
+      <c r="C154" s="9"/>
+      <c r="D154" s="9"/>
       <c r="M154" s="6"/>
     </row>
     <row r="155" spans="1:13">
-      <c r="A155" s="11"/>
-      <c r="B155" s="11"/>
-      <c r="C155" s="11"/>
-      <c r="D155" s="11"/>
+      <c r="A155" s="9"/>
+      <c r="B155" s="9"/>
+      <c r="C155" s="9"/>
+      <c r="D155" s="9"/>
       <c r="M155" s="6"/>
     </row>
     <row r="156" spans="1:13">
-      <c r="A156" s="11"/>
-      <c r="B156" s="11"/>
-      <c r="C156" s="11"/>
-      <c r="D156" s="11"/>
+      <c r="A156" s="9"/>
+      <c r="B156" s="9"/>
+      <c r="C156" s="9"/>
+      <c r="D156" s="9"/>
       <c r="M156" s="6"/>
     </row>
     <row r="157" spans="1:13">
-      <c r="A157" s="11"/>
-      <c r="B157" s="11"/>
-      <c r="C157" s="11"/>
-      <c r="D157" s="11"/>
+      <c r="A157" s="9"/>
+      <c r="B157" s="9"/>
+      <c r="C157" s="9"/>
+      <c r="D157" s="9"/>
       <c r="M157" s="6"/>
     </row>
     <row r="158" spans="1:13">
-      <c r="A158" s="11"/>
-      <c r="B158" s="11"/>
-      <c r="C158" s="11"/>
-      <c r="D158" s="11"/>
+      <c r="A158" s="9"/>
+      <c r="B158" s="9"/>
+      <c r="C158" s="9"/>
+      <c r="D158" s="9"/>
       <c r="M158" s="6"/>
     </row>
     <row r="159" spans="1:13">
-      <c r="A159" s="11"/>
-      <c r="B159" s="11"/>
-      <c r="C159" s="11"/>
-      <c r="D159" s="11"/>
+      <c r="A159" s="9"/>
+      <c r="B159" s="9"/>
+      <c r="C159" s="9"/>
+      <c r="D159" s="9"/>
       <c r="M159" s="6"/>
     </row>
     <row r="160" spans="1:13">
-      <c r="A160" s="11"/>
-      <c r="B160" s="11"/>
-      <c r="C160" s="11"/>
-      <c r="D160" s="11"/>
+      <c r="A160" s="9"/>
+      <c r="B160" s="9"/>
+      <c r="C160" s="9"/>
+      <c r="D160" s="9"/>
       <c r="M160" s="6"/>
     </row>
     <row r="161" spans="1:13">
-      <c r="A161" s="11"/>
-      <c r="B161" s="11"/>
-      <c r="C161" s="11"/>
-      <c r="D161" s="11"/>
+      <c r="A161" s="9"/>
+      <c r="B161" s="9"/>
+      <c r="C161" s="9"/>
+      <c r="D161" s="9"/>
       <c r="M161" s="6"/>
     </row>
     <row r="162" spans="1:13">
-      <c r="A162" s="11"/>
-      <c r="B162" s="11"/>
-      <c r="C162" s="11"/>
-      <c r="D162" s="11"/>
+      <c r="A162" s="9"/>
+      <c r="B162" s="9"/>
+      <c r="C162" s="9"/>
+      <c r="D162" s="9"/>
       <c r="M162" s="6"/>
     </row>
     <row r="163" spans="1:13">
-      <c r="A163" s="11"/>
-      <c r="B163" s="11"/>
-      <c r="C163" s="11"/>
-      <c r="D163" s="11"/>
+      <c r="A163" s="9"/>
+      <c r="B163" s="9"/>
+      <c r="C163" s="9"/>
+      <c r="D163" s="9"/>
       <c r="M163" s="6"/>
     </row>
     <row r="164" spans="1:13">
-      <c r="A164" s="11"/>
-      <c r="B164" s="11"/>
-      <c r="C164" s="11"/>
-      <c r="D164" s="11"/>
+      <c r="A164" s="9"/>
+      <c r="B164" s="9"/>
+      <c r="C164" s="9"/>
+      <c r="D164" s="9"/>
       <c r="M164" s="6"/>
     </row>
     <row r="165" spans="1:13">
-      <c r="A165" s="11"/>
-      <c r="B165" s="11"/>
-      <c r="C165" s="11"/>
-      <c r="D165" s="11"/>
+      <c r="A165" s="9"/>
+      <c r="B165" s="9"/>
+      <c r="C165" s="9"/>
+      <c r="D165" s="9"/>
       <c r="M165" s="6"/>
     </row>
     <row r="166" spans="1:13">
-      <c r="A166" s="11"/>
-      <c r="B166" s="11"/>
-      <c r="C166" s="11"/>
-      <c r="D166" s="11"/>
+      <c r="A166" s="9"/>
+      <c r="B166" s="9"/>
+      <c r="C166" s="9"/>
+      <c r="D166" s="9"/>
       <c r="M166" s="6"/>
     </row>
     <row r="167" spans="1:13">
@@ -2355,10 +2521,10 @@
       <c r="M167" s="6"/>
     </row>
     <row r="168" spans="1:13">
-      <c r="A168" s="11"/>
-      <c r="B168" s="11"/>
-      <c r="C168" s="11"/>
-      <c r="D168" s="11"/>
+      <c r="A168" s="9"/>
+      <c r="B168" s="9"/>
+      <c r="C168" s="9"/>
+      <c r="D168" s="9"/>
       <c r="M168" s="6"/>
     </row>
     <row r="169" spans="1:13">
@@ -2367,66 +2533,66 @@
       <c r="M169" s="6"/>
     </row>
     <row r="170" spans="1:13">
-      <c r="A170" s="11"/>
-      <c r="B170" s="11"/>
-      <c r="C170" s="11"/>
-      <c r="D170" s="11"/>
+      <c r="A170" s="9"/>
+      <c r="B170" s="9"/>
+      <c r="C170" s="9"/>
+      <c r="D170" s="9"/>
       <c r="M170" s="6"/>
     </row>
     <row r="171" spans="1:13">
-      <c r="A171" s="11"/>
-      <c r="B171" s="11"/>
-      <c r="C171" s="11"/>
-      <c r="D171" s="11"/>
+      <c r="A171" s="9"/>
+      <c r="B171" s="9"/>
+      <c r="C171" s="9"/>
+      <c r="D171" s="9"/>
       <c r="M171" s="6"/>
     </row>
     <row r="172" spans="1:13">
-      <c r="A172" s="11"/>
-      <c r="B172" s="11"/>
-      <c r="C172" s="11"/>
-      <c r="D172" s="11"/>
+      <c r="A172" s="9"/>
+      <c r="B172" s="9"/>
+      <c r="C172" s="9"/>
+      <c r="D172" s="9"/>
       <c r="M172" s="6"/>
     </row>
     <row r="173" spans="1:13">
-      <c r="A173" s="11"/>
-      <c r="B173" s="11"/>
-      <c r="C173" s="11"/>
-      <c r="D173" s="11"/>
+      <c r="A173" s="9"/>
+      <c r="B173" s="9"/>
+      <c r="C173" s="9"/>
+      <c r="D173" s="9"/>
       <c r="M173" s="6"/>
     </row>
     <row r="174" spans="1:13">
-      <c r="A174" s="11"/>
-      <c r="B174" s="11"/>
-      <c r="C174" s="11"/>
-      <c r="D174" s="11"/>
+      <c r="A174" s="9"/>
+      <c r="B174" s="9"/>
+      <c r="C174" s="9"/>
+      <c r="D174" s="9"/>
       <c r="M174" s="6"/>
     </row>
     <row r="175" spans="1:13">
-      <c r="A175" s="11"/>
-      <c r="B175" s="11"/>
-      <c r="C175" s="11"/>
-      <c r="D175" s="11"/>
+      <c r="A175" s="9"/>
+      <c r="B175" s="9"/>
+      <c r="C175" s="9"/>
+      <c r="D175" s="9"/>
       <c r="M175" s="6"/>
     </row>
     <row r="176" spans="1:13">
-      <c r="A176" s="11"/>
-      <c r="B176" s="11"/>
-      <c r="C176" s="11"/>
-      <c r="D176" s="11"/>
+      <c r="A176" s="9"/>
+      <c r="B176" s="9"/>
+      <c r="C176" s="9"/>
+      <c r="D176" s="9"/>
       <c r="M176" s="6"/>
     </row>
     <row r="177" spans="1:13">
-      <c r="A177" s="11"/>
-      <c r="B177" s="11"/>
-      <c r="C177" s="11"/>
-      <c r="D177" s="11"/>
+      <c r="A177" s="9"/>
+      <c r="B177" s="9"/>
+      <c r="C177" s="9"/>
+      <c r="D177" s="9"/>
       <c r="M177" s="6"/>
     </row>
     <row r="178" spans="1:13">
-      <c r="A178" s="11"/>
-      <c r="B178" s="11"/>
-      <c r="C178" s="11"/>
-      <c r="D178" s="11"/>
+      <c r="A178" s="9"/>
+      <c r="B178" s="9"/>
+      <c r="C178" s="9"/>
+      <c r="D178" s="9"/>
       <c r="M178" s="6"/>
     </row>
     <row r="179" spans="1:13">
@@ -2435,59 +2601,59 @@
       <c r="M179" s="6"/>
     </row>
     <row r="180" spans="1:13">
-      <c r="A180" s="11"/>
-      <c r="B180" s="11"/>
-      <c r="C180" s="11"/>
-      <c r="D180" s="11"/>
+      <c r="A180" s="9"/>
+      <c r="B180" s="9"/>
+      <c r="C180" s="9"/>
+      <c r="D180" s="9"/>
       <c r="M180" s="6"/>
     </row>
     <row r="181" spans="1:13">
-      <c r="A181" s="11"/>
-      <c r="B181" s="11"/>
-      <c r="C181" s="11"/>
-      <c r="D181" s="11"/>
+      <c r="A181" s="9"/>
+      <c r="B181" s="9"/>
+      <c r="C181" s="9"/>
+      <c r="D181" s="9"/>
       <c r="M181" s="6"/>
     </row>
     <row r="182" spans="1:13">
-      <c r="A182" s="11"/>
-      <c r="B182" s="11"/>
-      <c r="C182" s="11"/>
-      <c r="D182" s="11"/>
+      <c r="A182" s="9"/>
+      <c r="B182" s="9"/>
+      <c r="C182" s="9"/>
+      <c r="D182" s="9"/>
       <c r="M182" s="6"/>
     </row>
     <row r="183" spans="1:13">
-      <c r="A183" s="11"/>
-      <c r="B183" s="11"/>
-      <c r="C183" s="11"/>
-      <c r="D183" s="11"/>
+      <c r="A183" s="9"/>
+      <c r="B183" s="9"/>
+      <c r="C183" s="9"/>
+      <c r="D183" s="9"/>
       <c r="M183" s="6"/>
     </row>
     <row r="184" spans="1:13">
-      <c r="A184" s="11"/>
-      <c r="B184" s="11"/>
-      <c r="C184" s="11"/>
-      <c r="D184" s="11"/>
+      <c r="A184" s="9"/>
+      <c r="B184" s="9"/>
+      <c r="C184" s="9"/>
+      <c r="D184" s="9"/>
       <c r="M184" s="6"/>
     </row>
     <row r="185" spans="1:13">
-      <c r="A185" s="11"/>
-      <c r="B185" s="11"/>
-      <c r="C185" s="11"/>
-      <c r="D185" s="11"/>
+      <c r="A185" s="9"/>
+      <c r="B185" s="9"/>
+      <c r="C185" s="9"/>
+      <c r="D185" s="9"/>
       <c r="M185" s="6"/>
     </row>
     <row r="186" spans="1:13">
-      <c r="A186" s="11"/>
-      <c r="B186" s="11"/>
-      <c r="C186" s="11"/>
-      <c r="D186" s="11"/>
+      <c r="A186" s="9"/>
+      <c r="B186" s="9"/>
+      <c r="C186" s="9"/>
+      <c r="D186" s="9"/>
       <c r="M186" s="6"/>
     </row>
     <row r="187" spans="1:13">
-      <c r="A187" s="11"/>
-      <c r="B187" s="11"/>
-      <c r="C187" s="11"/>
-      <c r="D187" s="11"/>
+      <c r="A187" s="9"/>
+      <c r="B187" s="9"/>
+      <c r="C187" s="9"/>
+      <c r="D187" s="9"/>
       <c r="M187" s="6"/>
     </row>
     <row r="188" spans="1:13">
@@ -2496,66 +2662,66 @@
       <c r="M188" s="6"/>
     </row>
     <row r="189" spans="1:13">
-      <c r="A189" s="11"/>
-      <c r="B189" s="11"/>
-      <c r="C189" s="11"/>
-      <c r="D189" s="11"/>
+      <c r="A189" s="9"/>
+      <c r="B189" s="9"/>
+      <c r="C189" s="9"/>
+      <c r="D189" s="9"/>
       <c r="M189" s="6"/>
     </row>
     <row r="190" spans="1:13">
-      <c r="A190" s="11"/>
-      <c r="B190" s="11"/>
-      <c r="C190" s="11"/>
-      <c r="D190" s="11"/>
+      <c r="A190" s="9"/>
+      <c r="B190" s="9"/>
+      <c r="C190" s="9"/>
+      <c r="D190" s="9"/>
       <c r="M190" s="6"/>
     </row>
     <row r="191" spans="1:13">
-      <c r="A191" s="11"/>
-      <c r="B191" s="11"/>
-      <c r="C191" s="11"/>
-      <c r="D191" s="11"/>
+      <c r="A191" s="9"/>
+      <c r="B191" s="9"/>
+      <c r="C191" s="9"/>
+      <c r="D191" s="9"/>
       <c r="M191" s="6"/>
     </row>
     <row r="192" spans="1:13">
-      <c r="A192" s="11"/>
-      <c r="B192" s="11"/>
-      <c r="C192" s="11"/>
-      <c r="D192" s="11"/>
+      <c r="A192" s="9"/>
+      <c r="B192" s="9"/>
+      <c r="C192" s="9"/>
+      <c r="D192" s="9"/>
       <c r="M192" s="6"/>
     </row>
     <row r="193" spans="1:13">
-      <c r="A193" s="11"/>
-      <c r="B193" s="11"/>
-      <c r="C193" s="11"/>
-      <c r="D193" s="11"/>
+      <c r="A193" s="9"/>
+      <c r="B193" s="9"/>
+      <c r="C193" s="9"/>
+      <c r="D193" s="9"/>
       <c r="M193" s="6"/>
     </row>
     <row r="194" spans="1:13">
-      <c r="A194" s="11"/>
-      <c r="B194" s="11"/>
-      <c r="C194" s="11"/>
-      <c r="D194" s="11"/>
+      <c r="A194" s="9"/>
+      <c r="B194" s="9"/>
+      <c r="C194" s="9"/>
+      <c r="D194" s="9"/>
       <c r="M194" s="6"/>
     </row>
     <row r="195" spans="1:13">
-      <c r="A195" s="11"/>
-      <c r="B195" s="11"/>
-      <c r="C195" s="11"/>
-      <c r="D195" s="11"/>
+      <c r="A195" s="9"/>
+      <c r="B195" s="9"/>
+      <c r="C195" s="9"/>
+      <c r="D195" s="9"/>
       <c r="M195" s="6"/>
     </row>
     <row r="196" spans="1:13">
-      <c r="A196" s="11"/>
-      <c r="B196" s="11"/>
-      <c r="C196" s="11"/>
-      <c r="D196" s="11"/>
+      <c r="A196" s="9"/>
+      <c r="B196" s="9"/>
+      <c r="C196" s="9"/>
+      <c r="D196" s="9"/>
       <c r="M196" s="6"/>
     </row>
     <row r="197" spans="1:13">
-      <c r="A197" s="11"/>
-      <c r="B197" s="11"/>
-      <c r="C197" s="11"/>
-      <c r="D197" s="11"/>
+      <c r="A197" s="9"/>
+      <c r="B197" s="9"/>
+      <c r="C197" s="9"/>
+      <c r="D197" s="9"/>
       <c r="M197" s="6"/>
     </row>
     <row r="198" spans="1:13">
@@ -2564,45 +2730,45 @@
       <c r="M198" s="6"/>
     </row>
     <row r="199" spans="1:13">
-      <c r="A199" s="11"/>
-      <c r="B199" s="11"/>
-      <c r="C199" s="11"/>
-      <c r="D199" s="11"/>
+      <c r="A199" s="9"/>
+      <c r="B199" s="9"/>
+      <c r="C199" s="9"/>
+      <c r="D199" s="9"/>
       <c r="M199" s="6"/>
     </row>
     <row r="200" spans="1:13">
-      <c r="A200" s="11"/>
-      <c r="B200" s="11"/>
-      <c r="C200" s="11"/>
-      <c r="D200" s="11"/>
+      <c r="A200" s="9"/>
+      <c r="B200" s="9"/>
+      <c r="C200" s="9"/>
+      <c r="D200" s="9"/>
       <c r="M200" s="6"/>
     </row>
     <row r="201" spans="1:13">
-      <c r="A201" s="11"/>
-      <c r="B201" s="11"/>
-      <c r="C201" s="11"/>
-      <c r="D201" s="11"/>
+      <c r="A201" s="9"/>
+      <c r="B201" s="9"/>
+      <c r="C201" s="9"/>
+      <c r="D201" s="9"/>
       <c r="M201" s="6"/>
     </row>
     <row r="202" spans="1:13">
-      <c r="A202" s="11"/>
-      <c r="B202" s="11"/>
-      <c r="C202" s="11"/>
-      <c r="D202" s="11"/>
+      <c r="A202" s="9"/>
+      <c r="B202" s="9"/>
+      <c r="C202" s="9"/>
+      <c r="D202" s="9"/>
       <c r="M202" s="6"/>
     </row>
     <row r="203" spans="1:13">
-      <c r="A203" s="11"/>
-      <c r="B203" s="11"/>
-      <c r="C203" s="11"/>
-      <c r="D203" s="11"/>
+      <c r="A203" s="9"/>
+      <c r="B203" s="9"/>
+      <c r="C203" s="9"/>
+      <c r="D203" s="9"/>
       <c r="M203" s="6"/>
     </row>
     <row r="204" spans="1:13">
-      <c r="A204" s="11"/>
-      <c r="B204" s="11"/>
-      <c r="C204" s="11"/>
-      <c r="D204" s="11"/>
+      <c r="A204" s="9"/>
+      <c r="B204" s="9"/>
+      <c r="C204" s="9"/>
+      <c r="D204" s="9"/>
       <c r="M204" s="6"/>
     </row>
     <row r="205" spans="1:13">
@@ -2611,17 +2777,17 @@
       <c r="M205" s="6"/>
     </row>
     <row r="206" spans="1:13">
-      <c r="A206" s="11"/>
-      <c r="B206" s="11"/>
-      <c r="C206" s="11"/>
-      <c r="D206" s="11"/>
+      <c r="A206" s="9"/>
+      <c r="B206" s="9"/>
+      <c r="C206" s="9"/>
+      <c r="D206" s="9"/>
       <c r="M206" s="6"/>
     </row>
     <row r="207" spans="1:13">
-      <c r="A207" s="11"/>
-      <c r="B207" s="11"/>
-      <c r="C207" s="11"/>
-      <c r="D207" s="11"/>
+      <c r="A207" s="9"/>
+      <c r="B207" s="9"/>
+      <c r="C207" s="9"/>
+      <c r="D207" s="9"/>
       <c r="M207" s="6"/>
     </row>
     <row r="208" spans="1:13">
@@ -2630,143 +2796,143 @@
       <c r="M208" s="6"/>
     </row>
     <row r="209" spans="1:13">
-      <c r="A209" s="11"/>
-      <c r="B209" s="11"/>
-      <c r="C209" s="11"/>
-      <c r="D209" s="11"/>
+      <c r="A209" s="9"/>
+      <c r="B209" s="9"/>
+      <c r="C209" s="9"/>
+      <c r="D209" s="9"/>
       <c r="M209" s="6"/>
     </row>
     <row r="210" spans="1:13">
-      <c r="A210" s="11"/>
-      <c r="B210" s="11"/>
-      <c r="C210" s="11"/>
-      <c r="D210" s="11"/>
+      <c r="A210" s="9"/>
+      <c r="B210" s="9"/>
+      <c r="C210" s="9"/>
+      <c r="D210" s="9"/>
       <c r="M210" s="6"/>
     </row>
     <row r="211" spans="1:13">
-      <c r="A211" s="11"/>
-      <c r="B211" s="11"/>
-      <c r="C211" s="11"/>
-      <c r="D211" s="11"/>
+      <c r="A211" s="9"/>
+      <c r="B211" s="9"/>
+      <c r="C211" s="9"/>
+      <c r="D211" s="9"/>
       <c r="M211" s="6"/>
     </row>
     <row r="212" spans="1:13">
-      <c r="A212" s="11"/>
-      <c r="B212" s="11"/>
-      <c r="C212" s="11"/>
-      <c r="D212" s="11"/>
+      <c r="A212" s="9"/>
+      <c r="B212" s="9"/>
+      <c r="C212" s="9"/>
+      <c r="D212" s="9"/>
       <c r="M212" s="6"/>
     </row>
     <row r="213" spans="1:13">
-      <c r="A213" s="11"/>
-      <c r="B213" s="11"/>
-      <c r="C213" s="11"/>
-      <c r="D213" s="11"/>
+      <c r="A213" s="9"/>
+      <c r="B213" s="9"/>
+      <c r="C213" s="9"/>
+      <c r="D213" s="9"/>
       <c r="M213" s="6"/>
     </row>
     <row r="214" spans="1:13">
-      <c r="A214" s="11"/>
-      <c r="B214" s="11"/>
-      <c r="C214" s="11"/>
-      <c r="D214" s="11"/>
+      <c r="A214" s="9"/>
+      <c r="B214" s="9"/>
+      <c r="C214" s="9"/>
+      <c r="D214" s="9"/>
       <c r="M214" s="6"/>
     </row>
     <row r="215" spans="1:13">
-      <c r="A215" s="11"/>
-      <c r="B215" s="11"/>
-      <c r="C215" s="11"/>
-      <c r="D215" s="11"/>
+      <c r="A215" s="9"/>
+      <c r="B215" s="9"/>
+      <c r="C215" s="9"/>
+      <c r="D215" s="9"/>
       <c r="M215" s="6"/>
     </row>
     <row r="216" spans="1:13">
-      <c r="A216" s="11"/>
-      <c r="B216" s="11"/>
-      <c r="C216" s="11"/>
-      <c r="D216" s="11"/>
+      <c r="A216" s="9"/>
+      <c r="B216" s="9"/>
+      <c r="C216" s="9"/>
+      <c r="D216" s="9"/>
       <c r="M216" s="6"/>
     </row>
     <row r="217" spans="1:13">
-      <c r="A217" s="11"/>
-      <c r="B217" s="11"/>
-      <c r="C217" s="11"/>
-      <c r="D217" s="11"/>
+      <c r="A217" s="9"/>
+      <c r="B217" s="9"/>
+      <c r="C217" s="9"/>
+      <c r="D217" s="9"/>
       <c r="M217" s="6"/>
     </row>
     <row r="218" spans="1:13">
-      <c r="A218" s="11"/>
-      <c r="B218" s="11"/>
-      <c r="C218" s="11"/>
-      <c r="D218" s="11"/>
+      <c r="A218" s="9"/>
+      <c r="B218" s="9"/>
+      <c r="C218" s="9"/>
+      <c r="D218" s="9"/>
       <c r="M218" s="6"/>
     </row>
     <row r="219" spans="1:13">
-      <c r="A219" s="11"/>
-      <c r="B219" s="11"/>
-      <c r="C219" s="11"/>
-      <c r="D219" s="11"/>
+      <c r="A219" s="9"/>
+      <c r="B219" s="9"/>
+      <c r="C219" s="9"/>
+      <c r="D219" s="9"/>
       <c r="M219" s="6"/>
     </row>
     <row r="220" spans="1:13">
-      <c r="A220" s="11"/>
-      <c r="B220" s="11"/>
-      <c r="C220" s="11"/>
-      <c r="D220" s="11"/>
+      <c r="A220" s="9"/>
+      <c r="B220" s="9"/>
+      <c r="C220" s="9"/>
+      <c r="D220" s="9"/>
       <c r="M220" s="6"/>
     </row>
     <row r="221" spans="1:13">
-      <c r="A221" s="11"/>
-      <c r="B221" s="11"/>
-      <c r="C221" s="11"/>
-      <c r="D221" s="11"/>
+      <c r="A221" s="9"/>
+      <c r="B221" s="9"/>
+      <c r="C221" s="9"/>
+      <c r="D221" s="9"/>
       <c r="M221" s="6"/>
     </row>
     <row r="222" spans="1:13">
-      <c r="A222" s="11"/>
-      <c r="B222" s="11"/>
-      <c r="C222" s="11"/>
-      <c r="D222" s="11"/>
+      <c r="A222" s="9"/>
+      <c r="B222" s="9"/>
+      <c r="C222" s="9"/>
+      <c r="D222" s="9"/>
       <c r="M222" s="6"/>
     </row>
     <row r="223" spans="1:13">
-      <c r="A223" s="11"/>
-      <c r="B223" s="11"/>
-      <c r="C223" s="11"/>
-      <c r="D223" s="11"/>
+      <c r="A223" s="9"/>
+      <c r="B223" s="9"/>
+      <c r="C223" s="9"/>
+      <c r="D223" s="9"/>
       <c r="M223" s="6"/>
     </row>
     <row r="224" spans="1:13">
-      <c r="A224" s="11"/>
-      <c r="B224" s="11"/>
-      <c r="C224" s="11"/>
-      <c r="D224" s="11"/>
+      <c r="A224" s="9"/>
+      <c r="B224" s="9"/>
+      <c r="C224" s="9"/>
+      <c r="D224" s="9"/>
       <c r="M224" s="6"/>
     </row>
     <row r="225" spans="1:13">
-      <c r="A225" s="11"/>
-      <c r="B225" s="11"/>
-      <c r="C225" s="11"/>
-      <c r="D225" s="11"/>
+      <c r="A225" s="9"/>
+      <c r="B225" s="9"/>
+      <c r="C225" s="9"/>
+      <c r="D225" s="9"/>
       <c r="M225" s="6"/>
     </row>
     <row r="226" spans="1:13">
-      <c r="A226" s="11"/>
-      <c r="B226" s="11"/>
-      <c r="C226" s="11"/>
-      <c r="D226" s="11"/>
+      <c r="A226" s="9"/>
+      <c r="B226" s="9"/>
+      <c r="C226" s="9"/>
+      <c r="D226" s="9"/>
       <c r="M226" s="6"/>
     </row>
     <row r="227" spans="1:13">
-      <c r="A227" s="11"/>
-      <c r="B227" s="11"/>
-      <c r="C227" s="11"/>
-      <c r="D227" s="11"/>
+      <c r="A227" s="9"/>
+      <c r="B227" s="9"/>
+      <c r="C227" s="9"/>
+      <c r="D227" s="9"/>
       <c r="M227" s="6"/>
     </row>
     <row r="228" spans="1:13">
-      <c r="A228" s="11"/>
-      <c r="B228" s="11"/>
-      <c r="C228" s="11"/>
-      <c r="D228" s="11"/>
+      <c r="A228" s="9"/>
+      <c r="B228" s="9"/>
+      <c r="C228" s="9"/>
+      <c r="D228" s="9"/>
       <c r="M228" s="6"/>
     </row>
   </sheetData>

--- a/cw71012026.xlsx
+++ b/cw71012026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C611FD02-BC06-244A-968E-20F635D3BC83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{498C4FEF-332C-7F40-94B5-C6872F758F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="27040" windowHeight="15620" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="92">
   <si>
     <t>Surname</t>
   </si>
@@ -308,6 +308,9 @@
   </si>
   <si>
     <t>H262827Z</t>
+  </si>
+  <si>
+    <t>Magumise</t>
   </si>
 </sst>
 </file>
@@ -461,7 +464,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -488,16 +491,17 @@
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -932,10 +936,10 @@
       </c>
     </row>
     <row r="2" spans="1:13" ht="20">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="23" t="s">
         <v>71</v>
       </c>
       <c r="C2" s="14" t="s">
@@ -945,7 +949,7 @@
         <v>0.85</v>
       </c>
       <c r="H2" s="5"/>
-      <c r="M2" s="24"/>
+      <c r="M2" s="21"/>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="12" t="s">
@@ -964,6 +968,9 @@
         <v>0.6</v>
       </c>
       <c r="H3" s="5"/>
+      <c r="J3">
+        <v>0.54</v>
+      </c>
       <c r="M3" s="11"/>
     </row>
     <row r="4" spans="1:13">
@@ -1021,7 +1028,10 @@
         <v>0.21</v>
       </c>
       <c r="H6" s="5"/>
-      <c r="M6" s="25"/>
+      <c r="J6">
+        <v>0.79</v>
+      </c>
+      <c r="M6" s="22"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="12" t="s">
@@ -1040,6 +1050,9 @@
         <v>0.67</v>
       </c>
       <c r="H7" s="5"/>
+      <c r="J7">
+        <v>0.69</v>
+      </c>
       <c r="M7" s="6"/>
     </row>
     <row r="8" spans="1:13">
@@ -1059,6 +1072,9 @@
         <v>0.32</v>
       </c>
       <c r="H8" s="5"/>
+      <c r="J8">
+        <v>0.79</v>
+      </c>
       <c r="M8" s="6"/>
     </row>
     <row r="9" spans="1:13">
@@ -1078,6 +1094,9 @@
         <v>0.16</v>
       </c>
       <c r="H9" s="5"/>
+      <c r="J9">
+        <v>0.82</v>
+      </c>
       <c r="M9" s="6"/>
     </row>
     <row r="10" spans="1:13">
@@ -1135,6 +1154,9 @@
         <v>0.23</v>
       </c>
       <c r="H12" s="5"/>
+      <c r="J12">
+        <v>0.76</v>
+      </c>
       <c r="M12" s="6"/>
     </row>
     <row r="13" spans="1:13">
@@ -1154,6 +1176,9 @@
         <v>0</v>
       </c>
       <c r="H13" s="5"/>
+      <c r="J13">
+        <v>0.69</v>
+      </c>
       <c r="M13" s="6"/>
     </row>
     <row r="14" spans="1:13">
@@ -1173,6 +1198,9 @@
         <v>0.49</v>
       </c>
       <c r="H14" s="5"/>
+      <c r="J14">
+        <v>0.79</v>
+      </c>
       <c r="M14" s="6"/>
     </row>
     <row r="15" spans="1:13">
@@ -1211,188 +1239,192 @@
         <v>0.37</v>
       </c>
       <c r="H16" s="5"/>
+      <c r="J16">
+        <v>0.75</v>
+      </c>
       <c r="M16" s="6"/>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="C17" s="12" t="s">
+      <c r="A17" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" s="24"/>
+      <c r="C17" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="12">
-        <v>0.96</v>
+      <c r="D17" s="4">
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="H17" s="5"/>
+      <c r="J17">
+        <v>0.48</v>
+      </c>
       <c r="M17" s="6"/>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="12" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>16</v>
       </c>
       <c r="D18" s="12">
-        <v>0.81</v>
+        <v>0.96</v>
       </c>
       <c r="G18">
-        <v>0.72</v>
+        <v>0.51</v>
       </c>
       <c r="H18" s="5"/>
       <c r="M18" s="6"/>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="12" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>16</v>
       </c>
       <c r="D19" s="12">
-        <v>0.91</v>
+        <v>0.81</v>
       </c>
       <c r="G19">
-        <v>0.47</v>
+        <v>0.72</v>
       </c>
       <c r="H19" s="5"/>
       <c r="M19" s="6"/>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>16</v>
       </c>
       <c r="D20" s="12">
-        <v>0.89</v>
+        <v>0.91</v>
       </c>
       <c r="G20">
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
       <c r="H20" s="5"/>
       <c r="M20" s="6"/>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="12">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="G21">
-        <v>0.49</v>
+        <v>0.33</v>
       </c>
       <c r="H21" s="5"/>
       <c r="M21" s="6"/>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="12">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G22">
-        <v>0.39</v>
+        <v>0.49</v>
       </c>
       <c r="H22" s="5"/>
       <c r="M22" s="6"/>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="12" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>16</v>
       </c>
       <c r="D23" s="12">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="G23">
-        <v>0.72</v>
+        <v>0.39</v>
       </c>
       <c r="H23" s="5"/>
       <c r="M23" s="6"/>
     </row>
-    <row r="24" spans="1:13" ht="20">
-      <c r="A24" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="B24" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="C24" s="14" t="s">
+    <row r="24" spans="1:13">
+      <c r="A24" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D24" s="19">
-        <v>0.87</v>
+      <c r="D24" s="12">
+        <v>0.95</v>
+      </c>
+      <c r="G24">
+        <v>0.72</v>
       </c>
       <c r="H24" s="5"/>
       <c r="M24" s="6"/>
     </row>
-    <row r="25" spans="1:13">
-      <c r="A25" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="B25" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="C25" s="12" t="s">
+    <row r="25" spans="1:13" ht="20">
+      <c r="A25" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="B25" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="C25" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D25" s="12">
-        <v>0.85</v>
-      </c>
-      <c r="G25">
-        <v>0.54</v>
+      <c r="D25" s="19">
+        <v>0.87</v>
       </c>
       <c r="H25" s="5"/>
       <c r="M25" s="6"/>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="B26" s="23" t="s">
-        <v>59</v>
+      <c r="A26" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>57</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>16</v>
       </c>
       <c r="D26" s="12">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="G26">
         <v>0.54</v>
@@ -1401,122 +1433,131 @@
       <c r="M26" s="6"/>
     </row>
     <row r="27" spans="1:13">
-      <c r="A27" s="23" t="s">
-        <v>60</v>
-      </c>
-      <c r="B27" s="23" t="s">
-        <v>61</v>
+      <c r="A27" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>59</v>
       </c>
       <c r="C27" s="12" t="s">
         <v>16</v>
       </c>
       <c r="D27" s="12">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="G27">
-        <v>0.18</v>
+        <v>0.54</v>
       </c>
       <c r="H27" s="5"/>
       <c r="M27" s="6"/>
     </row>
     <row r="28" spans="1:13">
-      <c r="A28" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="B28" s="23" t="s">
-        <v>63</v>
+      <c r="A28" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>61</v>
       </c>
       <c r="C28" s="12" t="s">
         <v>16</v>
       </c>
       <c r="D28" s="12">
-        <v>0.7</v>
+        <v>0.83</v>
       </c>
       <c r="G28">
-        <v>0.68</v>
+        <v>0.18</v>
       </c>
       <c r="H28" s="5"/>
       <c r="M28" s="6"/>
     </row>
     <row r="29" spans="1:13">
-      <c r="A29" s="23" t="s">
-        <v>64</v>
-      </c>
-      <c r="B29" s="23" t="s">
-        <v>65</v>
+      <c r="A29" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>63</v>
       </c>
       <c r="C29" s="12" t="s">
         <v>16</v>
       </c>
       <c r="D29" s="12">
-        <v>0.93</v>
+        <v>0.7</v>
       </c>
       <c r="G29">
-        <v>0.46</v>
+        <v>0.68</v>
       </c>
       <c r="H29" s="5"/>
       <c r="M29" s="6"/>
     </row>
     <row r="30" spans="1:13">
-      <c r="A30" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="B30" s="21" t="s">
-        <v>67</v>
+      <c r="A30" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30" s="20" t="s">
+        <v>65</v>
       </c>
       <c r="C30" s="12" t="s">
         <v>16</v>
       </c>
       <c r="D30" s="12">
-        <v>0.82</v>
+        <v>0.93</v>
       </c>
       <c r="G30">
-        <v>0.25</v>
+        <v>0.46</v>
       </c>
       <c r="H30" s="5"/>
       <c r="M30" s="6"/>
     </row>
     <row r="31" spans="1:13">
-      <c r="A31" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="B31" s="21" t="s">
-        <v>69</v>
+      <c r="A31" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31" s="20" t="s">
+        <v>67</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>16</v>
       </c>
       <c r="D31" s="12">
+        <v>0.82</v>
+      </c>
+      <c r="G31">
+        <v>0.25</v>
+      </c>
+      <c r="H31" s="5"/>
+      <c r="J31">
+        <v>0.66</v>
+      </c>
+      <c r="M31" s="6"/>
+    </row>
+    <row r="32" spans="1:13">
+      <c r="A32" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="B32" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32" s="12">
         <v>0.62</v>
       </c>
-      <c r="G31">
+      <c r="G32">
         <v>0.46</v>
       </c>
-      <c r="H31" s="5"/>
-      <c r="M31" s="6"/>
-    </row>
-    <row r="32" spans="1:13" ht="20">
-      <c r="A32" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="D32" s="19">
-        <v>0.93</v>
-      </c>
       <c r="H32" s="5"/>
+      <c r="J32">
+        <v>0.82</v>
+      </c>
       <c r="M32" s="6"/>
     </row>
     <row r="33" spans="1:13" ht="20">
       <c r="A33" s="13" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C33" s="14" t="s">
         <v>77</v>
@@ -1528,103 +1569,112 @@
       <c r="M33" s="6"/>
     </row>
     <row r="34" spans="1:13" ht="20">
-      <c r="A34" s="16" t="s">
+      <c r="A34" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="D34" s="19">
+        <v>0.93</v>
+      </c>
+      <c r="H34" s="5"/>
+      <c r="M34" s="6"/>
+    </row>
+    <row r="35" spans="1:13" ht="20">
+      <c r="A35" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="B34" s="16" t="s">
+      <c r="B35" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="C34" s="17" t="s">
+      <c r="C35" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="D34" s="19">
+      <c r="D35" s="19">
         <v>0.91</v>
       </c>
-      <c r="M34" s="6"/>
-    </row>
-    <row r="35" spans="1:13" ht="20">
-      <c r="A35" s="13" t="s">
+      <c r="M35" s="6"/>
+    </row>
+    <row r="36" spans="1:13" ht="20">
+      <c r="A36" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B36" s="13" t="s">
         <v>82</v>
-      </c>
-      <c r="C35" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="D35" s="19">
-        <v>0.75</v>
-      </c>
-      <c r="H35" s="5"/>
-      <c r="M35" s="6"/>
-    </row>
-    <row r="36" spans="1:13" ht="20">
-      <c r="A36" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="B36" s="15" t="s">
-        <v>84</v>
       </c>
       <c r="C36" s="14" t="s">
         <v>77</v>
       </c>
       <c r="D36" s="19">
-        <v>0.87</v>
+        <v>0.75</v>
       </c>
       <c r="H36" s="5"/>
       <c r="M36" s="6"/>
     </row>
     <row r="37" spans="1:13" ht="20">
-      <c r="A37" s="16" t="s">
+      <c r="A37" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="D37" s="19">
+        <v>0.87</v>
+      </c>
+      <c r="H37" s="5"/>
+      <c r="M37" s="6"/>
+    </row>
+    <row r="38" spans="1:13" ht="20">
+      <c r="A38" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="B37" s="16" t="s">
+      <c r="B38" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="C37" s="17" t="s">
+      <c r="C38" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="D37" s="19">
+      <c r="D38" s="19">
         <v>0.89</v>
       </c>
-      <c r="M37" s="6"/>
-    </row>
-    <row r="38" spans="1:13" ht="21">
-      <c r="A38" s="18" t="s">
+      <c r="M38" s="6"/>
+    </row>
+    <row r="39" spans="1:13" ht="21">
+      <c r="A39" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="B38" s="18" t="s">
+      <c r="B39" s="18" t="s">
         <v>88</v>
-      </c>
-      <c r="C38" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="D38" s="19">
-        <v>0.47</v>
-      </c>
-      <c r="H38" s="5"/>
-      <c r="M38" s="6"/>
-    </row>
-    <row r="39" spans="1:13" ht="20">
-      <c r="A39" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="B39" s="15" t="s">
-        <v>90</v>
       </c>
       <c r="C39" s="14" t="s">
         <v>77</v>
       </c>
       <c r="D39" s="19">
-        <v>0.94</v>
+        <v>0.47</v>
       </c>
       <c r="H39" s="5"/>
       <c r="M39" s="6"/>
     </row>
-    <row r="40" spans="1:13">
-      <c r="A40" s="7"/>
-      <c r="B40" s="7"/>
-      <c r="D40" s="4"/>
+    <row r="40" spans="1:13" ht="20">
+      <c r="A40" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="C40" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="D40" s="19">
+        <v>0.94</v>
+      </c>
       <c r="H40" s="5"/>
       <c r="M40" s="6"/>
     </row>

--- a/cw71012026.xlsx
+++ b/cw71012026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{498C4FEF-332C-7F40-94B5-C6872F758F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56EEF33A-6CA7-8D4C-AD5F-DA886A2D5419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="27040" windowHeight="15620" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
+    <workbookView xWindow="1060" yWindow="620" windowWidth="27040" windowHeight="15620" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="93">
   <si>
     <t>Surname</t>
   </si>
@@ -311,6 +311,9 @@
   </si>
   <si>
     <t>Magumise</t>
+  </si>
+  <si>
+    <t>Mbizana</t>
   </si>
 </sst>
 </file>
@@ -464,7 +467,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -498,10 +501,8 @@
     <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -936,10 +937,10 @@
       </c>
     </row>
     <row r="2" spans="1:13" ht="20">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="14" t="s">
         <v>71</v>
       </c>
       <c r="C2" s="14" t="s">
@@ -949,6 +950,9 @@
         <v>0.85</v>
       </c>
       <c r="H2" s="5"/>
+      <c r="J2">
+        <v>0.66</v>
+      </c>
       <c r="M2" s="21"/>
     </row>
     <row r="3" spans="1:13">
@@ -1245,10 +1249,10 @@
       <c r="M16" s="6"/>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" s="24" t="s">
+      <c r="A17" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="B17" s="24"/>
+      <c r="B17" s="23"/>
       <c r="C17" t="s">
         <v>16</v>
       </c>
@@ -1281,6 +1285,9 @@
         <v>0.51</v>
       </c>
       <c r="H18" s="5"/>
+      <c r="J18">
+        <v>0.85</v>
+      </c>
       <c r="M18" s="6"/>
     </row>
     <row r="19" spans="1:13">
@@ -1300,6 +1307,9 @@
         <v>0.72</v>
       </c>
       <c r="H19" s="5"/>
+      <c r="J19">
+        <v>0.79</v>
+      </c>
       <c r="M19" s="6"/>
     </row>
     <row r="20" spans="1:13">
@@ -1319,6 +1329,9 @@
         <v>0.47</v>
       </c>
       <c r="H20" s="5"/>
+      <c r="J20">
+        <v>0.87</v>
+      </c>
       <c r="M20" s="6"/>
     </row>
     <row r="21" spans="1:13">
@@ -1338,6 +1351,9 @@
         <v>0.33</v>
       </c>
       <c r="H21" s="5"/>
+      <c r="J21">
+        <v>0.67</v>
+      </c>
       <c r="M21" s="6"/>
     </row>
     <row r="22" spans="1:13">
@@ -1357,6 +1373,9 @@
         <v>0.49</v>
       </c>
       <c r="H22" s="5"/>
+      <c r="J22">
+        <v>0.87</v>
+      </c>
       <c r="M22" s="6"/>
     </row>
     <row r="23" spans="1:13">
@@ -1398,10 +1417,10 @@
       <c r="M24" s="6"/>
     </row>
     <row r="25" spans="1:13" ht="20">
-      <c r="A25" s="25" t="s">
+      <c r="A25" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="B25" s="25" t="s">
+      <c r="B25" s="24" t="s">
         <v>74</v>
       </c>
       <c r="C25" s="14" t="s">
@@ -1414,10 +1433,10 @@
       <c r="M25" s="6"/>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" s="26" t="s">
+      <c r="A26" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="B26" s="26" t="s">
+      <c r="B26" s="12" t="s">
         <v>57</v>
       </c>
       <c r="C26" s="12" t="s">
@@ -1430,13 +1449,16 @@
         <v>0.54</v>
       </c>
       <c r="H26" s="5"/>
+      <c r="J26">
+        <v>0.84</v>
+      </c>
       <c r="M26" s="6"/>
     </row>
     <row r="27" spans="1:13">
-      <c r="A27" s="26" t="s">
+      <c r="A27" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B27" s="26" t="s">
+      <c r="B27" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C27" s="12" t="s">
@@ -1449,13 +1471,16 @@
         <v>0.54</v>
       </c>
       <c r="H27" s="5"/>
+      <c r="J27">
+        <v>0.81</v>
+      </c>
       <c r="M27" s="6"/>
     </row>
     <row r="28" spans="1:13">
-      <c r="A28" s="26" t="s">
+      <c r="A28" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="B28" s="26" t="s">
+      <c r="B28" s="12" t="s">
         <v>61</v>
       </c>
       <c r="C28" s="12" t="s">
@@ -1471,10 +1496,10 @@
       <c r="M28" s="6"/>
     </row>
     <row r="29" spans="1:13">
-      <c r="A29" s="26" t="s">
+      <c r="A29" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="B29" s="26" t="s">
+      <c r="B29" s="12" t="s">
         <v>63</v>
       </c>
       <c r="C29" s="12" t="s">
@@ -1487,6 +1512,9 @@
         <v>0.68</v>
       </c>
       <c r="H29" s="5"/>
+      <c r="J29">
+        <v>0.79</v>
+      </c>
       <c r="M29" s="6"/>
     </row>
     <row r="30" spans="1:13">
@@ -1506,6 +1534,9 @@
         <v>0.46</v>
       </c>
       <c r="H30" s="5"/>
+      <c r="J30">
+        <v>0.75</v>
+      </c>
       <c r="M30" s="6"/>
     </row>
     <row r="31" spans="1:13">
@@ -1566,6 +1597,9 @@
         <v>0.93</v>
       </c>
       <c r="H33" s="5"/>
+      <c r="J33">
+        <v>0.6</v>
+      </c>
       <c r="M33" s="6"/>
     </row>
     <row r="34" spans="1:13" ht="20">
@@ -1582,6 +1616,9 @@
         <v>0.93</v>
       </c>
       <c r="H34" s="5"/>
+      <c r="J34">
+        <v>0.73</v>
+      </c>
       <c r="M34" s="6"/>
     </row>
     <row r="35" spans="1:13" ht="20">
@@ -1597,6 +1634,9 @@
       <c r="D35" s="19">
         <v>0.91</v>
       </c>
+      <c r="J35">
+        <v>0.75</v>
+      </c>
       <c r="M35" s="6"/>
     </row>
     <row r="36" spans="1:13" ht="20">
@@ -1613,6 +1653,9 @@
         <v>0.75</v>
       </c>
       <c r="H36" s="5"/>
+      <c r="J36">
+        <v>0.61</v>
+      </c>
       <c r="M36" s="6"/>
     </row>
     <row r="37" spans="1:13" ht="20">
@@ -1629,6 +1672,9 @@
         <v>0.87</v>
       </c>
       <c r="H37" s="5"/>
+      <c r="J37">
+        <v>0.57999999999999996</v>
+      </c>
       <c r="M37" s="6"/>
     </row>
     <row r="38" spans="1:13" ht="20">
@@ -1644,6 +1690,9 @@
       <c r="D38" s="19">
         <v>0.89</v>
       </c>
+      <c r="J38">
+        <v>0.82</v>
+      </c>
       <c r="M38" s="6"/>
     </row>
     <row r="39" spans="1:13" ht="21">
@@ -1660,6 +1709,9 @@
         <v>0.47</v>
       </c>
       <c r="H39" s="5"/>
+      <c r="J39">
+        <v>0.66</v>
+      </c>
       <c r="M39" s="6"/>
     </row>
     <row r="40" spans="1:13" ht="20">
@@ -1676,19 +1728,39 @@
         <v>0.94</v>
       </c>
       <c r="H40" s="5"/>
+      <c r="J40">
+        <v>0.72</v>
+      </c>
       <c r="M40" s="6"/>
     </row>
     <row r="41" spans="1:13">
-      <c r="A41" s="8"/>
-      <c r="B41" s="8"/>
-      <c r="D41" s="4"/>
+      <c r="A41" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C41" t="s">
+        <v>16</v>
+      </c>
+      <c r="D41" s="4">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
       <c r="H41" s="5"/>
+      <c r="J41">
+        <v>0.78</v>
+      </c>
       <c r="M41" s="6"/>
     </row>
     <row r="42" spans="1:13">
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
-      <c r="D42" s="4"/>
+      <c r="D42" s="4">
+        <v>0</v>
+      </c>
       <c r="H42" s="5"/>
       <c r="M42" s="6"/>
     </row>

--- a/cw71012026.xlsx
+++ b/cw71012026.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56EEF33A-6CA7-8D4C-AD5F-DA886A2D5419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{172244DF-7553-C449-86EB-EB77651098EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1060" yWindow="620" windowWidth="27040" windowHeight="15620" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
+    <workbookView xWindow="1060" yWindow="620" windowWidth="27040" windowHeight="17380" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,6 +27,7 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -467,7 +468,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -502,7 +503,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -937,10 +941,10 @@
       </c>
     </row>
     <row r="2" spans="1:13" ht="20">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="24" t="s">
         <v>71</v>
       </c>
       <c r="C2" s="14" t="s">
@@ -1398,216 +1402,219 @@
       <c r="M23" s="6"/>
     </row>
     <row r="24" spans="1:13">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="4">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24" s="5"/>
+      <c r="J24">
+        <v>0.78</v>
+      </c>
+      <c r="M24" s="6"/>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B25" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C25" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D24" s="12">
+      <c r="D25" s="12">
         <v>0.95</v>
       </c>
-      <c r="G24">
+      <c r="G25">
         <v>0.72</v>
-      </c>
-      <c r="H24" s="5"/>
-      <c r="M24" s="6"/>
-    </row>
-    <row r="25" spans="1:13" ht="20">
-      <c r="A25" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="B25" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D25" s="19">
-        <v>0.87</v>
       </c>
       <c r="H25" s="5"/>
       <c r="M25" s="6"/>
     </row>
-    <row r="26" spans="1:13">
-      <c r="A26" s="12" t="s">
+    <row r="26" spans="1:13" ht="20">
+      <c r="A26" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26" s="19">
+        <v>0.87</v>
+      </c>
+      <c r="H26" s="5"/>
+      <c r="M26" s="6"/>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="B27" s="27" t="s">
         <v>57</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D26" s="12">
-        <v>0.85</v>
-      </c>
-      <c r="G26">
-        <v>0.54</v>
-      </c>
-      <c r="H26" s="5"/>
-      <c r="J26">
-        <v>0.84</v>
-      </c>
-      <c r="M26" s="6"/>
-    </row>
-    <row r="27" spans="1:13">
-      <c r="A27" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>59</v>
       </c>
       <c r="C27" s="12" t="s">
         <v>16</v>
       </c>
       <c r="D27" s="12">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="G27">
         <v>0.54</v>
       </c>
       <c r="H27" s="5"/>
       <c r="J27">
-        <v>0.81</v>
+        <v>0.84</v>
       </c>
       <c r="M27" s="6"/>
     </row>
     <row r="28" spans="1:13">
-      <c r="A28" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>61</v>
+      <c r="A28" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28" s="27" t="s">
+        <v>59</v>
       </c>
       <c r="C28" s="12" t="s">
         <v>16</v>
       </c>
       <c r="D28" s="12">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="G28">
-        <v>0.18</v>
+        <v>0.54</v>
       </c>
       <c r="H28" s="5"/>
+      <c r="J28">
+        <v>0.81</v>
+      </c>
       <c r="M28" s="6"/>
     </row>
     <row r="29" spans="1:13">
-      <c r="A29" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>63</v>
+      <c r="A29" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" s="27" t="s">
+        <v>61</v>
       </c>
       <c r="C29" s="12" t="s">
         <v>16</v>
       </c>
       <c r="D29" s="12">
-        <v>0.7</v>
+        <v>0.83</v>
       </c>
       <c r="G29">
-        <v>0.68</v>
+        <v>0.18</v>
       </c>
       <c r="H29" s="5"/>
-      <c r="J29">
-        <v>0.79</v>
-      </c>
       <c r="M29" s="6"/>
     </row>
     <row r="30" spans="1:13">
       <c r="A30" s="20" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C30" s="12" t="s">
         <v>16</v>
       </c>
       <c r="D30" s="12">
-        <v>0.93</v>
+        <v>0.7</v>
       </c>
       <c r="G30">
-        <v>0.46</v>
+        <v>0.68</v>
       </c>
       <c r="H30" s="5"/>
       <c r="J30">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="M30" s="6"/>
     </row>
     <row r="31" spans="1:13">
       <c r="A31" s="20" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B31" s="20" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>16</v>
       </c>
       <c r="D31" s="12">
-        <v>0.82</v>
+        <v>0.93</v>
       </c>
       <c r="G31">
-        <v>0.25</v>
+        <v>0.46</v>
       </c>
       <c r="H31" s="5"/>
       <c r="J31">
-        <v>0.66</v>
+        <v>0.75</v>
       </c>
       <c r="M31" s="6"/>
     </row>
     <row r="32" spans="1:13">
       <c r="A32" s="20" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B32" s="20" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C32" s="12" t="s">
         <v>16</v>
       </c>
       <c r="D32" s="12">
-        <v>0.62</v>
+        <v>0.82</v>
       </c>
       <c r="G32">
-        <v>0.46</v>
+        <v>0.25</v>
       </c>
       <c r="H32" s="5"/>
       <c r="J32">
-        <v>0.82</v>
+        <v>0.66</v>
       </c>
       <c r="M32" s="6"/>
     </row>
-    <row r="33" spans="1:13" ht="20">
-      <c r="A33" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="B33" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="C33" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="D33" s="19">
-        <v>0.93</v>
+    <row r="33" spans="1:13">
+      <c r="A33" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="B33" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D33" s="12">
+        <v>0.62</v>
+      </c>
+      <c r="G33">
+        <v>0.46</v>
       </c>
       <c r="H33" s="5"/>
       <c r="J33">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="M33" s="6"/>
     </row>
     <row r="34" spans="1:13" ht="20">
       <c r="A34" s="13" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C34" s="14" t="s">
         <v>77</v>
@@ -1617,150 +1624,145 @@
       </c>
       <c r="H34" s="5"/>
       <c r="J34">
+        <v>0.6</v>
+      </c>
+      <c r="M34" s="6"/>
+    </row>
+    <row r="35" spans="1:13" ht="20">
+      <c r="A35" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="D35" s="19">
+        <v>0.93</v>
+      </c>
+      <c r="H35" s="5"/>
+      <c r="J35">
         <v>0.73</v>
       </c>
-      <c r="M34" s="6"/>
-    </row>
-    <row r="35" spans="1:13" ht="20">
-      <c r="A35" s="16" t="s">
+      <c r="M35" s="6"/>
+    </row>
+    <row r="36" spans="1:13" ht="20">
+      <c r="A36" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="B35" s="16" t="s">
+      <c r="B36" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="C35" s="17" t="s">
+      <c r="C36" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="D35" s="19">
+      <c r="D36" s="19">
         <v>0.91</v>
       </c>
-      <c r="J35">
+      <c r="J36">
         <v>0.75</v>
       </c>
-      <c r="M35" s="6"/>
-    </row>
-    <row r="36" spans="1:13" ht="20">
-      <c r="A36" s="13" t="s">
+      <c r="M36" s="6"/>
+    </row>
+    <row r="37" spans="1:13" ht="20">
+      <c r="A37" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="B36" s="13" t="s">
+      <c r="B37" s="13" t="s">
         <v>82</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="D36" s="19">
-        <v>0.75</v>
-      </c>
-      <c r="H36" s="5"/>
-      <c r="J36">
-        <v>0.61</v>
-      </c>
-      <c r="M36" s="6"/>
-    </row>
-    <row r="37" spans="1:13" ht="20">
-      <c r="A37" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="B37" s="15" t="s">
-        <v>84</v>
       </c>
       <c r="C37" s="14" t="s">
         <v>77</v>
       </c>
       <c r="D37" s="19">
-        <v>0.87</v>
+        <v>0.75</v>
       </c>
       <c r="H37" s="5"/>
       <c r="J37">
+        <v>0.61</v>
+      </c>
+      <c r="M37" s="6"/>
+    </row>
+    <row r="38" spans="1:13" ht="20">
+      <c r="A38" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="D38" s="19">
+        <v>0.87</v>
+      </c>
+      <c r="H38" s="5"/>
+      <c r="J38">
         <v>0.57999999999999996</v>
       </c>
-      <c r="M37" s="6"/>
-    </row>
-    <row r="38" spans="1:13" ht="20">
-      <c r="A38" s="16" t="s">
+      <c r="M38" s="6"/>
+    </row>
+    <row r="39" spans="1:13" ht="20">
+      <c r="A39" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="B38" s="16" t="s">
+      <c r="B39" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="C38" s="17" t="s">
+      <c r="C39" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="D38" s="19">
+      <c r="D39" s="19">
         <v>0.89</v>
       </c>
-      <c r="J38">
+      <c r="J39">
         <v>0.82</v>
       </c>
-      <c r="M38" s="6"/>
-    </row>
-    <row r="39" spans="1:13" ht="21">
-      <c r="A39" s="18" t="s">
+      <c r="M39" s="6"/>
+    </row>
+    <row r="40" spans="1:13" ht="21">
+      <c r="A40" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="B39" s="18" t="s">
+      <c r="B40" s="18" t="s">
         <v>88</v>
-      </c>
-      <c r="C39" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="D39" s="19">
-        <v>0.47</v>
-      </c>
-      <c r="H39" s="5"/>
-      <c r="J39">
-        <v>0.66</v>
-      </c>
-      <c r="M39" s="6"/>
-    </row>
-    <row r="40" spans="1:13" ht="20">
-      <c r="A40" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="B40" s="15" t="s">
-        <v>90</v>
       </c>
       <c r="C40" s="14" t="s">
         <v>77</v>
       </c>
       <c r="D40" s="19">
-        <v>0.94</v>
+        <v>0.47</v>
       </c>
       <c r="H40" s="5"/>
       <c r="J40">
-        <v>0.72</v>
+        <v>0.66</v>
       </c>
       <c r="M40" s="6"/>
     </row>
-    <row r="41" spans="1:13">
-      <c r="A41" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C41" t="s">
-        <v>16</v>
-      </c>
-      <c r="D41" s="4">
-        <v>0</v>
-      </c>
-      <c r="G41">
-        <v>0</v>
+    <row r="41" spans="1:13" ht="20">
+      <c r="A41" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="C41" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="D41" s="19">
+        <v>0.94</v>
       </c>
       <c r="H41" s="5"/>
       <c r="J41">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="M41" s="6"/>
     </row>
     <row r="42" spans="1:13">
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
-      <c r="D42" s="4">
-        <v>0</v>
-      </c>
+      <c r="D42" s="4"/>
       <c r="H42" s="5"/>
       <c r="M42" s="6"/>
     </row>

--- a/cw71012026.xlsx
+++ b/cw71012026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{172244DF-7553-C449-86EB-EB77651098EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD4302D-0DEB-744A-A751-7109E3400317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1060" yWindow="620" windowWidth="27040" windowHeight="17380" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
+    <workbookView xWindow="1080" yWindow="620" windowWidth="27040" windowHeight="17380" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -468,7 +468,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -503,10 +503,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -941,10 +938,10 @@
       </c>
     </row>
     <row r="2" spans="1:13" ht="20">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="14" t="s">
         <v>71</v>
       </c>
       <c r="C2" s="14" t="s">
@@ -952,6 +949,9 @@
       </c>
       <c r="D2" s="19">
         <v>0.85</v>
+      </c>
+      <c r="G2">
+        <v>0.35</v>
       </c>
       <c r="H2" s="5"/>
       <c r="J2">
@@ -1402,10 +1402,10 @@
       <c r="M23" s="6"/>
     </row>
     <row r="24" spans="1:13">
-      <c r="A24" s="26" t="s">
+      <c r="A24" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B24" s="26" t="s">
+      <c r="B24" s="10" t="s">
         <v>40</v>
       </c>
       <c r="C24" t="s">
@@ -1424,10 +1424,10 @@
       <c r="M24" s="6"/>
     </row>
     <row r="25" spans="1:13">
-      <c r="A25" s="27" t="s">
+      <c r="A25" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="B25" s="27" t="s">
+      <c r="B25" s="12" t="s">
         <v>55</v>
       </c>
       <c r="C25" s="12" t="s">
@@ -1443,10 +1443,10 @@
       <c r="M25" s="6"/>
     </row>
     <row r="26" spans="1:13" ht="20">
-      <c r="A26" s="25" t="s">
+      <c r="A26" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="B26" s="25" t="s">
+      <c r="B26" s="24" t="s">
         <v>74</v>
       </c>
       <c r="C26" s="14" t="s">
@@ -1455,14 +1455,17 @@
       <c r="D26" s="19">
         <v>0.87</v>
       </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
       <c r="H26" s="5"/>
       <c r="M26" s="6"/>
     </row>
     <row r="27" spans="1:13">
-      <c r="A27" s="27" t="s">
+      <c r="A27" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="B27" s="27" t="s">
+      <c r="B27" s="12" t="s">
         <v>57</v>
       </c>
       <c r="C27" s="12" t="s">
@@ -1481,10 +1484,10 @@
       <c r="M27" s="6"/>
     </row>
     <row r="28" spans="1:13">
-      <c r="A28" s="27" t="s">
+      <c r="A28" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B28" s="27" t="s">
+      <c r="B28" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C28" s="12" t="s">
@@ -1503,10 +1506,10 @@
       <c r="M28" s="6"/>
     </row>
     <row r="29" spans="1:13">
-      <c r="A29" s="27" t="s">
+      <c r="A29" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="B29" s="27" t="s">
+      <c r="B29" s="12" t="s">
         <v>61</v>
       </c>
       <c r="C29" s="12" t="s">
@@ -1622,6 +1625,9 @@
       <c r="D34" s="19">
         <v>0.93</v>
       </c>
+      <c r="G34">
+        <v>0.53</v>
+      </c>
       <c r="H34" s="5"/>
       <c r="J34">
         <v>0.6</v>
@@ -1641,6 +1647,9 @@
       <c r="D35" s="19">
         <v>0.93</v>
       </c>
+      <c r="G35">
+        <v>0.51</v>
+      </c>
       <c r="H35" s="5"/>
       <c r="J35">
         <v>0.73</v>
@@ -1660,6 +1669,9 @@
       <c r="D36" s="19">
         <v>0.91</v>
       </c>
+      <c r="G36">
+        <v>0.67</v>
+      </c>
       <c r="J36">
         <v>0.75</v>
       </c>
@@ -1678,6 +1690,9 @@
       <c r="D37" s="19">
         <v>0.75</v>
       </c>
+      <c r="G37">
+        <v>0.37</v>
+      </c>
       <c r="H37" s="5"/>
       <c r="J37">
         <v>0.61</v>
@@ -1697,6 +1712,9 @@
       <c r="D38" s="19">
         <v>0.87</v>
       </c>
+      <c r="G38">
+        <v>0.11</v>
+      </c>
       <c r="H38" s="5"/>
       <c r="J38">
         <v>0.57999999999999996</v>
@@ -1716,6 +1734,9 @@
       <c r="D39" s="19">
         <v>0.89</v>
       </c>
+      <c r="G39">
+        <v>0.28000000000000003</v>
+      </c>
       <c r="J39">
         <v>0.82</v>
       </c>
@@ -1734,6 +1755,9 @@
       <c r="D40" s="19">
         <v>0.47</v>
       </c>
+      <c r="G40">
+        <v>0.28000000000000003</v>
+      </c>
       <c r="H40" s="5"/>
       <c r="J40">
         <v>0.66</v>
@@ -1752,6 +1776,9 @@
       </c>
       <c r="D41" s="19">
         <v>0.94</v>
+      </c>
+      <c r="G41">
+        <v>0.49</v>
       </c>
       <c r="H41" s="5"/>
       <c r="J41">

--- a/cw71012026.xlsx
+++ b/cw71012026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD4302D-0DEB-744A-A751-7109E3400317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5711AD4B-2DAA-3B49-9462-58A74DC1557C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="620" windowWidth="27040" windowHeight="17380" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
+    <workbookView xWindow="1080" yWindow="620" windowWidth="14620" windowHeight="17380" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="95">
   <si>
     <t>Surname</t>
   </si>
@@ -315,6 +315,12 @@
   </si>
   <si>
     <t>Mbizana</t>
+  </si>
+  <si>
+    <t>Kada</t>
+  </si>
+  <si>
+    <t>H269439T</t>
   </si>
 </sst>
 </file>
@@ -468,7 +474,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -479,7 +485,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -503,7 +508,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -938,17 +946,20 @@
       </c>
     </row>
     <row r="2" spans="1:13" ht="20">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D2" s="19">
+      <c r="D2" s="18">
         <v>0.85</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
       </c>
       <c r="G2">
         <v>0.35</v>
@@ -957,20 +968,23 @@
       <c r="J2">
         <v>0.66</v>
       </c>
-      <c r="M2" s="21"/>
+      <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="11">
         <v>0.83</v>
+      </c>
+      <c r="E3">
+        <v>0.98</v>
       </c>
       <c r="G3">
         <v>0.6</v>
@@ -979,58 +993,67 @@
       <c r="J3">
         <v>0.54</v>
       </c>
-      <c r="M3" s="11"/>
+      <c r="M3" s="10"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="11">
         <v>0.87</v>
+      </c>
+      <c r="E4">
+        <v>0.98</v>
       </c>
       <c r="G4">
         <v>0.44</v>
       </c>
       <c r="H4" s="5"/>
-      <c r="M4" s="11"/>
+      <c r="M4" s="10"/>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="11">
         <v>0.88</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
       </c>
       <c r="G5">
         <v>0.21</v>
       </c>
       <c r="H5" s="5"/>
-      <c r="M5" s="11"/>
+      <c r="M5" s="10"/>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="11">
         <v>0.71</v>
+      </c>
+      <c r="E6">
+        <v>0.81</v>
       </c>
       <c r="G6">
         <v>0.21</v>
@@ -1039,20 +1062,23 @@
       <c r="J6">
         <v>0.79</v>
       </c>
-      <c r="M6" s="22"/>
+      <c r="M6" s="21"/>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="11">
         <v>0.88</v>
+      </c>
+      <c r="E7">
+        <v>0.96</v>
       </c>
       <c r="G7">
         <v>0.67</v>
@@ -1064,17 +1090,20 @@
       <c r="M7" s="6"/>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="11">
         <v>0.76</v>
+      </c>
+      <c r="E8">
+        <v>0.87</v>
       </c>
       <c r="G8">
         <v>0.32</v>
@@ -1086,17 +1115,20 @@
       <c r="M8" s="6"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="11">
         <v>0.6</v>
+      </c>
+      <c r="E9">
+        <v>0.97</v>
       </c>
       <c r="G9">
         <v>0.16</v>
@@ -1108,17 +1140,20 @@
       <c r="M9" s="6"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="11">
         <v>0.75</v>
+      </c>
+      <c r="E10">
+        <v>0.98</v>
       </c>
       <c r="G10">
         <v>0.26</v>
@@ -1127,17 +1162,20 @@
       <c r="M10" s="6"/>
     </row>
     <row r="11" spans="1:13">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="11">
         <v>0.61</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
       </c>
       <c r="G11">
         <v>0.18</v>
@@ -1146,17 +1184,20 @@
       <c r="M11" s="6"/>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="11">
         <v>0.83</v>
+      </c>
+      <c r="E12">
+        <v>0.98</v>
       </c>
       <c r="G12">
         <v>0.23</v>
@@ -1168,17 +1209,20 @@
       <c r="M12" s="6"/>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="11">
         <v>0.9</v>
+      </c>
+      <c r="E13">
+        <v>0.98</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1190,17 +1234,20 @@
       <c r="M13" s="6"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="11">
         <v>0.72</v>
+      </c>
+      <c r="E14">
+        <v>0.94</v>
       </c>
       <c r="G14">
         <v>0.49</v>
@@ -1212,17 +1259,20 @@
       <c r="M14" s="6"/>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="11">
         <v>0.87</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
       </c>
       <c r="G15">
         <v>0.39</v>
@@ -1231,17 +1281,20 @@
       <c r="M15" s="6"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="11">
         <v>0.86</v>
+      </c>
+      <c r="E16">
+        <v>0.8</v>
       </c>
       <c r="G16">
         <v>0.37</v>
@@ -1253,247 +1306,277 @@
       <c r="M16" s="6"/>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" s="23" t="s">
-        <v>91</v>
-      </c>
-      <c r="B17" s="23"/>
+      <c r="A17" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>94</v>
+      </c>
       <c r="C17" t="s">
         <v>16</v>
       </c>
       <c r="D17" s="4">
         <v>0</v>
       </c>
-      <c r="G17">
+      <c r="E17">
+        <v>0.98</v>
+      </c>
+      <c r="H17" s="5"/>
+      <c r="M17" s="6"/>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="B18" s="22"/>
+      <c r="C18" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="4">
         <v>0</v>
       </c>
-      <c r="H17" s="5"/>
-      <c r="J17">
-        <v>0.48</v>
-      </c>
-      <c r="M17" s="6"/>
-    </row>
-    <row r="18" spans="1:13">
-      <c r="A18" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D18" s="12">
-        <v>0.96</v>
+      <c r="E18">
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="H18" s="5"/>
       <c r="J18">
-        <v>0.85</v>
+        <v>0.48</v>
       </c>
       <c r="M18" s="6"/>
     </row>
     <row r="19" spans="1:13">
-      <c r="A19" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="C19" s="12" t="s">
+      <c r="A19" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D19" s="12">
-        <v>0.81</v>
+      <c r="D19" s="11">
+        <v>0.96</v>
+      </c>
+      <c r="E19">
+        <v>0.92</v>
       </c>
       <c r="G19">
-        <v>0.72</v>
+        <v>0.51</v>
       </c>
       <c r="H19" s="5"/>
       <c r="J19">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="M19" s="6"/>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="C20" s="12" t="s">
+      <c r="A20" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="12">
-        <v>0.91</v>
+      <c r="D20" s="11">
+        <v>0.81</v>
+      </c>
+      <c r="E20">
+        <v>0.94</v>
       </c>
       <c r="G20">
-        <v>0.47</v>
+        <v>0.72</v>
       </c>
       <c r="H20" s="5"/>
       <c r="J20">
-        <v>0.87</v>
+        <v>0.79</v>
       </c>
       <c r="M20" s="6"/>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C21" s="12" t="s">
+      <c r="A21" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="12">
-        <v>0.89</v>
+      <c r="D21" s="11">
+        <v>0.91</v>
+      </c>
+      <c r="E21">
+        <v>0.98</v>
       </c>
       <c r="G21">
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
       <c r="H21" s="5"/>
       <c r="J21">
-        <v>0.67</v>
+        <v>0.87</v>
       </c>
       <c r="M21" s="6"/>
     </row>
     <row r="22" spans="1:13">
-      <c r="A22" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C22" s="12" t="s">
+      <c r="A22" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="12">
-        <v>0.9</v>
+      <c r="D22" s="11">
+        <v>0.89</v>
+      </c>
+      <c r="E22">
+        <v>0.92</v>
       </c>
       <c r="G22">
-        <v>0.49</v>
+        <v>0.33</v>
       </c>
       <c r="H22" s="5"/>
       <c r="J22">
+        <v>0.67</v>
+      </c>
+      <c r="M22" s="6"/>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="11">
+        <v>0.9</v>
+      </c>
+      <c r="E23">
+        <v>0.94</v>
+      </c>
+      <c r="G23">
+        <v>0.49</v>
+      </c>
+      <c r="H23" s="5"/>
+      <c r="J23">
         <v>0.87</v>
       </c>
-      <c r="M22" s="6"/>
-    </row>
-    <row r="23" spans="1:13">
-      <c r="A23" s="12" t="s">
+      <c r="M23" s="6"/>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B24" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C24" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D23" s="12">
+      <c r="D24" s="11">
         <v>0.8</v>
       </c>
-      <c r="G23">
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="G24">
         <v>0.39</v>
       </c>
-      <c r="H23" s="5"/>
-      <c r="M23" s="6"/>
-    </row>
-    <row r="24" spans="1:13">
-      <c r="A24" s="10" t="s">
+      <c r="H24" s="5"/>
+      <c r="M24" s="6"/>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B25" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C25" t="s">
         <v>16</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D25" s="4">
         <v>0</v>
       </c>
-      <c r="G24">
+      <c r="E25">
+        <v>0.92</v>
+      </c>
+      <c r="G25">
         <v>0</v>
       </c>
-      <c r="H24" s="5"/>
-      <c r="J24">
+      <c r="H25" s="5"/>
+      <c r="J25">
         <v>0.78</v>
       </c>
-      <c r="M24" s="6"/>
-    </row>
-    <row r="25" spans="1:13">
-      <c r="A25" s="12" t="s">
+      <c r="M25" s="6"/>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="B26" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C26" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D25" s="12">
+      <c r="D26" s="11">
         <v>0.95</v>
       </c>
-      <c r="G25">
+      <c r="E26">
+        <v>0.98</v>
+      </c>
+      <c r="G26">
         <v>0.72</v>
-      </c>
-      <c r="H25" s="5"/>
-      <c r="M25" s="6"/>
-    </row>
-    <row r="26" spans="1:13" ht="20">
-      <c r="A26" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="B26" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D26" s="19">
-        <v>0.87</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
       </c>
       <c r="H26" s="5"/>
       <c r="M26" s="6"/>
     </row>
-    <row r="27" spans="1:13">
-      <c r="A27" s="12" t="s">
+    <row r="27" spans="1:13" ht="20">
+      <c r="A27" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" s="18">
+        <v>0.87</v>
+      </c>
+      <c r="E27">
+        <v>0.89</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27" s="5"/>
+      <c r="M27" s="6"/>
+    </row>
+    <row r="28" spans="1:13">
+      <c r="A28" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="B28" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C28" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D27" s="12">
+      <c r="D28" s="11">
         <v>0.85</v>
       </c>
-      <c r="G27">
-        <v>0.54</v>
-      </c>
-      <c r="H27" s="5"/>
-      <c r="J27">
-        <v>0.84</v>
-      </c>
-      <c r="M27" s="6"/>
-    </row>
-    <row r="28" spans="1:13">
-      <c r="A28" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D28" s="12">
+      <c r="E28">
         <v>0.89</v>
       </c>
       <c r="G28">
@@ -1501,296 +1584,353 @@
       </c>
       <c r="H28" s="5"/>
       <c r="J28">
+        <v>0.84</v>
+      </c>
+      <c r="M28" s="6"/>
+    </row>
+    <row r="29" spans="1:13">
+      <c r="A29" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D29" s="11">
+        <v>0.89</v>
+      </c>
+      <c r="E29">
+        <v>0.97</v>
+      </c>
+      <c r="G29">
+        <v>0.54</v>
+      </c>
+      <c r="H29" s="5"/>
+      <c r="J29">
         <v>0.81</v>
       </c>
-      <c r="M28" s="6"/>
-    </row>
-    <row r="29" spans="1:13">
-      <c r="A29" s="12" t="s">
+      <c r="M29" s="6"/>
+    </row>
+    <row r="30" spans="1:13">
+      <c r="A30" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="B29" s="12" t="s">
+      <c r="B30" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C30" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D29" s="12">
+      <c r="D30" s="11">
         <v>0.83</v>
       </c>
-      <c r="G29">
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="G30">
         <v>0.18</v>
       </c>
-      <c r="H29" s="5"/>
-      <c r="M29" s="6"/>
-    </row>
-    <row r="30" spans="1:13">
-      <c r="A30" s="20" t="s">
+      <c r="H30" s="5"/>
+      <c r="M30" s="6"/>
+    </row>
+    <row r="31" spans="1:13">
+      <c r="A31" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="B30" s="20" t="s">
+      <c r="B31" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C31" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D30" s="12">
+      <c r="D31" s="11">
         <v>0.7</v>
       </c>
-      <c r="G30">
+      <c r="E31">
+        <v>0.98</v>
+      </c>
+      <c r="G31">
         <v>0.68</v>
-      </c>
-      <c r="H30" s="5"/>
-      <c r="J30">
-        <v>0.79</v>
-      </c>
-      <c r="M30" s="6"/>
-    </row>
-    <row r="31" spans="1:13">
-      <c r="A31" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="B31" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D31" s="12">
-        <v>0.93</v>
-      </c>
-      <c r="G31">
-        <v>0.46</v>
       </c>
       <c r="H31" s="5"/>
       <c r="J31">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="M31" s="6"/>
     </row>
     <row r="32" spans="1:13">
-      <c r="A32" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="B32" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="C32" s="12" t="s">
+      <c r="A32" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D32" s="12">
-        <v>0.82</v>
+      <c r="D32" s="11">
+        <v>0.93</v>
+      </c>
+      <c r="E32">
+        <v>0.92</v>
       </c>
       <c r="G32">
-        <v>0.25</v>
+        <v>0.46</v>
       </c>
       <c r="H32" s="5"/>
       <c r="J32">
-        <v>0.66</v>
+        <v>0.75</v>
       </c>
       <c r="M32" s="6"/>
     </row>
     <row r="33" spans="1:13">
-      <c r="A33" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="B33" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="C33" s="12" t="s">
+      <c r="A33" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D33" s="12">
-        <v>0.62</v>
+      <c r="D33" s="11">
+        <v>0.82</v>
+      </c>
+      <c r="E33">
+        <v>0.94</v>
       </c>
       <c r="G33">
-        <v>0.46</v>
+        <v>0.25</v>
       </c>
       <c r="H33" s="5"/>
       <c r="J33">
-        <v>0.82</v>
+        <v>0.66</v>
       </c>
       <c r="M33" s="6"/>
     </row>
-    <row r="34" spans="1:13" ht="20">
-      <c r="A34" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="B34" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="D34" s="19">
-        <v>0.93</v>
+    <row r="34" spans="1:13">
+      <c r="A34" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D34" s="11">
+        <v>0.62</v>
+      </c>
+      <c r="E34">
+        <v>0.96</v>
       </c>
       <c r="G34">
-        <v>0.53</v>
+        <v>0.46</v>
       </c>
       <c r="H34" s="5"/>
       <c r="J34">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="M34" s="6"/>
     </row>
     <row r="35" spans="1:13" ht="20">
-      <c r="A35" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="B35" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="C35" s="14" t="s">
+      <c r="A35" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C35" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="D35" s="19">
+      <c r="D35" s="18">
         <v>0.93</v>
       </c>
+      <c r="E35">
+        <v>0.97</v>
+      </c>
       <c r="G35">
-        <v>0.51</v>
+        <v>0.53</v>
       </c>
       <c r="H35" s="5"/>
       <c r="J35">
+        <v>0.6</v>
+      </c>
+      <c r="M35" s="6"/>
+    </row>
+    <row r="36" spans="1:13" ht="20">
+      <c r="A36" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D36" s="18">
+        <v>0.93</v>
+      </c>
+      <c r="E36">
+        <v>0.96</v>
+      </c>
+      <c r="G36">
+        <v>0.51</v>
+      </c>
+      <c r="H36" s="5"/>
+      <c r="J36">
         <v>0.73</v>
       </c>
-      <c r="M35" s="6"/>
-    </row>
-    <row r="36" spans="1:13" ht="20">
-      <c r="A36" s="16" t="s">
+      <c r="M36" s="6"/>
+    </row>
+    <row r="37" spans="1:13" ht="20">
+      <c r="A37" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B36" s="16" t="s">
+      <c r="B37" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="17" t="s">
+      <c r="C37" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="D36" s="19">
+      <c r="D37" s="18">
         <v>0.91</v>
       </c>
-      <c r="G36">
+      <c r="E37">
+        <v>0.93</v>
+      </c>
+      <c r="G37">
         <v>0.67</v>
       </c>
-      <c r="J36">
+      <c r="J37">
         <v>0.75</v>
       </c>
-      <c r="M36" s="6"/>
-    </row>
-    <row r="37" spans="1:13" ht="20">
-      <c r="A37" s="13" t="s">
+      <c r="M37" s="6"/>
+    </row>
+    <row r="38" spans="1:13" ht="20">
+      <c r="A38" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="B37" s="13" t="s">
+      <c r="B38" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="C38" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="D37" s="19">
+      <c r="D38" s="18">
         <v>0.75</v>
       </c>
-      <c r="G37">
+      <c r="E38">
+        <v>0.91</v>
+      </c>
+      <c r="G38">
         <v>0.37</v>
-      </c>
-      <c r="H37" s="5"/>
-      <c r="J37">
-        <v>0.61</v>
-      </c>
-      <c r="M37" s="6"/>
-    </row>
-    <row r="38" spans="1:13" ht="20">
-      <c r="A38" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="B38" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="C38" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="D38" s="19">
-        <v>0.87</v>
-      </c>
-      <c r="G38">
-        <v>0.11</v>
       </c>
       <c r="H38" s="5"/>
       <c r="J38">
+        <v>0.61</v>
+      </c>
+      <c r="M38" s="6"/>
+    </row>
+    <row r="39" spans="1:13" ht="20">
+      <c r="A39" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D39" s="18">
+        <v>0.87</v>
+      </c>
+      <c r="E39">
+        <v>0.87</v>
+      </c>
+      <c r="G39">
+        <v>0.11</v>
+      </c>
+      <c r="H39" s="5"/>
+      <c r="J39">
         <v>0.57999999999999996</v>
       </c>
-      <c r="M38" s="6"/>
-    </row>
-    <row r="39" spans="1:13" ht="20">
-      <c r="A39" s="16" t="s">
+      <c r="M39" s="6"/>
+    </row>
+    <row r="40" spans="1:13" ht="20">
+      <c r="A40" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="B39" s="16" t="s">
+      <c r="B40" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="C39" s="17" t="s">
+      <c r="C40" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="D39" s="19">
+      <c r="D40" s="18">
         <v>0.89</v>
       </c>
-      <c r="G39">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="J39">
-        <v>0.82</v>
-      </c>
-      <c r="M39" s="6"/>
-    </row>
-    <row r="40" spans="1:13" ht="21">
-      <c r="A40" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="B40" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="C40" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="D40" s="19">
-        <v>0.47</v>
+      <c r="E40">
+        <v>0.98</v>
       </c>
       <c r="G40">
         <v>0.28000000000000003</v>
       </c>
-      <c r="H40" s="5"/>
       <c r="J40">
-        <v>0.66</v>
+        <v>0.82</v>
       </c>
       <c r="M40" s="6"/>
     </row>
-    <row r="41" spans="1:13" ht="20">
-      <c r="A41" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="B41" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="C41" s="14" t="s">
+    <row r="41" spans="1:13" ht="21">
+      <c r="A41" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="B41" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="C41" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="D41" s="19">
-        <v>0.94</v>
+      <c r="D41" s="18">
+        <v>0.47</v>
+      </c>
+      <c r="E41">
+        <v>0.8</v>
       </c>
       <c r="G41">
-        <v>0.49</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="H41" s="5"/>
       <c r="J41">
+        <v>0.66</v>
+      </c>
+      <c r="M41" s="6"/>
+    </row>
+    <row r="42" spans="1:13" ht="20">
+      <c r="A42" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D42" s="18">
+        <v>0.94</v>
+      </c>
+      <c r="E42">
+        <v>0.96</v>
+      </c>
+      <c r="G42">
+        <v>0.49</v>
+      </c>
+      <c r="H42" s="5"/>
+      <c r="J42">
         <v>0.72</v>
       </c>
-      <c r="M41" s="6"/>
-    </row>
-    <row r="42" spans="1:13">
-      <c r="A42" s="8"/>
-      <c r="B42" s="8"/>
-      <c r="D42" s="4"/>
-      <c r="H42" s="5"/>
       <c r="M42" s="6"/>
     </row>
     <row r="43" spans="1:13">
@@ -1808,262 +1948,262 @@
       <c r="M44" s="6"/>
     </row>
     <row r="45" spans="1:13">
-      <c r="A45" s="10"/>
-      <c r="B45" s="10"/>
+      <c r="A45" s="9"/>
+      <c r="B45" s="9"/>
       <c r="D45" s="4"/>
       <c r="H45" s="5"/>
       <c r="M45" s="6"/>
     </row>
     <row r="46" spans="1:13">
-      <c r="A46" s="10"/>
-      <c r="B46" s="10"/>
+      <c r="A46" s="9"/>
+      <c r="B46" s="9"/>
       <c r="D46" s="4"/>
       <c r="H46" s="5"/>
       <c r="M46" s="6"/>
     </row>
     <row r="47" spans="1:13">
-      <c r="A47" s="9"/>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
+      <c r="A47" s="8"/>
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
       <c r="H47" s="5"/>
       <c r="M47" s="6"/>
     </row>
     <row r="48" spans="1:13">
-      <c r="A48" s="9"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
+      <c r="A48" s="8"/>
+      <c r="B48" s="8"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="8"/>
       <c r="H48" s="5"/>
       <c r="M48" s="6"/>
     </row>
     <row r="49" spans="1:13">
-      <c r="A49" s="9"/>
-      <c r="B49" s="9"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9"/>
+      <c r="A49" s="8"/>
+      <c r="B49" s="8"/>
+      <c r="C49" s="8"/>
+      <c r="D49" s="8"/>
       <c r="H49" s="5"/>
       <c r="M49" s="6"/>
     </row>
     <row r="50" spans="1:13">
-      <c r="A50" s="9"/>
-      <c r="B50" s="9"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
+      <c r="A50" s="8"/>
+      <c r="B50" s="8"/>
+      <c r="C50" s="8"/>
+      <c r="D50" s="8"/>
       <c r="H50" s="5"/>
       <c r="M50" s="6"/>
     </row>
     <row r="51" spans="1:13">
-      <c r="A51" s="9"/>
-      <c r="B51" s="9"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
+      <c r="A51" s="8"/>
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
       <c r="H51" s="5"/>
       <c r="M51" s="6"/>
     </row>
     <row r="52" spans="1:13">
-      <c r="A52" s="9"/>
-      <c r="B52" s="9"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
+      <c r="A52" s="8"/>
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
       <c r="H52" s="5"/>
       <c r="M52" s="6"/>
     </row>
     <row r="53" spans="1:13">
-      <c r="A53" s="9"/>
-      <c r="B53" s="9"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
+      <c r="A53" s="8"/>
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
       <c r="H53" s="5"/>
       <c r="M53" s="6"/>
     </row>
     <row r="54" spans="1:13">
-      <c r="A54" s="9"/>
-      <c r="B54" s="9"/>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
+      <c r="A54" s="8"/>
+      <c r="B54" s="8"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="8"/>
       <c r="M54" s="6"/>
     </row>
     <row r="55" spans="1:13">
-      <c r="A55" s="9"/>
-      <c r="B55" s="9"/>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9"/>
+      <c r="A55" s="8"/>
+      <c r="B55" s="8"/>
+      <c r="C55" s="8"/>
+      <c r="D55" s="8"/>
       <c r="M55" s="6"/>
     </row>
     <row r="56" spans="1:13">
-      <c r="A56" s="9"/>
-      <c r="B56" s="9"/>
-      <c r="C56" s="9"/>
-      <c r="D56" s="9"/>
+      <c r="A56" s="8"/>
+      <c r="B56" s="8"/>
+      <c r="C56" s="8"/>
+      <c r="D56" s="8"/>
       <c r="M56" s="6"/>
     </row>
     <row r="57" spans="1:13">
-      <c r="A57" s="9"/>
-      <c r="B57" s="9"/>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9"/>
+      <c r="A57" s="8"/>
+      <c r="B57" s="8"/>
+      <c r="C57" s="8"/>
+      <c r="D57" s="8"/>
       <c r="M57" s="6"/>
     </row>
     <row r="58" spans="1:13">
-      <c r="A58" s="9"/>
-      <c r="B58" s="9"/>
-      <c r="C58" s="9"/>
-      <c r="D58" s="9"/>
+      <c r="A58" s="8"/>
+      <c r="B58" s="8"/>
+      <c r="C58" s="8"/>
+      <c r="D58" s="8"/>
       <c r="M58" s="6"/>
     </row>
     <row r="59" spans="1:13">
-      <c r="A59" s="9"/>
-      <c r="B59" s="9"/>
-      <c r="C59" s="9"/>
-      <c r="D59" s="9"/>
+      <c r="A59" s="8"/>
+      <c r="B59" s="8"/>
+      <c r="C59" s="8"/>
+      <c r="D59" s="8"/>
       <c r="M59" s="6"/>
     </row>
     <row r="60" spans="1:13">
-      <c r="A60" s="9"/>
-      <c r="B60" s="9"/>
-      <c r="C60" s="9"/>
-      <c r="D60" s="9"/>
+      <c r="A60" s="8"/>
+      <c r="B60" s="8"/>
+      <c r="C60" s="8"/>
+      <c r="D60" s="8"/>
       <c r="M60" s="6"/>
     </row>
     <row r="61" spans="1:13">
-      <c r="A61" s="9"/>
-      <c r="B61" s="9"/>
-      <c r="C61" s="9"/>
-      <c r="D61" s="9"/>
+      <c r="A61" s="8"/>
+      <c r="B61" s="8"/>
+      <c r="C61" s="8"/>
+      <c r="D61" s="8"/>
       <c r="M61" s="6"/>
     </row>
     <row r="62" spans="1:13">
-      <c r="A62" s="9"/>
-      <c r="B62" s="9"/>
-      <c r="C62" s="9"/>
-      <c r="D62" s="9"/>
+      <c r="A62" s="8"/>
+      <c r="B62" s="8"/>
+      <c r="C62" s="8"/>
+      <c r="D62" s="8"/>
       <c r="M62" s="6"/>
     </row>
     <row r="63" spans="1:13">
-      <c r="A63" s="9"/>
-      <c r="B63" s="9"/>
-      <c r="C63" s="9"/>
-      <c r="D63" s="9"/>
+      <c r="A63" s="8"/>
+      <c r="B63" s="8"/>
+      <c r="C63" s="8"/>
+      <c r="D63" s="8"/>
       <c r="M63" s="6"/>
     </row>
     <row r="64" spans="1:13">
-      <c r="A64" s="9"/>
-      <c r="B64" s="9"/>
-      <c r="C64" s="9"/>
-      <c r="D64" s="9"/>
+      <c r="A64" s="8"/>
+      <c r="B64" s="8"/>
+      <c r="C64" s="8"/>
+      <c r="D64" s="8"/>
       <c r="M64" s="6"/>
     </row>
     <row r="65" spans="1:13">
-      <c r="A65" s="9"/>
-      <c r="B65" s="9"/>
-      <c r="C65" s="9"/>
-      <c r="D65" s="9"/>
+      <c r="A65" s="8"/>
+      <c r="B65" s="8"/>
+      <c r="C65" s="8"/>
+      <c r="D65" s="8"/>
       <c r="M65" s="6"/>
     </row>
     <row r="66" spans="1:13">
-      <c r="A66" s="9"/>
-      <c r="B66" s="9"/>
-      <c r="C66" s="9"/>
-      <c r="D66" s="9"/>
+      <c r="A66" s="8"/>
+      <c r="B66" s="8"/>
+      <c r="C66" s="8"/>
+      <c r="D66" s="8"/>
       <c r="M66" s="6"/>
     </row>
     <row r="67" spans="1:13">
-      <c r="A67" s="9"/>
-      <c r="B67" s="9"/>
-      <c r="C67" s="9"/>
-      <c r="D67" s="9"/>
+      <c r="A67" s="8"/>
+      <c r="B67" s="8"/>
+      <c r="C67" s="8"/>
+      <c r="D67" s="8"/>
       <c r="M67" s="6"/>
     </row>
     <row r="68" spans="1:13">
-      <c r="A68" s="9"/>
-      <c r="B68" s="9"/>
-      <c r="C68" s="9"/>
-      <c r="D68" s="9"/>
+      <c r="A68" s="8"/>
+      <c r="B68" s="8"/>
+      <c r="C68" s="8"/>
+      <c r="D68" s="8"/>
       <c r="M68" s="6"/>
     </row>
     <row r="69" spans="1:13">
-      <c r="A69" s="9"/>
-      <c r="B69" s="9"/>
-      <c r="C69" s="9"/>
-      <c r="D69" s="9"/>
+      <c r="A69" s="8"/>
+      <c r="B69" s="8"/>
+      <c r="C69" s="8"/>
+      <c r="D69" s="8"/>
       <c r="M69" s="6"/>
     </row>
     <row r="70" spans="1:13">
-      <c r="A70" s="9"/>
-      <c r="B70" s="9"/>
-      <c r="C70" s="9"/>
-      <c r="D70" s="9"/>
+      <c r="A70" s="8"/>
+      <c r="B70" s="8"/>
+      <c r="C70" s="8"/>
+      <c r="D70" s="8"/>
       <c r="M70" s="6"/>
     </row>
     <row r="71" spans="1:13">
-      <c r="A71" s="9"/>
-      <c r="B71" s="9"/>
-      <c r="C71" s="9"/>
-      <c r="D71" s="9"/>
+      <c r="A71" s="8"/>
+      <c r="B71" s="8"/>
+      <c r="C71" s="8"/>
+      <c r="D71" s="8"/>
       <c r="M71" s="6"/>
     </row>
     <row r="72" spans="1:13">
-      <c r="A72" s="9"/>
-      <c r="B72" s="9"/>
-      <c r="C72" s="9"/>
-      <c r="D72" s="9"/>
+      <c r="A72" s="8"/>
+      <c r="B72" s="8"/>
+      <c r="C72" s="8"/>
+      <c r="D72" s="8"/>
       <c r="M72" s="6"/>
     </row>
     <row r="73" spans="1:13">
-      <c r="A73" s="9"/>
-      <c r="B73" s="9"/>
-      <c r="C73" s="9"/>
-      <c r="D73" s="9"/>
+      <c r="A73" s="8"/>
+      <c r="B73" s="8"/>
+      <c r="C73" s="8"/>
+      <c r="D73" s="8"/>
       <c r="M73" s="6"/>
     </row>
     <row r="74" spans="1:13">
-      <c r="A74" s="9"/>
-      <c r="B74" s="9"/>
-      <c r="C74" s="9"/>
-      <c r="D74" s="9"/>
+      <c r="A74" s="8"/>
+      <c r="B74" s="8"/>
+      <c r="C74" s="8"/>
+      <c r="D74" s="8"/>
       <c r="M74" s="6"/>
     </row>
     <row r="75" spans="1:13">
-      <c r="A75" s="9"/>
-      <c r="B75" s="9"/>
-      <c r="C75" s="9"/>
-      <c r="D75" s="9"/>
+      <c r="A75" s="8"/>
+      <c r="B75" s="8"/>
+      <c r="C75" s="8"/>
+      <c r="D75" s="8"/>
       <c r="M75" s="6"/>
     </row>
     <row r="76" spans="1:13">
-      <c r="A76" s="9"/>
-      <c r="B76" s="9"/>
-      <c r="C76" s="9"/>
-      <c r="D76" s="9"/>
+      <c r="A76" s="8"/>
+      <c r="B76" s="8"/>
+      <c r="C76" s="8"/>
+      <c r="D76" s="8"/>
       <c r="M76" s="6"/>
     </row>
     <row r="77" spans="1:13">
-      <c r="A77" s="9"/>
-      <c r="B77" s="9"/>
-      <c r="C77" s="9"/>
-      <c r="D77" s="9"/>
+      <c r="A77" s="8"/>
+      <c r="B77" s="8"/>
+      <c r="C77" s="8"/>
+      <c r="D77" s="8"/>
       <c r="M77" s="6"/>
     </row>
     <row r="78" spans="1:13">
-      <c r="A78" s="9"/>
-      <c r="B78" s="9"/>
-      <c r="C78" s="9"/>
-      <c r="D78" s="9"/>
+      <c r="A78" s="8"/>
+      <c r="B78" s="8"/>
+      <c r="C78" s="8"/>
+      <c r="D78" s="8"/>
       <c r="M78" s="6"/>
     </row>
     <row r="79" spans="1:13">
-      <c r="A79" s="9"/>
-      <c r="B79" s="9"/>
-      <c r="C79" s="9"/>
-      <c r="D79" s="9"/>
+      <c r="A79" s="8"/>
+      <c r="B79" s="8"/>
+      <c r="C79" s="8"/>
+      <c r="D79" s="8"/>
       <c r="M79" s="6"/>
     </row>
     <row r="80" spans="1:13">
-      <c r="A80" s="9"/>
-      <c r="B80" s="9"/>
-      <c r="C80" s="9"/>
-      <c r="D80" s="9"/>
+      <c r="A80" s="8"/>
+      <c r="B80" s="8"/>
+      <c r="C80" s="8"/>
+      <c r="D80" s="8"/>
       <c r="M80" s="6"/>
     </row>
     <row r="81" spans="1:13">
@@ -2072,598 +2212,598 @@
       <c r="M81" s="6"/>
     </row>
     <row r="82" spans="1:13">
-      <c r="A82" s="9"/>
-      <c r="B82" s="9"/>
-      <c r="C82" s="9"/>
-      <c r="D82" s="9"/>
+      <c r="A82" s="8"/>
+      <c r="B82" s="8"/>
+      <c r="C82" s="8"/>
+      <c r="D82" s="8"/>
       <c r="M82" s="6"/>
     </row>
     <row r="83" spans="1:13">
-      <c r="A83" s="9"/>
-      <c r="B83" s="9"/>
-      <c r="C83" s="9"/>
-      <c r="D83" s="9"/>
+      <c r="A83" s="8"/>
+      <c r="B83" s="8"/>
+      <c r="C83" s="8"/>
+      <c r="D83" s="8"/>
       <c r="M83" s="6"/>
     </row>
     <row r="84" spans="1:13">
-      <c r="A84" s="9"/>
-      <c r="B84" s="9"/>
-      <c r="C84" s="9"/>
-      <c r="D84" s="9"/>
+      <c r="A84" s="8"/>
+      <c r="B84" s="8"/>
+      <c r="C84" s="8"/>
+      <c r="D84" s="8"/>
       <c r="M84" s="6"/>
     </row>
     <row r="85" spans="1:13">
-      <c r="A85" s="9"/>
-      <c r="B85" s="9"/>
-      <c r="C85" s="9"/>
-      <c r="D85" s="9"/>
+      <c r="A85" s="8"/>
+      <c r="B85" s="8"/>
+      <c r="C85" s="8"/>
+      <c r="D85" s="8"/>
       <c r="M85" s="6"/>
     </row>
     <row r="86" spans="1:13">
-      <c r="A86" s="9"/>
-      <c r="B86" s="9"/>
-      <c r="C86" s="9"/>
-      <c r="D86" s="9"/>
+      <c r="A86" s="8"/>
+      <c r="B86" s="8"/>
+      <c r="C86" s="8"/>
+      <c r="D86" s="8"/>
       <c r="M86" s="6"/>
     </row>
     <row r="87" spans="1:13">
-      <c r="A87" s="9"/>
-      <c r="B87" s="9"/>
-      <c r="C87" s="9"/>
-      <c r="D87" s="9"/>
+      <c r="A87" s="8"/>
+      <c r="B87" s="8"/>
+      <c r="C87" s="8"/>
+      <c r="D87" s="8"/>
       <c r="M87" s="6"/>
     </row>
     <row r="88" spans="1:13">
-      <c r="A88" s="9"/>
-      <c r="B88" s="9"/>
-      <c r="C88" s="9"/>
-      <c r="D88" s="9"/>
+      <c r="A88" s="8"/>
+      <c r="B88" s="8"/>
+      <c r="C88" s="8"/>
+      <c r="D88" s="8"/>
       <c r="M88" s="6"/>
     </row>
     <row r="89" spans="1:13">
-      <c r="A89" s="9"/>
-      <c r="B89" s="9"/>
-      <c r="C89" s="9"/>
-      <c r="D89" s="9"/>
+      <c r="A89" s="8"/>
+      <c r="B89" s="8"/>
+      <c r="C89" s="8"/>
+      <c r="D89" s="8"/>
       <c r="M89" s="6"/>
     </row>
     <row r="90" spans="1:13">
-      <c r="A90" s="9"/>
-      <c r="B90" s="9"/>
-      <c r="C90" s="9"/>
-      <c r="D90" s="9"/>
+      <c r="A90" s="8"/>
+      <c r="B90" s="8"/>
+      <c r="C90" s="8"/>
+      <c r="D90" s="8"/>
       <c r="M90" s="6"/>
     </row>
     <row r="91" spans="1:13">
-      <c r="A91" s="9"/>
-      <c r="B91" s="9"/>
-      <c r="C91" s="9"/>
-      <c r="D91" s="9"/>
+      <c r="A91" s="8"/>
+      <c r="B91" s="8"/>
+      <c r="C91" s="8"/>
+      <c r="D91" s="8"/>
       <c r="M91" s="6"/>
     </row>
     <row r="92" spans="1:13">
-      <c r="A92" s="9"/>
-      <c r="B92" s="9"/>
-      <c r="C92" s="9"/>
-      <c r="D92" s="9"/>
+      <c r="A92" s="8"/>
+      <c r="B92" s="8"/>
+      <c r="C92" s="8"/>
+      <c r="D92" s="8"/>
       <c r="M92" s="6"/>
     </row>
     <row r="93" spans="1:13">
-      <c r="A93" s="9"/>
-      <c r="B93" s="9"/>
-      <c r="C93" s="9"/>
-      <c r="D93" s="9"/>
+      <c r="A93" s="8"/>
+      <c r="B93" s="8"/>
+      <c r="C93" s="8"/>
+      <c r="D93" s="8"/>
       <c r="M93" s="6"/>
     </row>
     <row r="94" spans="1:13">
-      <c r="A94" s="9"/>
-      <c r="B94" s="9"/>
-      <c r="C94" s="9"/>
-      <c r="D94" s="9"/>
+      <c r="A94" s="8"/>
+      <c r="B94" s="8"/>
+      <c r="C94" s="8"/>
+      <c r="D94" s="8"/>
       <c r="M94" s="6"/>
     </row>
     <row r="95" spans="1:13">
-      <c r="A95" s="9"/>
-      <c r="B95" s="9"/>
-      <c r="C95" s="9"/>
-      <c r="D95" s="9"/>
+      <c r="A95" s="8"/>
+      <c r="B95" s="8"/>
+      <c r="C95" s="8"/>
+      <c r="D95" s="8"/>
       <c r="M95" s="6"/>
     </row>
     <row r="96" spans="1:13">
-      <c r="A96" s="9"/>
-      <c r="B96" s="9"/>
-      <c r="C96" s="9"/>
-      <c r="D96" s="9"/>
+      <c r="A96" s="8"/>
+      <c r="B96" s="8"/>
+      <c r="C96" s="8"/>
+      <c r="D96" s="8"/>
       <c r="M96" s="6"/>
     </row>
     <row r="97" spans="1:13">
-      <c r="A97" s="9"/>
-      <c r="B97" s="9"/>
-      <c r="C97" s="9"/>
-      <c r="D97" s="9"/>
+      <c r="A97" s="8"/>
+      <c r="B97" s="8"/>
+      <c r="C97" s="8"/>
+      <c r="D97" s="8"/>
       <c r="M97" s="6"/>
     </row>
     <row r="98" spans="1:13">
-      <c r="A98" s="9"/>
-      <c r="B98" s="9"/>
-      <c r="C98" s="9"/>
-      <c r="D98" s="9"/>
+      <c r="A98" s="8"/>
+      <c r="B98" s="8"/>
+      <c r="C98" s="8"/>
+      <c r="D98" s="8"/>
       <c r="M98" s="6"/>
     </row>
     <row r="99" spans="1:13">
-      <c r="A99" s="9"/>
-      <c r="B99" s="9"/>
-      <c r="C99" s="9"/>
-      <c r="D99" s="9"/>
+      <c r="A99" s="8"/>
+      <c r="B99" s="8"/>
+      <c r="C99" s="8"/>
+      <c r="D99" s="8"/>
       <c r="M99" s="6"/>
     </row>
     <row r="100" spans="1:13">
-      <c r="A100" s="9"/>
-      <c r="B100" s="9"/>
-      <c r="C100" s="9"/>
-      <c r="D100" s="9"/>
+      <c r="A100" s="8"/>
+      <c r="B100" s="8"/>
+      <c r="C100" s="8"/>
+      <c r="D100" s="8"/>
       <c r="M100" s="6"/>
     </row>
     <row r="101" spans="1:13">
-      <c r="A101" s="9"/>
-      <c r="B101" s="9"/>
-      <c r="C101" s="9"/>
-      <c r="D101" s="9"/>
+      <c r="A101" s="8"/>
+      <c r="B101" s="8"/>
+      <c r="C101" s="8"/>
+      <c r="D101" s="8"/>
       <c r="M101" s="6"/>
     </row>
     <row r="102" spans="1:13">
-      <c r="A102" s="9"/>
-      <c r="B102" s="9"/>
-      <c r="C102" s="9"/>
-      <c r="D102" s="9"/>
+      <c r="A102" s="8"/>
+      <c r="B102" s="8"/>
+      <c r="C102" s="8"/>
+      <c r="D102" s="8"/>
       <c r="M102" s="6"/>
     </row>
     <row r="103" spans="1:13">
-      <c r="A103" s="9"/>
-      <c r="B103" s="9"/>
-      <c r="C103" s="9"/>
-      <c r="D103" s="9"/>
+      <c r="A103" s="8"/>
+      <c r="B103" s="8"/>
+      <c r="C103" s="8"/>
+      <c r="D103" s="8"/>
       <c r="M103" s="6"/>
     </row>
     <row r="104" spans="1:13">
-      <c r="A104" s="9"/>
-      <c r="B104" s="9"/>
-      <c r="C104" s="9"/>
-      <c r="D104" s="9"/>
+      <c r="A104" s="8"/>
+      <c r="B104" s="8"/>
+      <c r="C104" s="8"/>
+      <c r="D104" s="8"/>
       <c r="M104" s="6"/>
     </row>
     <row r="105" spans="1:13">
-      <c r="A105" s="9"/>
-      <c r="B105" s="9"/>
-      <c r="C105" s="9"/>
-      <c r="D105" s="9"/>
+      <c r="A105" s="8"/>
+      <c r="B105" s="8"/>
+      <c r="C105" s="8"/>
+      <c r="D105" s="8"/>
       <c r="M105" s="6"/>
     </row>
     <row r="106" spans="1:13">
-      <c r="A106" s="9"/>
-      <c r="B106" s="9"/>
-      <c r="C106" s="9"/>
-      <c r="D106" s="9"/>
+      <c r="A106" s="8"/>
+      <c r="B106" s="8"/>
+      <c r="C106" s="8"/>
+      <c r="D106" s="8"/>
       <c r="M106" s="6"/>
     </row>
     <row r="107" spans="1:13">
-      <c r="A107" s="9"/>
-      <c r="B107" s="9"/>
-      <c r="C107" s="9"/>
-      <c r="D107" s="9"/>
+      <c r="A107" s="8"/>
+      <c r="B107" s="8"/>
+      <c r="C107" s="8"/>
+      <c r="D107" s="8"/>
       <c r="M107" s="6"/>
     </row>
     <row r="108" spans="1:13">
-      <c r="A108" s="9"/>
-      <c r="B108" s="9"/>
-      <c r="C108" s="9"/>
-      <c r="D108" s="9"/>
+      <c r="A108" s="8"/>
+      <c r="B108" s="8"/>
+      <c r="C108" s="8"/>
+      <c r="D108" s="8"/>
       <c r="M108" s="6"/>
     </row>
     <row r="109" spans="1:13">
-      <c r="A109" s="9"/>
-      <c r="B109" s="9"/>
-      <c r="C109" s="9"/>
-      <c r="D109" s="9"/>
+      <c r="A109" s="8"/>
+      <c r="B109" s="8"/>
+      <c r="C109" s="8"/>
+      <c r="D109" s="8"/>
       <c r="M109" s="6"/>
     </row>
     <row r="110" spans="1:13">
-      <c r="A110" s="9"/>
-      <c r="B110" s="9"/>
-      <c r="C110" s="9"/>
-      <c r="D110" s="9"/>
+      <c r="A110" s="8"/>
+      <c r="B110" s="8"/>
+      <c r="C110" s="8"/>
+      <c r="D110" s="8"/>
       <c r="M110" s="6"/>
     </row>
     <row r="111" spans="1:13">
-      <c r="A111" s="9"/>
-      <c r="B111" s="9"/>
-      <c r="C111" s="9"/>
-      <c r="D111" s="9"/>
+      <c r="A111" s="8"/>
+      <c r="B111" s="8"/>
+      <c r="C111" s="8"/>
+      <c r="D111" s="8"/>
       <c r="M111" s="6"/>
     </row>
     <row r="112" spans="1:13">
-      <c r="A112" s="9"/>
-      <c r="B112" s="9"/>
-      <c r="C112" s="9"/>
-      <c r="D112" s="9"/>
+      <c r="A112" s="8"/>
+      <c r="B112" s="8"/>
+      <c r="C112" s="8"/>
+      <c r="D112" s="8"/>
       <c r="M112" s="6"/>
     </row>
     <row r="113" spans="1:13">
-      <c r="A113" s="9"/>
-      <c r="B113" s="9"/>
-      <c r="C113" s="9"/>
-      <c r="D113" s="9"/>
+      <c r="A113" s="8"/>
+      <c r="B113" s="8"/>
+      <c r="C113" s="8"/>
+      <c r="D113" s="8"/>
       <c r="M113" s="6"/>
     </row>
     <row r="114" spans="1:13">
-      <c r="A114" s="9"/>
-      <c r="B114" s="9"/>
-      <c r="C114" s="9"/>
-      <c r="D114" s="9"/>
+      <c r="A114" s="8"/>
+      <c r="B114" s="8"/>
+      <c r="C114" s="8"/>
+      <c r="D114" s="8"/>
       <c r="M114" s="6"/>
     </row>
     <row r="115" spans="1:13">
-      <c r="A115" s="9"/>
-      <c r="B115" s="9"/>
-      <c r="C115" s="9"/>
-      <c r="D115" s="9"/>
+      <c r="A115" s="8"/>
+      <c r="B115" s="8"/>
+      <c r="C115" s="8"/>
+      <c r="D115" s="8"/>
       <c r="M115" s="6"/>
     </row>
     <row r="116" spans="1:13">
-      <c r="A116" s="9"/>
-      <c r="B116" s="9"/>
-      <c r="C116" s="9"/>
-      <c r="D116" s="9"/>
+      <c r="A116" s="8"/>
+      <c r="B116" s="8"/>
+      <c r="C116" s="8"/>
+      <c r="D116" s="8"/>
       <c r="M116" s="6"/>
     </row>
     <row r="117" spans="1:13">
-      <c r="A117" s="9"/>
-      <c r="B117" s="9"/>
-      <c r="C117" s="9"/>
-      <c r="D117" s="9"/>
+      <c r="A117" s="8"/>
+      <c r="B117" s="8"/>
+      <c r="C117" s="8"/>
+      <c r="D117" s="8"/>
       <c r="M117" s="6"/>
     </row>
     <row r="118" spans="1:13">
-      <c r="A118" s="9"/>
-      <c r="B118" s="9"/>
-      <c r="C118" s="9"/>
-      <c r="D118" s="9"/>
+      <c r="A118" s="8"/>
+      <c r="B118" s="8"/>
+      <c r="C118" s="8"/>
+      <c r="D118" s="8"/>
       <c r="M118" s="6"/>
     </row>
     <row r="119" spans="1:13">
-      <c r="A119" s="9"/>
-      <c r="B119" s="9"/>
-      <c r="C119" s="9"/>
-      <c r="D119" s="9"/>
+      <c r="A119" s="8"/>
+      <c r="B119" s="8"/>
+      <c r="C119" s="8"/>
+      <c r="D119" s="8"/>
       <c r="M119" s="6"/>
     </row>
     <row r="120" spans="1:13">
-      <c r="A120" s="9"/>
-      <c r="B120" s="9"/>
-      <c r="C120" s="9"/>
-      <c r="D120" s="9"/>
+      <c r="A120" s="8"/>
+      <c r="B120" s="8"/>
+      <c r="C120" s="8"/>
+      <c r="D120" s="8"/>
       <c r="M120" s="6"/>
     </row>
     <row r="121" spans="1:13">
-      <c r="A121" s="9"/>
-      <c r="B121" s="9"/>
-      <c r="C121" s="9"/>
-      <c r="D121" s="9"/>
+      <c r="A121" s="8"/>
+      <c r="B121" s="8"/>
+      <c r="C121" s="8"/>
+      <c r="D121" s="8"/>
       <c r="M121" s="6"/>
     </row>
     <row r="122" spans="1:13">
-      <c r="A122" s="9"/>
-      <c r="B122" s="9"/>
-      <c r="C122" s="9"/>
-      <c r="D122" s="9"/>
+      <c r="A122" s="8"/>
+      <c r="B122" s="8"/>
+      <c r="C122" s="8"/>
+      <c r="D122" s="8"/>
       <c r="M122" s="6"/>
     </row>
     <row r="123" spans="1:13">
-      <c r="A123" s="9"/>
-      <c r="B123" s="9"/>
-      <c r="C123" s="9"/>
-      <c r="D123" s="9"/>
+      <c r="A123" s="8"/>
+      <c r="B123" s="8"/>
+      <c r="C123" s="8"/>
+      <c r="D123" s="8"/>
       <c r="M123" s="6"/>
     </row>
     <row r="124" spans="1:13">
-      <c r="A124" s="9"/>
-      <c r="B124" s="9"/>
-      <c r="C124" s="9"/>
-      <c r="D124" s="9"/>
+      <c r="A124" s="8"/>
+      <c r="B124" s="8"/>
+      <c r="C124" s="8"/>
+      <c r="D124" s="8"/>
       <c r="M124" s="6"/>
     </row>
     <row r="125" spans="1:13">
-      <c r="A125" s="9"/>
-      <c r="B125" s="9"/>
-      <c r="C125" s="9"/>
-      <c r="D125" s="9"/>
+      <c r="A125" s="8"/>
+      <c r="B125" s="8"/>
+      <c r="C125" s="8"/>
+      <c r="D125" s="8"/>
       <c r="M125" s="6"/>
     </row>
     <row r="126" spans="1:13">
-      <c r="A126" s="9"/>
-      <c r="B126" s="9"/>
-      <c r="C126" s="9"/>
-      <c r="D126" s="9"/>
+      <c r="A126" s="8"/>
+      <c r="B126" s="8"/>
+      <c r="C126" s="8"/>
+      <c r="D126" s="8"/>
       <c r="M126" s="6"/>
     </row>
     <row r="127" spans="1:13">
-      <c r="A127" s="9"/>
-      <c r="B127" s="9"/>
-      <c r="C127" s="9"/>
-      <c r="D127" s="9"/>
+      <c r="A127" s="8"/>
+      <c r="B127" s="8"/>
+      <c r="C127" s="8"/>
+      <c r="D127" s="8"/>
       <c r="M127" s="6"/>
     </row>
     <row r="128" spans="1:13">
-      <c r="A128" s="9"/>
-      <c r="B128" s="9"/>
-      <c r="C128" s="9"/>
-      <c r="D128" s="9"/>
+      <c r="A128" s="8"/>
+      <c r="B128" s="8"/>
+      <c r="C128" s="8"/>
+      <c r="D128" s="8"/>
       <c r="M128" s="6"/>
     </row>
     <row r="129" spans="1:13">
-      <c r="A129" s="9"/>
-      <c r="B129" s="9"/>
-      <c r="C129" s="9"/>
-      <c r="D129" s="9"/>
+      <c r="A129" s="8"/>
+      <c r="B129" s="8"/>
+      <c r="C129" s="8"/>
+      <c r="D129" s="8"/>
       <c r="M129" s="6"/>
     </row>
     <row r="130" spans="1:13">
-      <c r="A130" s="9"/>
-      <c r="B130" s="9"/>
-      <c r="C130" s="9"/>
-      <c r="D130" s="9"/>
+      <c r="A130" s="8"/>
+      <c r="B130" s="8"/>
+      <c r="C130" s="8"/>
+      <c r="D130" s="8"/>
       <c r="M130" s="6"/>
     </row>
     <row r="131" spans="1:13">
-      <c r="A131" s="9"/>
-      <c r="B131" s="9"/>
-      <c r="C131" s="9"/>
-      <c r="D131" s="9"/>
+      <c r="A131" s="8"/>
+      <c r="B131" s="8"/>
+      <c r="C131" s="8"/>
+      <c r="D131" s="8"/>
       <c r="M131" s="6"/>
     </row>
     <row r="132" spans="1:13">
-      <c r="A132" s="9"/>
-      <c r="B132" s="9"/>
-      <c r="C132" s="9"/>
-      <c r="D132" s="9"/>
+      <c r="A132" s="8"/>
+      <c r="B132" s="8"/>
+      <c r="C132" s="8"/>
+      <c r="D132" s="8"/>
       <c r="M132" s="6"/>
     </row>
     <row r="133" spans="1:13">
-      <c r="A133" s="9"/>
-      <c r="B133" s="9"/>
-      <c r="C133" s="9"/>
-      <c r="D133" s="9"/>
+      <c r="A133" s="8"/>
+      <c r="B133" s="8"/>
+      <c r="C133" s="8"/>
+      <c r="D133" s="8"/>
       <c r="M133" s="6"/>
     </row>
     <row r="134" spans="1:13">
-      <c r="A134" s="9"/>
-      <c r="B134" s="9"/>
-      <c r="C134" s="9"/>
-      <c r="D134" s="9"/>
+      <c r="A134" s="8"/>
+      <c r="B134" s="8"/>
+      <c r="C134" s="8"/>
+      <c r="D134" s="8"/>
       <c r="M134" s="6"/>
     </row>
     <row r="135" spans="1:13">
-      <c r="A135" s="9"/>
-      <c r="B135" s="9"/>
-      <c r="C135" s="9"/>
-      <c r="D135" s="9"/>
+      <c r="A135" s="8"/>
+      <c r="B135" s="8"/>
+      <c r="C135" s="8"/>
+      <c r="D135" s="8"/>
       <c r="M135" s="6"/>
     </row>
     <row r="136" spans="1:13">
-      <c r="A136" s="9"/>
-      <c r="B136" s="9"/>
-      <c r="C136" s="9"/>
-      <c r="D136" s="9"/>
+      <c r="A136" s="8"/>
+      <c r="B136" s="8"/>
+      <c r="C136" s="8"/>
+      <c r="D136" s="8"/>
       <c r="M136" s="6"/>
     </row>
     <row r="137" spans="1:13">
-      <c r="A137" s="9"/>
-      <c r="B137" s="9"/>
-      <c r="C137" s="9"/>
-      <c r="D137" s="9"/>
+      <c r="A137" s="8"/>
+      <c r="B137" s="8"/>
+      <c r="C137" s="8"/>
+      <c r="D137" s="8"/>
       <c r="M137" s="6"/>
     </row>
     <row r="138" spans="1:13">
-      <c r="A138" s="9"/>
-      <c r="B138" s="9"/>
-      <c r="C138" s="9"/>
-      <c r="D138" s="9"/>
+      <c r="A138" s="8"/>
+      <c r="B138" s="8"/>
+      <c r="C138" s="8"/>
+      <c r="D138" s="8"/>
       <c r="M138" s="6"/>
     </row>
     <row r="139" spans="1:13">
-      <c r="A139" s="9"/>
-      <c r="B139" s="9"/>
-      <c r="C139" s="9"/>
-      <c r="D139" s="9"/>
+      <c r="A139" s="8"/>
+      <c r="B139" s="8"/>
+      <c r="C139" s="8"/>
+      <c r="D139" s="8"/>
       <c r="M139" s="6"/>
     </row>
     <row r="140" spans="1:13">
-      <c r="A140" s="9"/>
-      <c r="B140" s="9"/>
-      <c r="C140" s="9"/>
-      <c r="D140" s="9"/>
+      <c r="A140" s="8"/>
+      <c r="B140" s="8"/>
+      <c r="C140" s="8"/>
+      <c r="D140" s="8"/>
       <c r="M140" s="6"/>
     </row>
     <row r="141" spans="1:13">
-      <c r="A141" s="9"/>
-      <c r="B141" s="9"/>
-      <c r="C141" s="9"/>
-      <c r="D141" s="9"/>
+      <c r="A141" s="8"/>
+      <c r="B141" s="8"/>
+      <c r="C141" s="8"/>
+      <c r="D141" s="8"/>
       <c r="M141" s="6"/>
     </row>
     <row r="142" spans="1:13">
-      <c r="A142" s="9"/>
-      <c r="B142" s="9"/>
-      <c r="C142" s="9"/>
-      <c r="D142" s="9"/>
+      <c r="A142" s="8"/>
+      <c r="B142" s="8"/>
+      <c r="C142" s="8"/>
+      <c r="D142" s="8"/>
       <c r="M142" s="6"/>
     </row>
     <row r="143" spans="1:13">
-      <c r="A143" s="9"/>
-      <c r="B143" s="9"/>
-      <c r="C143" s="9"/>
-      <c r="D143" s="9"/>
+      <c r="A143" s="8"/>
+      <c r="B143" s="8"/>
+      <c r="C143" s="8"/>
+      <c r="D143" s="8"/>
       <c r="M143" s="6"/>
     </row>
     <row r="144" spans="1:13">
-      <c r="A144" s="9"/>
-      <c r="B144" s="9"/>
-      <c r="C144" s="9"/>
-      <c r="D144" s="9"/>
+      <c r="A144" s="8"/>
+      <c r="B144" s="8"/>
+      <c r="C144" s="8"/>
+      <c r="D144" s="8"/>
       <c r="M144" s="6"/>
     </row>
     <row r="145" spans="1:13">
-      <c r="A145" s="9"/>
-      <c r="B145" s="9"/>
-      <c r="C145" s="9"/>
-      <c r="D145" s="9"/>
+      <c r="A145" s="8"/>
+      <c r="B145" s="8"/>
+      <c r="C145" s="8"/>
+      <c r="D145" s="8"/>
       <c r="M145" s="6"/>
     </row>
     <row r="146" spans="1:13">
-      <c r="A146" s="9"/>
-      <c r="B146" s="9"/>
-      <c r="C146" s="9"/>
-      <c r="D146" s="9"/>
+      <c r="A146" s="8"/>
+      <c r="B146" s="8"/>
+      <c r="C146" s="8"/>
+      <c r="D146" s="8"/>
       <c r="M146" s="6"/>
     </row>
     <row r="147" spans="1:13">
-      <c r="A147" s="9"/>
-      <c r="B147" s="9"/>
-      <c r="C147" s="9"/>
-      <c r="D147" s="9"/>
+      <c r="A147" s="8"/>
+      <c r="B147" s="8"/>
+      <c r="C147" s="8"/>
+      <c r="D147" s="8"/>
       <c r="M147" s="6"/>
     </row>
     <row r="148" spans="1:13">
-      <c r="A148" s="9"/>
-      <c r="B148" s="9"/>
-      <c r="C148" s="9"/>
-      <c r="D148" s="9"/>
+      <c r="A148" s="8"/>
+      <c r="B148" s="8"/>
+      <c r="C148" s="8"/>
+      <c r="D148" s="8"/>
       <c r="M148" s="6"/>
     </row>
     <row r="149" spans="1:13">
-      <c r="A149" s="9"/>
-      <c r="B149" s="9"/>
-      <c r="C149" s="9"/>
-      <c r="D149" s="9"/>
+      <c r="A149" s="8"/>
+      <c r="B149" s="8"/>
+      <c r="C149" s="8"/>
+      <c r="D149" s="8"/>
       <c r="M149" s="6"/>
     </row>
     <row r="150" spans="1:13">
-      <c r="A150" s="9"/>
-      <c r="B150" s="9"/>
-      <c r="C150" s="9"/>
-      <c r="D150" s="9"/>
+      <c r="A150" s="8"/>
+      <c r="B150" s="8"/>
+      <c r="C150" s="8"/>
+      <c r="D150" s="8"/>
       <c r="M150" s="6"/>
     </row>
     <row r="151" spans="1:13">
-      <c r="A151" s="9"/>
-      <c r="B151" s="9"/>
-      <c r="C151" s="9"/>
-      <c r="D151" s="9"/>
+      <c r="A151" s="8"/>
+      <c r="B151" s="8"/>
+      <c r="C151" s="8"/>
+      <c r="D151" s="8"/>
       <c r="M151" s="6"/>
     </row>
     <row r="152" spans="1:13">
-      <c r="A152" s="9"/>
-      <c r="B152" s="9"/>
-      <c r="C152" s="9"/>
-      <c r="D152" s="9"/>
+      <c r="A152" s="8"/>
+      <c r="B152" s="8"/>
+      <c r="C152" s="8"/>
+      <c r="D152" s="8"/>
       <c r="M152" s="6"/>
     </row>
     <row r="153" spans="1:13">
-      <c r="A153" s="9"/>
-      <c r="B153" s="9"/>
-      <c r="C153" s="9"/>
-      <c r="D153" s="9"/>
+      <c r="A153" s="8"/>
+      <c r="B153" s="8"/>
+      <c r="C153" s="8"/>
+      <c r="D153" s="8"/>
       <c r="M153" s="6"/>
     </row>
     <row r="154" spans="1:13">
-      <c r="A154" s="9"/>
-      <c r="B154" s="9"/>
-      <c r="C154" s="9"/>
-      <c r="D154" s="9"/>
+      <c r="A154" s="8"/>
+      <c r="B154" s="8"/>
+      <c r="C154" s="8"/>
+      <c r="D154" s="8"/>
       <c r="M154" s="6"/>
     </row>
     <row r="155" spans="1:13">
-      <c r="A155" s="9"/>
-      <c r="B155" s="9"/>
-      <c r="C155" s="9"/>
-      <c r="D155" s="9"/>
+      <c r="A155" s="8"/>
+      <c r="B155" s="8"/>
+      <c r="C155" s="8"/>
+      <c r="D155" s="8"/>
       <c r="M155" s="6"/>
     </row>
     <row r="156" spans="1:13">
-      <c r="A156" s="9"/>
-      <c r="B156" s="9"/>
-      <c r="C156" s="9"/>
-      <c r="D156" s="9"/>
+      <c r="A156" s="8"/>
+      <c r="B156" s="8"/>
+      <c r="C156" s="8"/>
+      <c r="D156" s="8"/>
       <c r="M156" s="6"/>
     </row>
     <row r="157" spans="1:13">
-      <c r="A157" s="9"/>
-      <c r="B157" s="9"/>
-      <c r="C157" s="9"/>
-      <c r="D157" s="9"/>
+      <c r="A157" s="8"/>
+      <c r="B157" s="8"/>
+      <c r="C157" s="8"/>
+      <c r="D157" s="8"/>
       <c r="M157" s="6"/>
     </row>
     <row r="158" spans="1:13">
-      <c r="A158" s="9"/>
-      <c r="B158" s="9"/>
-      <c r="C158" s="9"/>
-      <c r="D158" s="9"/>
+      <c r="A158" s="8"/>
+      <c r="B158" s="8"/>
+      <c r="C158" s="8"/>
+      <c r="D158" s="8"/>
       <c r="M158" s="6"/>
     </row>
     <row r="159" spans="1:13">
-      <c r="A159" s="9"/>
-      <c r="B159" s="9"/>
-      <c r="C159" s="9"/>
-      <c r="D159" s="9"/>
+      <c r="A159" s="8"/>
+      <c r="B159" s="8"/>
+      <c r="C159" s="8"/>
+      <c r="D159" s="8"/>
       <c r="M159" s="6"/>
     </row>
     <row r="160" spans="1:13">
-      <c r="A160" s="9"/>
-      <c r="B160" s="9"/>
-      <c r="C160" s="9"/>
-      <c r="D160" s="9"/>
+      <c r="A160" s="8"/>
+      <c r="B160" s="8"/>
+      <c r="C160" s="8"/>
+      <c r="D160" s="8"/>
       <c r="M160" s="6"/>
     </row>
     <row r="161" spans="1:13">
-      <c r="A161" s="9"/>
-      <c r="B161" s="9"/>
-      <c r="C161" s="9"/>
-      <c r="D161" s="9"/>
+      <c r="A161" s="8"/>
+      <c r="B161" s="8"/>
+      <c r="C161" s="8"/>
+      <c r="D161" s="8"/>
       <c r="M161" s="6"/>
     </row>
     <row r="162" spans="1:13">
-      <c r="A162" s="9"/>
-      <c r="B162" s="9"/>
-      <c r="C162" s="9"/>
-      <c r="D162" s="9"/>
+      <c r="A162" s="8"/>
+      <c r="B162" s="8"/>
+      <c r="C162" s="8"/>
+      <c r="D162" s="8"/>
       <c r="M162" s="6"/>
     </row>
     <row r="163" spans="1:13">
-      <c r="A163" s="9"/>
-      <c r="B163" s="9"/>
-      <c r="C163" s="9"/>
-      <c r="D163" s="9"/>
+      <c r="A163" s="8"/>
+      <c r="B163" s="8"/>
+      <c r="C163" s="8"/>
+      <c r="D163" s="8"/>
       <c r="M163" s="6"/>
     </row>
     <row r="164" spans="1:13">
-      <c r="A164" s="9"/>
-      <c r="B164" s="9"/>
-      <c r="C164" s="9"/>
-      <c r="D164" s="9"/>
+      <c r="A164" s="8"/>
+      <c r="B164" s="8"/>
+      <c r="C164" s="8"/>
+      <c r="D164" s="8"/>
       <c r="M164" s="6"/>
     </row>
     <row r="165" spans="1:13">
-      <c r="A165" s="9"/>
-      <c r="B165" s="9"/>
-      <c r="C165" s="9"/>
-      <c r="D165" s="9"/>
+      <c r="A165" s="8"/>
+      <c r="B165" s="8"/>
+      <c r="C165" s="8"/>
+      <c r="D165" s="8"/>
       <c r="M165" s="6"/>
     </row>
     <row r="166" spans="1:13">
-      <c r="A166" s="9"/>
-      <c r="B166" s="9"/>
-      <c r="C166" s="9"/>
-      <c r="D166" s="9"/>
+      <c r="A166" s="8"/>
+      <c r="B166" s="8"/>
+      <c r="C166" s="8"/>
+      <c r="D166" s="8"/>
       <c r="M166" s="6"/>
     </row>
     <row r="167" spans="1:13">
@@ -2672,10 +2812,10 @@
       <c r="M167" s="6"/>
     </row>
     <row r="168" spans="1:13">
-      <c r="A168" s="9"/>
-      <c r="B168" s="9"/>
-      <c r="C168" s="9"/>
-      <c r="D168" s="9"/>
+      <c r="A168" s="8"/>
+      <c r="B168" s="8"/>
+      <c r="C168" s="8"/>
+      <c r="D168" s="8"/>
       <c r="M168" s="6"/>
     </row>
     <row r="169" spans="1:13">
@@ -2684,66 +2824,66 @@
       <c r="M169" s="6"/>
     </row>
     <row r="170" spans="1:13">
-      <c r="A170" s="9"/>
-      <c r="B170" s="9"/>
-      <c r="C170" s="9"/>
-      <c r="D170" s="9"/>
+      <c r="A170" s="8"/>
+      <c r="B170" s="8"/>
+      <c r="C170" s="8"/>
+      <c r="D170" s="8"/>
       <c r="M170" s="6"/>
     </row>
     <row r="171" spans="1:13">
-      <c r="A171" s="9"/>
-      <c r="B171" s="9"/>
-      <c r="C171" s="9"/>
-      <c r="D171" s="9"/>
+      <c r="A171" s="8"/>
+      <c r="B171" s="8"/>
+      <c r="C171" s="8"/>
+      <c r="D171" s="8"/>
       <c r="M171" s="6"/>
     </row>
     <row r="172" spans="1:13">
-      <c r="A172" s="9"/>
-      <c r="B172" s="9"/>
-      <c r="C172" s="9"/>
-      <c r="D172" s="9"/>
+      <c r="A172" s="8"/>
+      <c r="B172" s="8"/>
+      <c r="C172" s="8"/>
+      <c r="D172" s="8"/>
       <c r="M172" s="6"/>
     </row>
     <row r="173" spans="1:13">
-      <c r="A173" s="9"/>
-      <c r="B173" s="9"/>
-      <c r="C173" s="9"/>
-      <c r="D173" s="9"/>
+      <c r="A173" s="8"/>
+      <c r="B173" s="8"/>
+      <c r="C173" s="8"/>
+      <c r="D173" s="8"/>
       <c r="M173" s="6"/>
     </row>
     <row r="174" spans="1:13">
-      <c r="A174" s="9"/>
-      <c r="B174" s="9"/>
-      <c r="C174" s="9"/>
-      <c r="D174" s="9"/>
+      <c r="A174" s="8"/>
+      <c r="B174" s="8"/>
+      <c r="C174" s="8"/>
+      <c r="D174" s="8"/>
       <c r="M174" s="6"/>
     </row>
     <row r="175" spans="1:13">
-      <c r="A175" s="9"/>
-      <c r="B175" s="9"/>
-      <c r="C175" s="9"/>
-      <c r="D175" s="9"/>
+      <c r="A175" s="8"/>
+      <c r="B175" s="8"/>
+      <c r="C175" s="8"/>
+      <c r="D175" s="8"/>
       <c r="M175" s="6"/>
     </row>
     <row r="176" spans="1:13">
-      <c r="A176" s="9"/>
-      <c r="B176" s="9"/>
-      <c r="C176" s="9"/>
-      <c r="D176" s="9"/>
+      <c r="A176" s="8"/>
+      <c r="B176" s="8"/>
+      <c r="C176" s="8"/>
+      <c r="D176" s="8"/>
       <c r="M176" s="6"/>
     </row>
     <row r="177" spans="1:13">
-      <c r="A177" s="9"/>
-      <c r="B177" s="9"/>
-      <c r="C177" s="9"/>
-      <c r="D177" s="9"/>
+      <c r="A177" s="8"/>
+      <c r="B177" s="8"/>
+      <c r="C177" s="8"/>
+      <c r="D177" s="8"/>
       <c r="M177" s="6"/>
     </row>
     <row r="178" spans="1:13">
-      <c r="A178" s="9"/>
-      <c r="B178" s="9"/>
-      <c r="C178" s="9"/>
-      <c r="D178" s="9"/>
+      <c r="A178" s="8"/>
+      <c r="B178" s="8"/>
+      <c r="C178" s="8"/>
+      <c r="D178" s="8"/>
       <c r="M178" s="6"/>
     </row>
     <row r="179" spans="1:13">
@@ -2752,59 +2892,59 @@
       <c r="M179" s="6"/>
     </row>
     <row r="180" spans="1:13">
-      <c r="A180" s="9"/>
-      <c r="B180" s="9"/>
-      <c r="C180" s="9"/>
-      <c r="D180" s="9"/>
+      <c r="A180" s="8"/>
+      <c r="B180" s="8"/>
+      <c r="C180" s="8"/>
+      <c r="D180" s="8"/>
       <c r="M180" s="6"/>
     </row>
     <row r="181" spans="1:13">
-      <c r="A181" s="9"/>
-      <c r="B181" s="9"/>
-      <c r="C181" s="9"/>
-      <c r="D181" s="9"/>
+      <c r="A181" s="8"/>
+      <c r="B181" s="8"/>
+      <c r="C181" s="8"/>
+      <c r="D181" s="8"/>
       <c r="M181" s="6"/>
     </row>
     <row r="182" spans="1:13">
-      <c r="A182" s="9"/>
-      <c r="B182" s="9"/>
-      <c r="C182" s="9"/>
-      <c r="D182" s="9"/>
+      <c r="A182" s="8"/>
+      <c r="B182" s="8"/>
+      <c r="C182" s="8"/>
+      <c r="D182" s="8"/>
       <c r="M182" s="6"/>
     </row>
     <row r="183" spans="1:13">
-      <c r="A183" s="9"/>
-      <c r="B183" s="9"/>
-      <c r="C183" s="9"/>
-      <c r="D183" s="9"/>
+      <c r="A183" s="8"/>
+      <c r="B183" s="8"/>
+      <c r="C183" s="8"/>
+      <c r="D183" s="8"/>
       <c r="M183" s="6"/>
     </row>
     <row r="184" spans="1:13">
-      <c r="A184" s="9"/>
-      <c r="B184" s="9"/>
-      <c r="C184" s="9"/>
-      <c r="D184" s="9"/>
+      <c r="A184" s="8"/>
+      <c r="B184" s="8"/>
+      <c r="C184" s="8"/>
+      <c r="D184" s="8"/>
       <c r="M184" s="6"/>
     </row>
     <row r="185" spans="1:13">
-      <c r="A185" s="9"/>
-      <c r="B185" s="9"/>
-      <c r="C185" s="9"/>
-      <c r="D185" s="9"/>
+      <c r="A185" s="8"/>
+      <c r="B185" s="8"/>
+      <c r="C185" s="8"/>
+      <c r="D185" s="8"/>
       <c r="M185" s="6"/>
     </row>
     <row r="186" spans="1:13">
-      <c r="A186" s="9"/>
-      <c r="B186" s="9"/>
-      <c r="C186" s="9"/>
-      <c r="D186" s="9"/>
+      <c r="A186" s="8"/>
+      <c r="B186" s="8"/>
+      <c r="C186" s="8"/>
+      <c r="D186" s="8"/>
       <c r="M186" s="6"/>
     </row>
     <row r="187" spans="1:13">
-      <c r="A187" s="9"/>
-      <c r="B187" s="9"/>
-      <c r="C187" s="9"/>
-      <c r="D187" s="9"/>
+      <c r="A187" s="8"/>
+      <c r="B187" s="8"/>
+      <c r="C187" s="8"/>
+      <c r="D187" s="8"/>
       <c r="M187" s="6"/>
     </row>
     <row r="188" spans="1:13">
@@ -2813,66 +2953,66 @@
       <c r="M188" s="6"/>
     </row>
     <row r="189" spans="1:13">
-      <c r="A189" s="9"/>
-      <c r="B189" s="9"/>
-      <c r="C189" s="9"/>
-      <c r="D189" s="9"/>
+      <c r="A189" s="8"/>
+      <c r="B189" s="8"/>
+      <c r="C189" s="8"/>
+      <c r="D189" s="8"/>
       <c r="M189" s="6"/>
     </row>
     <row r="190" spans="1:13">
-      <c r="A190" s="9"/>
-      <c r="B190" s="9"/>
-      <c r="C190" s="9"/>
-      <c r="D190" s="9"/>
+      <c r="A190" s="8"/>
+      <c r="B190" s="8"/>
+      <c r="C190" s="8"/>
+      <c r="D190" s="8"/>
       <c r="M190" s="6"/>
     </row>
     <row r="191" spans="1:13">
-      <c r="A191" s="9"/>
-      <c r="B191" s="9"/>
-      <c r="C191" s="9"/>
-      <c r="D191" s="9"/>
+      <c r="A191" s="8"/>
+      <c r="B191" s="8"/>
+      <c r="C191" s="8"/>
+      <c r="D191" s="8"/>
       <c r="M191" s="6"/>
     </row>
     <row r="192" spans="1:13">
-      <c r="A192" s="9"/>
-      <c r="B192" s="9"/>
-      <c r="C192" s="9"/>
-      <c r="D192" s="9"/>
+      <c r="A192" s="8"/>
+      <c r="B192" s="8"/>
+      <c r="C192" s="8"/>
+      <c r="D192" s="8"/>
       <c r="M192" s="6"/>
     </row>
     <row r="193" spans="1:13">
-      <c r="A193" s="9"/>
-      <c r="B193" s="9"/>
-      <c r="C193" s="9"/>
-      <c r="D193" s="9"/>
+      <c r="A193" s="8"/>
+      <c r="B193" s="8"/>
+      <c r="C193" s="8"/>
+      <c r="D193" s="8"/>
       <c r="M193" s="6"/>
     </row>
     <row r="194" spans="1:13">
-      <c r="A194" s="9"/>
-      <c r="B194" s="9"/>
-      <c r="C194" s="9"/>
-      <c r="D194" s="9"/>
+      <c r="A194" s="8"/>
+      <c r="B194" s="8"/>
+      <c r="C194" s="8"/>
+      <c r="D194" s="8"/>
       <c r="M194" s="6"/>
     </row>
     <row r="195" spans="1:13">
-      <c r="A195" s="9"/>
-      <c r="B195" s="9"/>
-      <c r="C195" s="9"/>
-      <c r="D195" s="9"/>
+      <c r="A195" s="8"/>
+      <c r="B195" s="8"/>
+      <c r="C195" s="8"/>
+      <c r="D195" s="8"/>
       <c r="M195" s="6"/>
     </row>
     <row r="196" spans="1:13">
-      <c r="A196" s="9"/>
-      <c r="B196" s="9"/>
-      <c r="C196" s="9"/>
-      <c r="D196" s="9"/>
+      <c r="A196" s="8"/>
+      <c r="B196" s="8"/>
+      <c r="C196" s="8"/>
+      <c r="D196" s="8"/>
       <c r="M196" s="6"/>
     </row>
     <row r="197" spans="1:13">
-      <c r="A197" s="9"/>
-      <c r="B197" s="9"/>
-      <c r="C197" s="9"/>
-      <c r="D197" s="9"/>
+      <c r="A197" s="8"/>
+      <c r="B197" s="8"/>
+      <c r="C197" s="8"/>
+      <c r="D197" s="8"/>
       <c r="M197" s="6"/>
     </row>
     <row r="198" spans="1:13">
@@ -2881,45 +3021,45 @@
       <c r="M198" s="6"/>
     </row>
     <row r="199" spans="1:13">
-      <c r="A199" s="9"/>
-      <c r="B199" s="9"/>
-      <c r="C199" s="9"/>
-      <c r="D199" s="9"/>
+      <c r="A199" s="8"/>
+      <c r="B199" s="8"/>
+      <c r="C199" s="8"/>
+      <c r="D199" s="8"/>
       <c r="M199" s="6"/>
     </row>
     <row r="200" spans="1:13">
-      <c r="A200" s="9"/>
-      <c r="B200" s="9"/>
-      <c r="C200" s="9"/>
-      <c r="D200" s="9"/>
+      <c r="A200" s="8"/>
+      <c r="B200" s="8"/>
+      <c r="C200" s="8"/>
+      <c r="D200" s="8"/>
       <c r="M200" s="6"/>
     </row>
     <row r="201" spans="1:13">
-      <c r="A201" s="9"/>
-      <c r="B201" s="9"/>
-      <c r="C201" s="9"/>
-      <c r="D201" s="9"/>
+      <c r="A201" s="8"/>
+      <c r="B201" s="8"/>
+      <c r="C201" s="8"/>
+      <c r="D201" s="8"/>
       <c r="M201" s="6"/>
     </row>
     <row r="202" spans="1:13">
-      <c r="A202" s="9"/>
-      <c r="B202" s="9"/>
-      <c r="C202" s="9"/>
-      <c r="D202" s="9"/>
+      <c r="A202" s="8"/>
+      <c r="B202" s="8"/>
+      <c r="C202" s="8"/>
+      <c r="D202" s="8"/>
       <c r="M202" s="6"/>
     </row>
     <row r="203" spans="1:13">
-      <c r="A203" s="9"/>
-      <c r="B203" s="9"/>
-      <c r="C203" s="9"/>
-      <c r="D203" s="9"/>
+      <c r="A203" s="8"/>
+      <c r="B203" s="8"/>
+      <c r="C203" s="8"/>
+      <c r="D203" s="8"/>
       <c r="M203" s="6"/>
     </row>
     <row r="204" spans="1:13">
-      <c r="A204" s="9"/>
-      <c r="B204" s="9"/>
-      <c r="C204" s="9"/>
-      <c r="D204" s="9"/>
+      <c r="A204" s="8"/>
+      <c r="B204" s="8"/>
+      <c r="C204" s="8"/>
+      <c r="D204" s="8"/>
       <c r="M204" s="6"/>
     </row>
     <row r="205" spans="1:13">
@@ -2928,17 +3068,17 @@
       <c r="M205" s="6"/>
     </row>
     <row r="206" spans="1:13">
-      <c r="A206" s="9"/>
-      <c r="B206" s="9"/>
-      <c r="C206" s="9"/>
-      <c r="D206" s="9"/>
+      <c r="A206" s="8"/>
+      <c r="B206" s="8"/>
+      <c r="C206" s="8"/>
+      <c r="D206" s="8"/>
       <c r="M206" s="6"/>
     </row>
     <row r="207" spans="1:13">
-      <c r="A207" s="9"/>
-      <c r="B207" s="9"/>
-      <c r="C207" s="9"/>
-      <c r="D207" s="9"/>
+      <c r="A207" s="8"/>
+      <c r="B207" s="8"/>
+      <c r="C207" s="8"/>
+      <c r="D207" s="8"/>
       <c r="M207" s="6"/>
     </row>
     <row r="208" spans="1:13">
@@ -2947,143 +3087,143 @@
       <c r="M208" s="6"/>
     </row>
     <row r="209" spans="1:13">
-      <c r="A209" s="9"/>
-      <c r="B209" s="9"/>
-      <c r="C209" s="9"/>
-      <c r="D209" s="9"/>
+      <c r="A209" s="8"/>
+      <c r="B209" s="8"/>
+      <c r="C209" s="8"/>
+      <c r="D209" s="8"/>
       <c r="M209" s="6"/>
     </row>
     <row r="210" spans="1:13">
-      <c r="A210" s="9"/>
-      <c r="B210" s="9"/>
-      <c r="C210" s="9"/>
-      <c r="D210" s="9"/>
+      <c r="A210" s="8"/>
+      <c r="B210" s="8"/>
+      <c r="C210" s="8"/>
+      <c r="D210" s="8"/>
       <c r="M210" s="6"/>
     </row>
     <row r="211" spans="1:13">
-      <c r="A211" s="9"/>
-      <c r="B211" s="9"/>
-      <c r="C211" s="9"/>
-      <c r="D211" s="9"/>
+      <c r="A211" s="8"/>
+      <c r="B211" s="8"/>
+      <c r="C211" s="8"/>
+      <c r="D211" s="8"/>
       <c r="M211" s="6"/>
     </row>
     <row r="212" spans="1:13">
-      <c r="A212" s="9"/>
-      <c r="B212" s="9"/>
-      <c r="C212" s="9"/>
-      <c r="D212" s="9"/>
+      <c r="A212" s="8"/>
+      <c r="B212" s="8"/>
+      <c r="C212" s="8"/>
+      <c r="D212" s="8"/>
       <c r="M212" s="6"/>
     </row>
     <row r="213" spans="1:13">
-      <c r="A213" s="9"/>
-      <c r="B213" s="9"/>
-      <c r="C213" s="9"/>
-      <c r="D213" s="9"/>
+      <c r="A213" s="8"/>
+      <c r="B213" s="8"/>
+      <c r="C213" s="8"/>
+      <c r="D213" s="8"/>
       <c r="M213" s="6"/>
     </row>
     <row r="214" spans="1:13">
-      <c r="A214" s="9"/>
-      <c r="B214" s="9"/>
-      <c r="C214" s="9"/>
-      <c r="D214" s="9"/>
+      <c r="A214" s="8"/>
+      <c r="B214" s="8"/>
+      <c r="C214" s="8"/>
+      <c r="D214" s="8"/>
       <c r="M214" s="6"/>
     </row>
     <row r="215" spans="1:13">
-      <c r="A215" s="9"/>
-      <c r="B215" s="9"/>
-      <c r="C215" s="9"/>
-      <c r="D215" s="9"/>
+      <c r="A215" s="8"/>
+      <c r="B215" s="8"/>
+      <c r="C215" s="8"/>
+      <c r="D215" s="8"/>
       <c r="M215" s="6"/>
     </row>
     <row r="216" spans="1:13">
-      <c r="A216" s="9"/>
-      <c r="B216" s="9"/>
-      <c r="C216" s="9"/>
-      <c r="D216" s="9"/>
+      <c r="A216" s="8"/>
+      <c r="B216" s="8"/>
+      <c r="C216" s="8"/>
+      <c r="D216" s="8"/>
       <c r="M216" s="6"/>
     </row>
     <row r="217" spans="1:13">
-      <c r="A217" s="9"/>
-      <c r="B217" s="9"/>
-      <c r="C217" s="9"/>
-      <c r="D217" s="9"/>
+      <c r="A217" s="8"/>
+      <c r="B217" s="8"/>
+      <c r="C217" s="8"/>
+      <c r="D217" s="8"/>
       <c r="M217" s="6"/>
     </row>
     <row r="218" spans="1:13">
-      <c r="A218" s="9"/>
-      <c r="B218" s="9"/>
-      <c r="C218" s="9"/>
-      <c r="D218" s="9"/>
+      <c r="A218" s="8"/>
+      <c r="B218" s="8"/>
+      <c r="C218" s="8"/>
+      <c r="D218" s="8"/>
       <c r="M218" s="6"/>
     </row>
     <row r="219" spans="1:13">
-      <c r="A219" s="9"/>
-      <c r="B219" s="9"/>
-      <c r="C219" s="9"/>
-      <c r="D219" s="9"/>
+      <c r="A219" s="8"/>
+      <c r="B219" s="8"/>
+      <c r="C219" s="8"/>
+      <c r="D219" s="8"/>
       <c r="M219" s="6"/>
     </row>
     <row r="220" spans="1:13">
-      <c r="A220" s="9"/>
-      <c r="B220" s="9"/>
-      <c r="C220" s="9"/>
-      <c r="D220" s="9"/>
+      <c r="A220" s="8"/>
+      <c r="B220" s="8"/>
+      <c r="C220" s="8"/>
+      <c r="D220" s="8"/>
       <c r="M220" s="6"/>
     </row>
     <row r="221" spans="1:13">
-      <c r="A221" s="9"/>
-      <c r="B221" s="9"/>
-      <c r="C221" s="9"/>
-      <c r="D221" s="9"/>
+      <c r="A221" s="8"/>
+      <c r="B221" s="8"/>
+      <c r="C221" s="8"/>
+      <c r="D221" s="8"/>
       <c r="M221" s="6"/>
     </row>
     <row r="222" spans="1:13">
-      <c r="A222" s="9"/>
-      <c r="B222" s="9"/>
-      <c r="C222" s="9"/>
-      <c r="D222" s="9"/>
+      <c r="A222" s="8"/>
+      <c r="B222" s="8"/>
+      <c r="C222" s="8"/>
+      <c r="D222" s="8"/>
       <c r="M222" s="6"/>
     </row>
     <row r="223" spans="1:13">
-      <c r="A223" s="9"/>
-      <c r="B223" s="9"/>
-      <c r="C223" s="9"/>
-      <c r="D223" s="9"/>
+      <c r="A223" s="8"/>
+      <c r="B223" s="8"/>
+      <c r="C223" s="8"/>
+      <c r="D223" s="8"/>
       <c r="M223" s="6"/>
     </row>
     <row r="224" spans="1:13">
-      <c r="A224" s="9"/>
-      <c r="B224" s="9"/>
-      <c r="C224" s="9"/>
-      <c r="D224" s="9"/>
+      <c r="A224" s="8"/>
+      <c r="B224" s="8"/>
+      <c r="C224" s="8"/>
+      <c r="D224" s="8"/>
       <c r="M224" s="6"/>
     </row>
     <row r="225" spans="1:13">
-      <c r="A225" s="9"/>
-      <c r="B225" s="9"/>
-      <c r="C225" s="9"/>
-      <c r="D225" s="9"/>
+      <c r="A225" s="8"/>
+      <c r="B225" s="8"/>
+      <c r="C225" s="8"/>
+      <c r="D225" s="8"/>
       <c r="M225" s="6"/>
     </row>
     <row r="226" spans="1:13">
-      <c r="A226" s="9"/>
-      <c r="B226" s="9"/>
-      <c r="C226" s="9"/>
-      <c r="D226" s="9"/>
+      <c r="A226" s="8"/>
+      <c r="B226" s="8"/>
+      <c r="C226" s="8"/>
+      <c r="D226" s="8"/>
       <c r="M226" s="6"/>
     </row>
     <row r="227" spans="1:13">
-      <c r="A227" s="9"/>
-      <c r="B227" s="9"/>
-      <c r="C227" s="9"/>
-      <c r="D227" s="9"/>
+      <c r="A227" s="8"/>
+      <c r="B227" s="8"/>
+      <c r="C227" s="8"/>
+      <c r="D227" s="8"/>
       <c r="M227" s="6"/>
     </row>
     <row r="228" spans="1:13">
-      <c r="A228" s="9"/>
-      <c r="B228" s="9"/>
-      <c r="C228" s="9"/>
-      <c r="D228" s="9"/>
+      <c r="A228" s="8"/>
+      <c r="B228" s="8"/>
+      <c r="C228" s="8"/>
+      <c r="D228" s="8"/>
       <c r="M228" s="6"/>
     </row>
   </sheetData>

--- a/cw71012026.xlsx
+++ b/cw71012026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5711AD4B-2DAA-3B49-9462-58A74DC1557C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD359BC5-F077-E74B-9BC3-1216593DE0AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="620" windowWidth="14620" windowHeight="17380" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
+    <workbookView xWindow="120" yWindow="640" windowWidth="20680" windowHeight="17380" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="97">
   <si>
     <t>Surname</t>
   </si>
@@ -321,6 +321,12 @@
   </si>
   <si>
     <t>H269439T</t>
+  </si>
+  <si>
+    <t>Mariga</t>
+  </si>
+  <si>
+    <t>H231095Q</t>
   </si>
 </sst>
 </file>
@@ -474,7 +480,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -499,7 +505,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -508,20 +513,46 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="6">
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -562,13 +593,13 @@
   </sortState>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{1B9A59CC-67BA-3D4E-8BF2-E846FAA4CCF7}" name="Surname"/>
-    <tableColumn id="2" xr3:uid="{F58DECFD-039A-A04B-8F5C-EAB87EBDF67E}" name="Reg" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{F58DECFD-039A-A04B-8F5C-EAB87EBDF67E}" name="Reg" dataDxfId="5"/>
     <tableColumn id="3" xr3:uid="{B367B5B8-26A8-004D-8405-A55D6B3FB2B6}" name="Dept"/>
-    <tableColumn id="4" xr3:uid="{248CFFC4-D566-4C47-A784-2D182108B777}" name="Quiz_1" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{4A2A2B68-EF30-7742-9921-AE9C8CB19994}" name="Quiz_2"/>
-    <tableColumn id="6" xr3:uid="{F4845CBF-1A2D-6F4D-8189-BDA9FF51FC40}" name="Quiz_3"/>
-    <tableColumn id="7" xr3:uid="{C50393AC-DA9E-B244-B444-966939E941DB}" name="Test_1"/>
-    <tableColumn id="8" xr3:uid="{8357C7A6-F90C-A948-931D-7D4829EE9A20}" name="Test_2 " dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{248CFFC4-D566-4C47-A784-2D182108B777}" name="Quiz_1" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{4A2A2B68-EF30-7742-9921-AE9C8CB19994}" name="Quiz_2" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{F4845CBF-1A2D-6F4D-8189-BDA9FF51FC40}" name="Quiz_3" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{C50393AC-DA9E-B244-B444-966939E941DB}" name="Test_1" dataDxfId="0"/>
+    <tableColumn id="8" xr3:uid="{8357C7A6-F90C-A948-931D-7D4829EE9A20}" name="Test_2 " dataDxfId="1"/>
     <tableColumn id="9" xr3:uid="{AF37A560-C5F8-4E49-A224-CE84A49E046A}" name="Test_3 "/>
     <tableColumn id="10" xr3:uid="{E7DCE493-9761-F446-9017-EFE5CA173E6F}" name="AS_1"/>
     <tableColumn id="11" xr3:uid="{22CC7E9A-51CA-274B-9C92-B1E8F88F4324}" name="AS_2 "/>
@@ -901,6 +932,7 @@
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="4" max="7" width="10.7109375" style="22"/>
     <col min="8" max="8" width="10.7109375" style="4"/>
   </cols>
   <sheetData>
@@ -914,16 +946,16 @@
       <c r="C1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="22" t="s">
         <v>8</v>
       </c>
       <c r="H1" s="4" t="s">
@@ -946,29 +978,31 @@
       </c>
     </row>
     <row r="2" spans="1:13" ht="20">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="27" t="s">
         <v>71</v>
       </c>
       <c r="C2" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D2" s="18">
+      <c r="D2" s="23">
         <v>0.85</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="22">
         <v>0</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="22">
         <v>0.35</v>
       </c>
-      <c r="H2" s="5"/>
+      <c r="H2" s="5">
+        <v>0</v>
+      </c>
       <c r="J2">
         <v>0.66</v>
       </c>
-      <c r="M2" s="20"/>
+      <c r="M2" s="19"/>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="11" t="s">
@@ -980,16 +1014,21 @@
       <c r="C3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="24">
         <v>0.83</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="22">
         <v>0.98</v>
       </c>
-      <c r="G3">
+      <c r="F3" s="22">
+        <v>0.94</v>
+      </c>
+      <c r="G3" s="22">
         <v>0.6</v>
       </c>
-      <c r="H3" s="5"/>
+      <c r="H3" s="5">
+        <v>0.76</v>
+      </c>
       <c r="J3">
         <v>0.54</v>
       </c>
@@ -1005,16 +1044,21 @@
       <c r="C4" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="24">
         <v>0.87</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="22">
         <v>0.98</v>
       </c>
-      <c r="G4">
+      <c r="F4" s="22">
+        <v>0</v>
+      </c>
+      <c r="G4" s="22">
         <v>0.44</v>
       </c>
-      <c r="H4" s="5"/>
+      <c r="H4" s="5">
+        <v>0.67</v>
+      </c>
       <c r="M4" s="10"/>
     </row>
     <row r="5" spans="1:13">
@@ -1027,16 +1071,21 @@
       <c r="C5" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="24">
         <v>0.88</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="22">
         <v>1</v>
       </c>
-      <c r="G5">
+      <c r="F5" s="22">
+        <v>0.97</v>
+      </c>
+      <c r="G5" s="22">
         <v>0.21</v>
       </c>
-      <c r="H5" s="5"/>
+      <c r="H5" s="5">
+        <v>0.59</v>
+      </c>
       <c r="M5" s="10"/>
     </row>
     <row r="6" spans="1:13">
@@ -1049,20 +1098,25 @@
       <c r="C6" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="24">
         <v>0.71</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="22">
         <v>0.81</v>
       </c>
-      <c r="G6">
+      <c r="F6" s="22">
+        <v>0.97</v>
+      </c>
+      <c r="G6" s="22">
         <v>0.21</v>
       </c>
-      <c r="H6" s="5"/>
+      <c r="H6" s="5">
+        <v>0.22</v>
+      </c>
       <c r="J6">
         <v>0.79</v>
       </c>
-      <c r="M6" s="21"/>
+      <c r="M6" s="20"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="11" t="s">
@@ -1074,16 +1128,21 @@
       <c r="C7" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="24">
         <v>0.88</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="22">
         <v>0.96</v>
       </c>
-      <c r="G7">
+      <c r="F7" s="22">
+        <v>0.97</v>
+      </c>
+      <c r="G7" s="22">
         <v>0.67</v>
       </c>
-      <c r="H7" s="5"/>
+      <c r="H7" s="5">
+        <v>0.8</v>
+      </c>
       <c r="J7">
         <v>0.69</v>
       </c>
@@ -1099,16 +1158,21 @@
       <c r="C8" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="24">
         <v>0.76</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="22">
         <v>0.87</v>
       </c>
-      <c r="G8">
+      <c r="F8" s="22">
+        <v>0.84</v>
+      </c>
+      <c r="G8" s="22">
         <v>0.32</v>
       </c>
-      <c r="H8" s="5"/>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
       <c r="J8">
         <v>0.79</v>
       </c>
@@ -1124,16 +1188,21 @@
       <c r="C9" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="24">
         <v>0.6</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="22">
         <v>0.97</v>
       </c>
-      <c r="G9">
+      <c r="F9" s="22">
+        <v>1</v>
+      </c>
+      <c r="G9" s="22">
         <v>0.16</v>
       </c>
-      <c r="H9" s="5"/>
+      <c r="H9" s="5">
+        <v>0.24</v>
+      </c>
       <c r="J9">
         <v>0.82</v>
       </c>
@@ -1149,16 +1218,21 @@
       <c r="C10" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="24">
         <v>0.75</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="22">
         <v>0.98</v>
       </c>
-      <c r="G10">
+      <c r="F10" s="22">
+        <v>0.94</v>
+      </c>
+      <c r="G10" s="22">
         <v>0.26</v>
       </c>
-      <c r="H10" s="5"/>
+      <c r="H10" s="5">
+        <v>0.22</v>
+      </c>
       <c r="M10" s="6"/>
     </row>
     <row r="11" spans="1:13">
@@ -1171,16 +1245,21 @@
       <c r="C11" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="24">
         <v>0.61</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="22">
         <v>0</v>
       </c>
-      <c r="G11">
+      <c r="F11" s="22">
+        <v>0.91</v>
+      </c>
+      <c r="G11" s="22">
         <v>0.18</v>
       </c>
-      <c r="H11" s="5"/>
+      <c r="H11" s="5">
+        <v>0.45</v>
+      </c>
       <c r="M11" s="6"/>
     </row>
     <row r="12" spans="1:13">
@@ -1193,16 +1272,21 @@
       <c r="C12" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="24">
         <v>0.83</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="22">
         <v>0.98</v>
       </c>
-      <c r="G12">
+      <c r="F12" s="22">
+        <v>1</v>
+      </c>
+      <c r="G12" s="22">
         <v>0.23</v>
       </c>
-      <c r="H12" s="5"/>
+      <c r="H12" s="5">
+        <v>0.71</v>
+      </c>
       <c r="J12">
         <v>0.76</v>
       </c>
@@ -1218,16 +1302,21 @@
       <c r="C13" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="24">
         <v>0.9</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="22">
         <v>0.98</v>
       </c>
-      <c r="G13">
+      <c r="F13" s="22">
+        <v>1</v>
+      </c>
+      <c r="G13" s="22">
         <v>0</v>
       </c>
-      <c r="H13" s="5"/>
+      <c r="H13" s="5">
+        <v>0.12</v>
+      </c>
       <c r="J13">
         <v>0.69</v>
       </c>
@@ -1243,16 +1332,21 @@
       <c r="C14" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="24">
         <v>0.72</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="22">
         <v>0.94</v>
       </c>
-      <c r="G14">
+      <c r="F14" s="22">
+        <v>0.91</v>
+      </c>
+      <c r="G14" s="22">
         <v>0.49</v>
       </c>
-      <c r="H14" s="5"/>
+      <c r="H14" s="5">
+        <v>0.71</v>
+      </c>
       <c r="J14">
         <v>0.79</v>
       </c>
@@ -1268,16 +1362,21 @@
       <c r="C15" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="24">
         <v>0.87</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="22">
         <v>0</v>
       </c>
-      <c r="G15">
+      <c r="F15" s="22">
+        <v>0</v>
+      </c>
+      <c r="G15" s="22">
         <v>0.39</v>
       </c>
-      <c r="H15" s="5"/>
+      <c r="H15" s="5">
+        <v>0.67</v>
+      </c>
       <c r="M15" s="6"/>
     </row>
     <row r="16" spans="1:13">
@@ -1290,58 +1389,73 @@
       <c r="C16" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="24">
         <v>0.86</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="22">
         <v>0.8</v>
       </c>
-      <c r="G16">
+      <c r="F16" s="22">
+        <v>0</v>
+      </c>
+      <c r="G16" s="22">
         <v>0.37</v>
       </c>
-      <c r="H16" s="5"/>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
       <c r="J16">
         <v>0.75</v>
       </c>
       <c r="M16" s="6"/>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" s="24" t="s">
+      <c r="A17" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="B17" s="24" t="s">
+      <c r="B17" s="9" t="s">
         <v>94</v>
       </c>
       <c r="C17" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="25">
         <v>0</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="22">
         <v>0.98</v>
       </c>
-      <c r="H17" s="5"/>
+      <c r="F17" s="22">
+        <v>0.94</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0.71</v>
+      </c>
       <c r="M17" s="6"/>
     </row>
     <row r="18" spans="1:13">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="B18" s="22"/>
+      <c r="B18" s="21"/>
       <c r="C18" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="25">
         <v>0</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="22">
         <v>0</v>
       </c>
-      <c r="G18">
+      <c r="F18" s="22">
         <v>0</v>
       </c>
-      <c r="H18" s="5"/>
+      <c r="G18" s="22">
+        <v>0</v>
+      </c>
+      <c r="H18" s="5">
+        <v>0</v>
+      </c>
       <c r="J18">
         <v>0.48</v>
       </c>
@@ -1357,16 +1471,21 @@
       <c r="C19" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="24">
         <v>0.96</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="22">
         <v>0.92</v>
       </c>
-      <c r="G19">
+      <c r="F19" s="22">
+        <v>0.97</v>
+      </c>
+      <c r="G19" s="22">
         <v>0.51</v>
       </c>
-      <c r="H19" s="5"/>
+      <c r="H19" s="5">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="J19">
         <v>0.85</v>
       </c>
@@ -1382,16 +1501,21 @@
       <c r="C20" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="11">
+      <c r="D20" s="24">
         <v>0.81</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="22">
         <v>0.94</v>
       </c>
-      <c r="G20">
+      <c r="F20" s="22">
+        <v>0.97</v>
+      </c>
+      <c r="G20" s="22">
         <v>0.72</v>
       </c>
-      <c r="H20" s="5"/>
+      <c r="H20" s="5">
+        <v>0.61</v>
+      </c>
       <c r="J20">
         <v>0.79</v>
       </c>
@@ -1407,16 +1531,21 @@
       <c r="C21" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="11">
+      <c r="D21" s="24">
         <v>0.91</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="22">
         <v>0.98</v>
       </c>
-      <c r="G21">
+      <c r="F21" s="22">
+        <v>0</v>
+      </c>
+      <c r="G21" s="22">
         <v>0.47</v>
       </c>
-      <c r="H21" s="5"/>
+      <c r="H21" s="5">
+        <v>0.12</v>
+      </c>
       <c r="J21">
         <v>0.87</v>
       </c>
@@ -1432,532 +1561,617 @@
       <c r="C22" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="11">
+      <c r="D22" s="24">
         <v>0.89</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="22">
         <v>0.92</v>
       </c>
-      <c r="G22">
+      <c r="F22" s="22">
+        <v>0</v>
+      </c>
+      <c r="G22" s="22">
         <v>0.33</v>
       </c>
-      <c r="H22" s="5"/>
+      <c r="H22" s="5">
+        <v>0.45</v>
+      </c>
       <c r="J22">
         <v>0.67</v>
       </c>
       <c r="M22" s="6"/>
     </row>
     <row r="23" spans="1:13">
-      <c r="A23" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C23" s="11" t="s">
+      <c r="A23" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" t="s">
         <v>16</v>
       </c>
-      <c r="D23" s="11">
-        <v>0.9</v>
-      </c>
-      <c r="E23">
-        <v>0.94</v>
-      </c>
-      <c r="G23">
-        <v>0.49</v>
-      </c>
-      <c r="H23" s="5"/>
-      <c r="J23">
-        <v>0.87</v>
+      <c r="D23" s="25">
+        <v>0</v>
+      </c>
+      <c r="E23" s="22">
+        <v>0</v>
+      </c>
+      <c r="F23" s="22">
+        <v>1</v>
+      </c>
+      <c r="G23" s="22">
+        <v>0</v>
+      </c>
+      <c r="H23" s="5">
+        <v>0</v>
       </c>
       <c r="M23" s="6"/>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D24" s="11">
+      <c r="D24" s="24">
+        <v>0.9</v>
+      </c>
+      <c r="E24" s="22">
+        <v>0.94</v>
+      </c>
+      <c r="F24" s="22">
+        <v>1</v>
+      </c>
+      <c r="G24" s="22">
+        <v>0.49</v>
+      </c>
+      <c r="H24" s="5">
+        <v>0.47</v>
+      </c>
+      <c r="J24">
+        <v>0.87</v>
+      </c>
+      <c r="M24" s="6"/>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="24">
         <v>0.8</v>
       </c>
-      <c r="E24">
+      <c r="E25" s="22">
         <v>1</v>
       </c>
-      <c r="G24">
+      <c r="F25" s="22">
+        <v>0</v>
+      </c>
+      <c r="G25" s="22">
         <v>0.39</v>
       </c>
-      <c r="H24" s="5"/>
-      <c r="M24" s="6"/>
-    </row>
-    <row r="25" spans="1:13">
-      <c r="A25" s="9" t="s">
+      <c r="H25" s="5">
+        <v>0.63</v>
+      </c>
+      <c r="M25" s="6"/>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B26" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C26" t="s">
         <v>16</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D26" s="25">
         <v>0</v>
       </c>
-      <c r="E25">
+      <c r="E26" s="22">
         <v>0.92</v>
       </c>
-      <c r="G25">
+      <c r="F26" s="22">
+        <v>0.94</v>
+      </c>
+      <c r="G26" s="22">
         <v>0</v>
       </c>
-      <c r="H25" s="5"/>
-      <c r="J25">
+      <c r="H26" s="5">
+        <v>0</v>
+      </c>
+      <c r="J26">
         <v>0.78</v>
       </c>
-      <c r="M25" s="6"/>
-    </row>
-    <row r="26" spans="1:13">
-      <c r="A26" s="26" t="s">
+      <c r="M26" s="6"/>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="B26" s="26" t="s">
+      <c r="B27" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C27" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D26" s="11">
+      <c r="D27" s="24">
         <v>0.95</v>
       </c>
-      <c r="E26">
+      <c r="E27" s="22">
         <v>0.98</v>
       </c>
-      <c r="G26">
+      <c r="F27" s="22">
+        <v>0.94</v>
+      </c>
+      <c r="G27" s="22">
         <v>0.72</v>
       </c>
-      <c r="H26" s="5"/>
-      <c r="M26" s="6"/>
-    </row>
-    <row r="27" spans="1:13" ht="20">
-      <c r="A27" s="25" t="s">
+      <c r="H27" s="5">
+        <v>0.65</v>
+      </c>
+      <c r="M27" s="6"/>
+    </row>
+    <row r="28" spans="1:13" ht="20">
+      <c r="A28" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="B27" s="25" t="s">
+      <c r="B28" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C28" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D27" s="18">
+      <c r="D28" s="23">
         <v>0.87</v>
       </c>
-      <c r="E27">
+      <c r="E28" s="22">
         <v>0.89</v>
       </c>
-      <c r="G27">
+      <c r="F28" s="22">
+        <v>0.97</v>
+      </c>
+      <c r="G28" s="22">
         <v>0</v>
       </c>
-      <c r="H27" s="5"/>
-      <c r="M27" s="6"/>
-    </row>
-    <row r="28" spans="1:13">
-      <c r="A28" s="26" t="s">
+      <c r="H28" s="5">
+        <v>0.59</v>
+      </c>
+      <c r="M28" s="6"/>
+    </row>
+    <row r="29" spans="1:13">
+      <c r="A29" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="26" t="s">
+      <c r="B29" s="31" t="s">
         <v>57</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D28" s="11">
-        <v>0.85</v>
-      </c>
-      <c r="E28">
-        <v>0.89</v>
-      </c>
-      <c r="G28">
-        <v>0.54</v>
-      </c>
-      <c r="H28" s="5"/>
-      <c r="J28">
-        <v>0.84</v>
-      </c>
-      <c r="M28" s="6"/>
-    </row>
-    <row r="29" spans="1:13">
-      <c r="A29" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="B29" s="26" t="s">
-        <v>59</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D29" s="11">
+      <c r="D29" s="24">
+        <v>0.85</v>
+      </c>
+      <c r="E29" s="22">
         <v>0.89</v>
       </c>
-      <c r="E29">
-        <v>0.97</v>
-      </c>
-      <c r="G29">
+      <c r="F29" s="22">
+        <v>0.94</v>
+      </c>
+      <c r="G29" s="22">
         <v>0.54</v>
       </c>
-      <c r="H29" s="5"/>
+      <c r="H29" s="5">
+        <v>0.76</v>
+      </c>
       <c r="J29">
-        <v>0.81</v>
+        <v>0.84</v>
       </c>
       <c r="M29" s="6"/>
     </row>
     <row r="30" spans="1:13">
-      <c r="A30" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="B30" s="19" t="s">
-        <v>61</v>
+      <c r="A30" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>59</v>
       </c>
       <c r="C30" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D30" s="11">
-        <v>0.83</v>
-      </c>
-      <c r="E30">
+      <c r="D30" s="24">
+        <v>0.89</v>
+      </c>
+      <c r="E30" s="22">
+        <v>0.97</v>
+      </c>
+      <c r="F30" s="22">
         <v>1</v>
       </c>
-      <c r="G30">
-        <v>0.18</v>
-      </c>
-      <c r="H30" s="5"/>
+      <c r="G30" s="22">
+        <v>0.54</v>
+      </c>
+      <c r="H30" s="5">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="J30">
+        <v>0.81</v>
+      </c>
       <c r="M30" s="6"/>
     </row>
     <row r="31" spans="1:13">
-      <c r="A31" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="B31" s="19" t="s">
-        <v>63</v>
+      <c r="A31" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>61</v>
       </c>
       <c r="C31" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D31" s="11">
-        <v>0.7</v>
-      </c>
-      <c r="E31">
-        <v>0.98</v>
-      </c>
-      <c r="G31">
-        <v>0.68</v>
-      </c>
-      <c r="H31" s="5"/>
-      <c r="J31">
-        <v>0.79</v>
+      <c r="D31" s="24">
+        <v>0.83</v>
+      </c>
+      <c r="E31" s="22">
+        <v>1</v>
+      </c>
+      <c r="F31" s="22">
+        <v>1</v>
+      </c>
+      <c r="G31" s="22">
+        <v>0.18</v>
+      </c>
+      <c r="H31" s="5">
+        <v>0.16</v>
       </c>
       <c r="M31" s="6"/>
     </row>
     <row r="32" spans="1:13">
-      <c r="A32" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="B32" s="19" t="s">
-        <v>65</v>
+      <c r="A32" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>63</v>
       </c>
       <c r="C32" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D32" s="11">
-        <v>0.93</v>
-      </c>
-      <c r="E32">
-        <v>0.92</v>
-      </c>
-      <c r="G32">
-        <v>0.46</v>
-      </c>
-      <c r="H32" s="5"/>
+      <c r="D32" s="24">
+        <v>0.7</v>
+      </c>
+      <c r="E32" s="22">
+        <v>0.98</v>
+      </c>
+      <c r="F32" s="22">
+        <v>0.94</v>
+      </c>
+      <c r="G32" s="22">
+        <v>0.68</v>
+      </c>
+      <c r="H32" s="5">
+        <v>0.35</v>
+      </c>
       <c r="J32">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="M32" s="6"/>
     </row>
     <row r="33" spans="1:13">
-      <c r="A33" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="B33" s="19" t="s">
-        <v>67</v>
+      <c r="A33" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>65</v>
       </c>
       <c r="C33" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D33" s="11">
-        <v>0.82</v>
-      </c>
-      <c r="E33">
+      <c r="D33" s="24">
+        <v>0.93</v>
+      </c>
+      <c r="E33" s="22">
+        <v>0.92</v>
+      </c>
+      <c r="F33" s="22">
         <v>0.94</v>
       </c>
-      <c r="G33">
-        <v>0.25</v>
-      </c>
-      <c r="H33" s="5"/>
+      <c r="G33" s="22">
+        <v>0.46</v>
+      </c>
+      <c r="H33" s="5">
+        <v>0.67</v>
+      </c>
       <c r="J33">
-        <v>0.66</v>
+        <v>0.75</v>
       </c>
       <c r="M33" s="6"/>
     </row>
     <row r="34" spans="1:13">
-      <c r="A34" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="B34" s="19" t="s">
-        <v>69</v>
+      <c r="A34" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="B34" s="18" t="s">
+        <v>67</v>
       </c>
       <c r="C34" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D34" s="11">
+      <c r="D34" s="24">
+        <v>0.82</v>
+      </c>
+      <c r="E34" s="22">
+        <v>0.94</v>
+      </c>
+      <c r="F34" s="22">
+        <v>1</v>
+      </c>
+      <c r="G34" s="22">
+        <v>0.25</v>
+      </c>
+      <c r="H34" s="5">
+        <v>0.12</v>
+      </c>
+      <c r="J34">
+        <v>0.66</v>
+      </c>
+      <c r="M34" s="6"/>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D35" s="24">
         <v>0.62</v>
       </c>
-      <c r="E34">
+      <c r="E35" s="22">
         <v>0.96</v>
       </c>
-      <c r="G34">
+      <c r="F35" s="22">
+        <v>1</v>
+      </c>
+      <c r="G35" s="22">
         <v>0.46</v>
       </c>
-      <c r="H34" s="5"/>
-      <c r="J34">
+      <c r="H35" s="5">
+        <v>0.67</v>
+      </c>
+      <c r="J35">
         <v>0.82</v>
-      </c>
-      <c r="M34" s="6"/>
-    </row>
-    <row r="35" spans="1:13" ht="20">
-      <c r="A35" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="B35" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C35" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="D35" s="18">
-        <v>0.93</v>
-      </c>
-      <c r="E35">
-        <v>0.97</v>
-      </c>
-      <c r="G35">
-        <v>0.53</v>
-      </c>
-      <c r="H35" s="5"/>
-      <c r="J35">
-        <v>0.6</v>
       </c>
       <c r="M35" s="6"/>
     </row>
     <row r="36" spans="1:13" ht="20">
       <c r="A36" s="12" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C36" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="D36" s="18">
+      <c r="D36" s="23">
         <v>0.93</v>
       </c>
-      <c r="E36">
-        <v>0.96</v>
-      </c>
-      <c r="G36">
-        <v>0.51</v>
+      <c r="E36" s="22">
+        <v>0.97</v>
+      </c>
+      <c r="G36" s="22">
+        <v>0.53</v>
       </c>
       <c r="H36" s="5"/>
       <c r="J36">
+        <v>0.6</v>
+      </c>
+      <c r="M36" s="6"/>
+    </row>
+    <row r="37" spans="1:13" ht="20">
+      <c r="A37" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D37" s="23">
+        <v>0.93</v>
+      </c>
+      <c r="E37" s="22">
+        <v>0.96</v>
+      </c>
+      <c r="G37" s="22">
+        <v>0.51</v>
+      </c>
+      <c r="H37" s="5"/>
+      <c r="J37">
         <v>0.73</v>
       </c>
-      <c r="M36" s="6"/>
-    </row>
-    <row r="37" spans="1:13" ht="20">
-      <c r="A37" s="15" t="s">
+      <c r="M37" s="6"/>
+    </row>
+    <row r="38" spans="1:13" ht="20">
+      <c r="A38" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="B38" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C37" s="16" t="s">
+      <c r="C38" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="D37" s="18">
+      <c r="D38" s="23">
         <v>0.91</v>
       </c>
-      <c r="E37">
+      <c r="E38" s="22">
         <v>0.93</v>
       </c>
-      <c r="G37">
+      <c r="G38" s="22">
         <v>0.67</v>
       </c>
-      <c r="J37">
+      <c r="J38">
         <v>0.75</v>
       </c>
-      <c r="M37" s="6"/>
-    </row>
-    <row r="38" spans="1:13" ht="20">
-      <c r="A38" s="12" t="s">
+      <c r="M38" s="6"/>
+    </row>
+    <row r="39" spans="1:13" ht="20">
+      <c r="A39" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="B38" s="12" t="s">
+      <c r="B39" s="12" t="s">
         <v>82</v>
-      </c>
-      <c r="C38" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="D38" s="18">
-        <v>0.75</v>
-      </c>
-      <c r="E38">
-        <v>0.91</v>
-      </c>
-      <c r="G38">
-        <v>0.37</v>
-      </c>
-      <c r="H38" s="5"/>
-      <c r="J38">
-        <v>0.61</v>
-      </c>
-      <c r="M38" s="6"/>
-    </row>
-    <row r="39" spans="1:13" ht="20">
-      <c r="A39" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="B39" s="14" t="s">
-        <v>84</v>
       </c>
       <c r="C39" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="D39" s="18">
-        <v>0.87</v>
-      </c>
-      <c r="E39">
-        <v>0.87</v>
-      </c>
-      <c r="G39">
-        <v>0.11</v>
+      <c r="D39" s="23">
+        <v>0.75</v>
+      </c>
+      <c r="E39" s="22">
+        <v>0.91</v>
+      </c>
+      <c r="G39" s="22">
+        <v>0.37</v>
       </c>
       <c r="H39" s="5"/>
       <c r="J39">
+        <v>0.61</v>
+      </c>
+      <c r="M39" s="6"/>
+    </row>
+    <row r="40" spans="1:13" ht="20">
+      <c r="A40" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D40" s="23">
+        <v>0.87</v>
+      </c>
+      <c r="E40" s="22">
+        <v>0.87</v>
+      </c>
+      <c r="G40" s="22">
+        <v>0.11</v>
+      </c>
+      <c r="H40" s="5"/>
+      <c r="J40">
         <v>0.57999999999999996</v>
       </c>
-      <c r="M39" s="6"/>
-    </row>
-    <row r="40" spans="1:13" ht="20">
-      <c r="A40" s="15" t="s">
+      <c r="M40" s="6"/>
+    </row>
+    <row r="41" spans="1:13" ht="20">
+      <c r="A41" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="B40" s="15" t="s">
+      <c r="B41" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="C40" s="16" t="s">
+      <c r="C41" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="D40" s="18">
+      <c r="D41" s="23">
         <v>0.89</v>
       </c>
-      <c r="E40">
+      <c r="E41" s="22">
         <v>0.98</v>
       </c>
-      <c r="G40">
+      <c r="G41" s="22">
         <v>0.28000000000000003</v>
       </c>
-      <c r="J40">
+      <c r="J41">
         <v>0.82</v>
       </c>
-      <c r="M40" s="6"/>
-    </row>
-    <row r="41" spans="1:13" ht="21">
-      <c r="A41" s="17" t="s">
+      <c r="M41" s="6"/>
+    </row>
+    <row r="42" spans="1:13" ht="21">
+      <c r="A42" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="B41" s="17" t="s">
+      <c r="B42" s="17" t="s">
         <v>88</v>
-      </c>
-      <c r="C41" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="D41" s="18">
-        <v>0.47</v>
-      </c>
-      <c r="E41">
-        <v>0.8</v>
-      </c>
-      <c r="G41">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="H41" s="5"/>
-      <c r="J41">
-        <v>0.66</v>
-      </c>
-      <c r="M41" s="6"/>
-    </row>
-    <row r="42" spans="1:13" ht="20">
-      <c r="A42" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="B42" s="14" t="s">
-        <v>90</v>
       </c>
       <c r="C42" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="D42" s="18">
-        <v>0.94</v>
-      </c>
-      <c r="E42">
-        <v>0.96</v>
-      </c>
-      <c r="G42">
-        <v>0.49</v>
+      <c r="D42" s="23">
+        <v>0.47</v>
+      </c>
+      <c r="E42" s="22">
+        <v>0.8</v>
+      </c>
+      <c r="G42" s="22">
+        <v>0.28000000000000003</v>
       </c>
       <c r="H42" s="5"/>
       <c r="J42">
+        <v>0.66</v>
+      </c>
+      <c r="M42" s="6"/>
+    </row>
+    <row r="43" spans="1:13" ht="20">
+      <c r="A43" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D43" s="23">
+        <v>0.94</v>
+      </c>
+      <c r="E43" s="22">
+        <v>0.96</v>
+      </c>
+      <c r="G43" s="22">
+        <v>0.49</v>
+      </c>
+      <c r="H43" s="5"/>
+      <c r="J43">
         <v>0.72</v>
       </c>
-      <c r="M42" s="6"/>
-    </row>
-    <row r="43" spans="1:13">
-      <c r="A43" s="7"/>
-      <c r="B43" s="7"/>
-      <c r="D43" s="4"/>
-      <c r="H43" s="5"/>
       <c r="M43" s="6"/>
     </row>
     <row r="44" spans="1:13">
       <c r="A44" s="7"/>
       <c r="B44" s="7"/>
-      <c r="D44" s="4"/>
+      <c r="D44" s="25"/>
       <c r="H44" s="5"/>
       <c r="M44" s="6"/>
     </row>
     <row r="45" spans="1:13">
       <c r="A45" s="9"/>
       <c r="B45" s="9"/>
-      <c r="D45" s="4"/>
+      <c r="D45" s="25"/>
       <c r="H45" s="5"/>
       <c r="M45" s="6"/>
     </row>
     <row r="46" spans="1:13">
       <c r="A46" s="9"/>
       <c r="B46" s="9"/>
-      <c r="D46" s="4"/>
+      <c r="D46" s="25"/>
       <c r="H46" s="5"/>
       <c r="M46" s="6"/>
     </row>
@@ -1965,7 +2179,7 @@
       <c r="A47" s="8"/>
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
+      <c r="D47" s="26"/>
       <c r="H47" s="5"/>
       <c r="M47" s="6"/>
     </row>
@@ -1973,7 +2187,7 @@
       <c r="A48" s="8"/>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
+      <c r="D48" s="26"/>
       <c r="H48" s="5"/>
       <c r="M48" s="6"/>
     </row>
@@ -1981,7 +2195,7 @@
       <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
+      <c r="D49" s="26"/>
       <c r="H49" s="5"/>
       <c r="M49" s="6"/>
     </row>
@@ -1989,7 +2203,7 @@
       <c r="A50" s="8"/>
       <c r="B50" s="8"/>
       <c r="C50" s="8"/>
-      <c r="D50" s="8"/>
+      <c r="D50" s="26"/>
       <c r="H50" s="5"/>
       <c r="M50" s="6"/>
     </row>
@@ -1997,7 +2211,7 @@
       <c r="A51" s="8"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
-      <c r="D51" s="8"/>
+      <c r="D51" s="26"/>
       <c r="H51" s="5"/>
       <c r="M51" s="6"/>
     </row>
@@ -2005,7 +2219,7 @@
       <c r="A52" s="8"/>
       <c r="B52" s="8"/>
       <c r="C52" s="8"/>
-      <c r="D52" s="8"/>
+      <c r="D52" s="26"/>
       <c r="H52" s="5"/>
       <c r="M52" s="6"/>
     </row>
@@ -2013,7 +2227,7 @@
       <c r="A53" s="8"/>
       <c r="B53" s="8"/>
       <c r="C53" s="8"/>
-      <c r="D53" s="8"/>
+      <c r="D53" s="26"/>
       <c r="H53" s="5"/>
       <c r="M53" s="6"/>
     </row>
@@ -2021,1209 +2235,1209 @@
       <c r="A54" s="8"/>
       <c r="B54" s="8"/>
       <c r="C54" s="8"/>
-      <c r="D54" s="8"/>
+      <c r="D54" s="26"/>
       <c r="M54" s="6"/>
     </row>
     <row r="55" spans="1:13">
       <c r="A55" s="8"/>
       <c r="B55" s="8"/>
       <c r="C55" s="8"/>
-      <c r="D55" s="8"/>
+      <c r="D55" s="26"/>
       <c r="M55" s="6"/>
     </row>
     <row r="56" spans="1:13">
       <c r="A56" s="8"/>
       <c r="B56" s="8"/>
       <c r="C56" s="8"/>
-      <c r="D56" s="8"/>
+      <c r="D56" s="26"/>
       <c r="M56" s="6"/>
     </row>
     <row r="57" spans="1:13">
       <c r="A57" s="8"/>
       <c r="B57" s="8"/>
       <c r="C57" s="8"/>
-      <c r="D57" s="8"/>
+      <c r="D57" s="26"/>
       <c r="M57" s="6"/>
     </row>
     <row r="58" spans="1:13">
       <c r="A58" s="8"/>
       <c r="B58" s="8"/>
       <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
+      <c r="D58" s="26"/>
       <c r="M58" s="6"/>
     </row>
     <row r="59" spans="1:13">
       <c r="A59" s="8"/>
       <c r="B59" s="8"/>
       <c r="C59" s="8"/>
-      <c r="D59" s="8"/>
+      <c r="D59" s="26"/>
       <c r="M59" s="6"/>
     </row>
     <row r="60" spans="1:13">
       <c r="A60" s="8"/>
       <c r="B60" s="8"/>
       <c r="C60" s="8"/>
-      <c r="D60" s="8"/>
+      <c r="D60" s="26"/>
       <c r="M60" s="6"/>
     </row>
     <row r="61" spans="1:13">
       <c r="A61" s="8"/>
       <c r="B61" s="8"/>
       <c r="C61" s="8"/>
-      <c r="D61" s="8"/>
+      <c r="D61" s="26"/>
       <c r="M61" s="6"/>
     </row>
     <row r="62" spans="1:13">
       <c r="A62" s="8"/>
       <c r="B62" s="8"/>
       <c r="C62" s="8"/>
-      <c r="D62" s="8"/>
+      <c r="D62" s="26"/>
       <c r="M62" s="6"/>
     </row>
     <row r="63" spans="1:13">
       <c r="A63" s="8"/>
       <c r="B63" s="8"/>
       <c r="C63" s="8"/>
-      <c r="D63" s="8"/>
+      <c r="D63" s="26"/>
       <c r="M63" s="6"/>
     </row>
     <row r="64" spans="1:13">
       <c r="A64" s="8"/>
       <c r="B64" s="8"/>
       <c r="C64" s="8"/>
-      <c r="D64" s="8"/>
+      <c r="D64" s="26"/>
       <c r="M64" s="6"/>
     </row>
     <row r="65" spans="1:13">
       <c r="A65" s="8"/>
       <c r="B65" s="8"/>
       <c r="C65" s="8"/>
-      <c r="D65" s="8"/>
+      <c r="D65" s="26"/>
       <c r="M65" s="6"/>
     </row>
     <row r="66" spans="1:13">
       <c r="A66" s="8"/>
       <c r="B66" s="8"/>
       <c r="C66" s="8"/>
-      <c r="D66" s="8"/>
+      <c r="D66" s="26"/>
       <c r="M66" s="6"/>
     </row>
     <row r="67" spans="1:13">
       <c r="A67" s="8"/>
       <c r="B67" s="8"/>
       <c r="C67" s="8"/>
-      <c r="D67" s="8"/>
+      <c r="D67" s="26"/>
       <c r="M67" s="6"/>
     </row>
     <row r="68" spans="1:13">
       <c r="A68" s="8"/>
       <c r="B68" s="8"/>
       <c r="C68" s="8"/>
-      <c r="D68" s="8"/>
+      <c r="D68" s="26"/>
       <c r="M68" s="6"/>
     </row>
     <row r="69" spans="1:13">
       <c r="A69" s="8"/>
       <c r="B69" s="8"/>
       <c r="C69" s="8"/>
-      <c r="D69" s="8"/>
+      <c r="D69" s="26"/>
       <c r="M69" s="6"/>
     </row>
     <row r="70" spans="1:13">
       <c r="A70" s="8"/>
       <c r="B70" s="8"/>
       <c r="C70" s="8"/>
-      <c r="D70" s="8"/>
+      <c r="D70" s="26"/>
       <c r="M70" s="6"/>
     </row>
     <row r="71" spans="1:13">
       <c r="A71" s="8"/>
       <c r="B71" s="8"/>
       <c r="C71" s="8"/>
-      <c r="D71" s="8"/>
+      <c r="D71" s="26"/>
       <c r="M71" s="6"/>
     </row>
     <row r="72" spans="1:13">
       <c r="A72" s="8"/>
       <c r="B72" s="8"/>
       <c r="C72" s="8"/>
-      <c r="D72" s="8"/>
+      <c r="D72" s="26"/>
       <c r="M72" s="6"/>
     </row>
     <row r="73" spans="1:13">
       <c r="A73" s="8"/>
       <c r="B73" s="8"/>
       <c r="C73" s="8"/>
-      <c r="D73" s="8"/>
+      <c r="D73" s="26"/>
       <c r="M73" s="6"/>
     </row>
     <row r="74" spans="1:13">
       <c r="A74" s="8"/>
       <c r="B74" s="8"/>
       <c r="C74" s="8"/>
-      <c r="D74" s="8"/>
+      <c r="D74" s="26"/>
       <c r="M74" s="6"/>
     </row>
     <row r="75" spans="1:13">
       <c r="A75" s="8"/>
       <c r="B75" s="8"/>
       <c r="C75" s="8"/>
-      <c r="D75" s="8"/>
+      <c r="D75" s="26"/>
       <c r="M75" s="6"/>
     </row>
     <row r="76" spans="1:13">
       <c r="A76" s="8"/>
       <c r="B76" s="8"/>
       <c r="C76" s="8"/>
-      <c r="D76" s="8"/>
+      <c r="D76" s="26"/>
       <c r="M76" s="6"/>
     </row>
     <row r="77" spans="1:13">
       <c r="A77" s="8"/>
       <c r="B77" s="8"/>
       <c r="C77" s="8"/>
-      <c r="D77" s="8"/>
+      <c r="D77" s="26"/>
       <c r="M77" s="6"/>
     </row>
     <row r="78" spans="1:13">
       <c r="A78" s="8"/>
       <c r="B78" s="8"/>
       <c r="C78" s="8"/>
-      <c r="D78" s="8"/>
+      <c r="D78" s="26"/>
       <c r="M78" s="6"/>
     </row>
     <row r="79" spans="1:13">
       <c r="A79" s="8"/>
       <c r="B79" s="8"/>
       <c r="C79" s="8"/>
-      <c r="D79" s="8"/>
+      <c r="D79" s="26"/>
       <c r="M79" s="6"/>
     </row>
     <row r="80" spans="1:13">
       <c r="A80" s="8"/>
       <c r="B80" s="8"/>
       <c r="C80" s="8"/>
-      <c r="D80" s="8"/>
+      <c r="D80" s="26"/>
       <c r="M80" s="6"/>
     </row>
     <row r="81" spans="1:13">
       <c r="B81" s="2"/>
-      <c r="D81" s="4"/>
+      <c r="D81" s="25"/>
       <c r="M81" s="6"/>
     </row>
     <row r="82" spans="1:13">
       <c r="A82" s="8"/>
       <c r="B82" s="8"/>
       <c r="C82" s="8"/>
-      <c r="D82" s="8"/>
+      <c r="D82" s="26"/>
       <c r="M82" s="6"/>
     </row>
     <row r="83" spans="1:13">
       <c r="A83" s="8"/>
       <c r="B83" s="8"/>
       <c r="C83" s="8"/>
-      <c r="D83" s="8"/>
+      <c r="D83" s="26"/>
       <c r="M83" s="6"/>
     </row>
     <row r="84" spans="1:13">
       <c r="A84" s="8"/>
       <c r="B84" s="8"/>
       <c r="C84" s="8"/>
-      <c r="D84" s="8"/>
+      <c r="D84" s="26"/>
       <c r="M84" s="6"/>
     </row>
     <row r="85" spans="1:13">
       <c r="A85" s="8"/>
       <c r="B85" s="8"/>
       <c r="C85" s="8"/>
-      <c r="D85" s="8"/>
+      <c r="D85" s="26"/>
       <c r="M85" s="6"/>
     </row>
     <row r="86" spans="1:13">
       <c r="A86" s="8"/>
       <c r="B86" s="8"/>
       <c r="C86" s="8"/>
-      <c r="D86" s="8"/>
+      <c r="D86" s="26"/>
       <c r="M86" s="6"/>
     </row>
     <row r="87" spans="1:13">
       <c r="A87" s="8"/>
       <c r="B87" s="8"/>
       <c r="C87" s="8"/>
-      <c r="D87" s="8"/>
+      <c r="D87" s="26"/>
       <c r="M87" s="6"/>
     </row>
     <row r="88" spans="1:13">
       <c r="A88" s="8"/>
       <c r="B88" s="8"/>
       <c r="C88" s="8"/>
-      <c r="D88" s="8"/>
+      <c r="D88" s="26"/>
       <c r="M88" s="6"/>
     </row>
     <row r="89" spans="1:13">
       <c r="A89" s="8"/>
       <c r="B89" s="8"/>
       <c r="C89" s="8"/>
-      <c r="D89" s="8"/>
+      <c r="D89" s="26"/>
       <c r="M89" s="6"/>
     </row>
     <row r="90" spans="1:13">
       <c r="A90" s="8"/>
       <c r="B90" s="8"/>
       <c r="C90" s="8"/>
-      <c r="D90" s="8"/>
+      <c r="D90" s="26"/>
       <c r="M90" s="6"/>
     </row>
     <row r="91" spans="1:13">
       <c r="A91" s="8"/>
       <c r="B91" s="8"/>
       <c r="C91" s="8"/>
-      <c r="D91" s="8"/>
+      <c r="D91" s="26"/>
       <c r="M91" s="6"/>
     </row>
     <row r="92" spans="1:13">
       <c r="A92" s="8"/>
       <c r="B92" s="8"/>
       <c r="C92" s="8"/>
-      <c r="D92" s="8"/>
+      <c r="D92" s="26"/>
       <c r="M92" s="6"/>
     </row>
     <row r="93" spans="1:13">
       <c r="A93" s="8"/>
       <c r="B93" s="8"/>
       <c r="C93" s="8"/>
-      <c r="D93" s="8"/>
+      <c r="D93" s="26"/>
       <c r="M93" s="6"/>
     </row>
     <row r="94" spans="1:13">
       <c r="A94" s="8"/>
       <c r="B94" s="8"/>
       <c r="C94" s="8"/>
-      <c r="D94" s="8"/>
+      <c r="D94" s="26"/>
       <c r="M94" s="6"/>
     </row>
     <row r="95" spans="1:13">
       <c r="A95" s="8"/>
       <c r="B95" s="8"/>
       <c r="C95" s="8"/>
-      <c r="D95" s="8"/>
+      <c r="D95" s="26"/>
       <c r="M95" s="6"/>
     </row>
     <row r="96" spans="1:13">
       <c r="A96" s="8"/>
       <c r="B96" s="8"/>
       <c r="C96" s="8"/>
-      <c r="D96" s="8"/>
+      <c r="D96" s="26"/>
       <c r="M96" s="6"/>
     </row>
     <row r="97" spans="1:13">
       <c r="A97" s="8"/>
       <c r="B97" s="8"/>
       <c r="C97" s="8"/>
-      <c r="D97" s="8"/>
+      <c r="D97" s="26"/>
       <c r="M97" s="6"/>
     </row>
     <row r="98" spans="1:13">
       <c r="A98" s="8"/>
       <c r="B98" s="8"/>
       <c r="C98" s="8"/>
-      <c r="D98" s="8"/>
+      <c r="D98" s="26"/>
       <c r="M98" s="6"/>
     </row>
     <row r="99" spans="1:13">
       <c r="A99" s="8"/>
       <c r="B99" s="8"/>
       <c r="C99" s="8"/>
-      <c r="D99" s="8"/>
+      <c r="D99" s="26"/>
       <c r="M99" s="6"/>
     </row>
     <row r="100" spans="1:13">
       <c r="A100" s="8"/>
       <c r="B100" s="8"/>
       <c r="C100" s="8"/>
-      <c r="D100" s="8"/>
+      <c r="D100" s="26"/>
       <c r="M100" s="6"/>
     </row>
     <row r="101" spans="1:13">
       <c r="A101" s="8"/>
       <c r="B101" s="8"/>
       <c r="C101" s="8"/>
-      <c r="D101" s="8"/>
+      <c r="D101" s="26"/>
       <c r="M101" s="6"/>
     </row>
     <row r="102" spans="1:13">
       <c r="A102" s="8"/>
       <c r="B102" s="8"/>
       <c r="C102" s="8"/>
-      <c r="D102" s="8"/>
+      <c r="D102" s="26"/>
       <c r="M102" s="6"/>
     </row>
     <row r="103" spans="1:13">
       <c r="A103" s="8"/>
       <c r="B103" s="8"/>
       <c r="C103" s="8"/>
-      <c r="D103" s="8"/>
+      <c r="D103" s="26"/>
       <c r="M103" s="6"/>
     </row>
     <row r="104" spans="1:13">
       <c r="A104" s="8"/>
       <c r="B104" s="8"/>
       <c r="C104" s="8"/>
-      <c r="D104" s="8"/>
+      <c r="D104" s="26"/>
       <c r="M104" s="6"/>
     </row>
     <row r="105" spans="1:13">
       <c r="A105" s="8"/>
       <c r="B105" s="8"/>
       <c r="C105" s="8"/>
-      <c r="D105" s="8"/>
+      <c r="D105" s="26"/>
       <c r="M105" s="6"/>
     </row>
     <row r="106" spans="1:13">
       <c r="A106" s="8"/>
       <c r="B106" s="8"/>
       <c r="C106" s="8"/>
-      <c r="D106" s="8"/>
+      <c r="D106" s="26"/>
       <c r="M106" s="6"/>
     </row>
     <row r="107" spans="1:13">
       <c r="A107" s="8"/>
       <c r="B107" s="8"/>
       <c r="C107" s="8"/>
-      <c r="D107" s="8"/>
+      <c r="D107" s="26"/>
       <c r="M107" s="6"/>
     </row>
     <row r="108" spans="1:13">
       <c r="A108" s="8"/>
       <c r="B108" s="8"/>
       <c r="C108" s="8"/>
-      <c r="D108" s="8"/>
+      <c r="D108" s="26"/>
       <c r="M108" s="6"/>
     </row>
     <row r="109" spans="1:13">
       <c r="A109" s="8"/>
       <c r="B109" s="8"/>
       <c r="C109" s="8"/>
-      <c r="D109" s="8"/>
+      <c r="D109" s="26"/>
       <c r="M109" s="6"/>
     </row>
     <row r="110" spans="1:13">
       <c r="A110" s="8"/>
       <c r="B110" s="8"/>
       <c r="C110" s="8"/>
-      <c r="D110" s="8"/>
+      <c r="D110" s="26"/>
       <c r="M110" s="6"/>
     </row>
     <row r="111" spans="1:13">
       <c r="A111" s="8"/>
       <c r="B111" s="8"/>
       <c r="C111" s="8"/>
-      <c r="D111" s="8"/>
+      <c r="D111" s="26"/>
       <c r="M111" s="6"/>
     </row>
     <row r="112" spans="1:13">
       <c r="A112" s="8"/>
       <c r="B112" s="8"/>
       <c r="C112" s="8"/>
-      <c r="D112" s="8"/>
+      <c r="D112" s="26"/>
       <c r="M112" s="6"/>
     </row>
     <row r="113" spans="1:13">
       <c r="A113" s="8"/>
       <c r="B113" s="8"/>
       <c r="C113" s="8"/>
-      <c r="D113" s="8"/>
+      <c r="D113" s="26"/>
       <c r="M113" s="6"/>
     </row>
     <row r="114" spans="1:13">
       <c r="A114" s="8"/>
       <c r="B114" s="8"/>
       <c r="C114" s="8"/>
-      <c r="D114" s="8"/>
+      <c r="D114" s="26"/>
       <c r="M114" s="6"/>
     </row>
     <row r="115" spans="1:13">
       <c r="A115" s="8"/>
       <c r="B115" s="8"/>
       <c r="C115" s="8"/>
-      <c r="D115" s="8"/>
+      <c r="D115" s="26"/>
       <c r="M115" s="6"/>
     </row>
     <row r="116" spans="1:13">
       <c r="A116" s="8"/>
       <c r="B116" s="8"/>
       <c r="C116" s="8"/>
-      <c r="D116" s="8"/>
+      <c r="D116" s="26"/>
       <c r="M116" s="6"/>
     </row>
     <row r="117" spans="1:13">
       <c r="A117" s="8"/>
       <c r="B117" s="8"/>
       <c r="C117" s="8"/>
-      <c r="D117" s="8"/>
+      <c r="D117" s="26"/>
       <c r="M117" s="6"/>
     </row>
     <row r="118" spans="1:13">
       <c r="A118" s="8"/>
       <c r="B118" s="8"/>
       <c r="C118" s="8"/>
-      <c r="D118" s="8"/>
+      <c r="D118" s="26"/>
       <c r="M118" s="6"/>
     </row>
     <row r="119" spans="1:13">
       <c r="A119" s="8"/>
       <c r="B119" s="8"/>
       <c r="C119" s="8"/>
-      <c r="D119" s="8"/>
+      <c r="D119" s="26"/>
       <c r="M119" s="6"/>
     </row>
     <row r="120" spans="1:13">
       <c r="A120" s="8"/>
       <c r="B120" s="8"/>
       <c r="C120" s="8"/>
-      <c r="D120" s="8"/>
+      <c r="D120" s="26"/>
       <c r="M120" s="6"/>
     </row>
     <row r="121" spans="1:13">
       <c r="A121" s="8"/>
       <c r="B121" s="8"/>
       <c r="C121" s="8"/>
-      <c r="D121" s="8"/>
+      <c r="D121" s="26"/>
       <c r="M121" s="6"/>
     </row>
     <row r="122" spans="1:13">
       <c r="A122" s="8"/>
       <c r="B122" s="8"/>
       <c r="C122" s="8"/>
-      <c r="D122" s="8"/>
+      <c r="D122" s="26"/>
       <c r="M122" s="6"/>
     </row>
     <row r="123" spans="1:13">
       <c r="A123" s="8"/>
       <c r="B123" s="8"/>
       <c r="C123" s="8"/>
-      <c r="D123" s="8"/>
+      <c r="D123" s="26"/>
       <c r="M123" s="6"/>
     </row>
     <row r="124" spans="1:13">
       <c r="A124" s="8"/>
       <c r="B124" s="8"/>
       <c r="C124" s="8"/>
-      <c r="D124" s="8"/>
+      <c r="D124" s="26"/>
       <c r="M124" s="6"/>
     </row>
     <row r="125" spans="1:13">
       <c r="A125" s="8"/>
       <c r="B125" s="8"/>
       <c r="C125" s="8"/>
-      <c r="D125" s="8"/>
+      <c r="D125" s="26"/>
       <c r="M125" s="6"/>
     </row>
     <row r="126" spans="1:13">
       <c r="A126" s="8"/>
       <c r="B126" s="8"/>
       <c r="C126" s="8"/>
-      <c r="D126" s="8"/>
+      <c r="D126" s="26"/>
       <c r="M126" s="6"/>
     </row>
     <row r="127" spans="1:13">
       <c r="A127" s="8"/>
       <c r="B127" s="8"/>
       <c r="C127" s="8"/>
-      <c r="D127" s="8"/>
+      <c r="D127" s="26"/>
       <c r="M127" s="6"/>
     </row>
     <row r="128" spans="1:13">
       <c r="A128" s="8"/>
       <c r="B128" s="8"/>
       <c r="C128" s="8"/>
-      <c r="D128" s="8"/>
+      <c r="D128" s="26"/>
       <c r="M128" s="6"/>
     </row>
     <row r="129" spans="1:13">
       <c r="A129" s="8"/>
       <c r="B129" s="8"/>
       <c r="C129" s="8"/>
-      <c r="D129" s="8"/>
+      <c r="D129" s="26"/>
       <c r="M129" s="6"/>
     </row>
     <row r="130" spans="1:13">
       <c r="A130" s="8"/>
       <c r="B130" s="8"/>
       <c r="C130" s="8"/>
-      <c r="D130" s="8"/>
+      <c r="D130" s="26"/>
       <c r="M130" s="6"/>
     </row>
     <row r="131" spans="1:13">
       <c r="A131" s="8"/>
       <c r="B131" s="8"/>
       <c r="C131" s="8"/>
-      <c r="D131" s="8"/>
+      <c r="D131" s="26"/>
       <c r="M131" s="6"/>
     </row>
     <row r="132" spans="1:13">
       <c r="A132" s="8"/>
       <c r="B132" s="8"/>
       <c r="C132" s="8"/>
-      <c r="D132" s="8"/>
+      <c r="D132" s="26"/>
       <c r="M132" s="6"/>
     </row>
     <row r="133" spans="1:13">
       <c r="A133" s="8"/>
       <c r="B133" s="8"/>
       <c r="C133" s="8"/>
-      <c r="D133" s="8"/>
+      <c r="D133" s="26"/>
       <c r="M133" s="6"/>
     </row>
     <row r="134" spans="1:13">
       <c r="A134" s="8"/>
       <c r="B134" s="8"/>
       <c r="C134" s="8"/>
-      <c r="D134" s="8"/>
+      <c r="D134" s="26"/>
       <c r="M134" s="6"/>
     </row>
     <row r="135" spans="1:13">
       <c r="A135" s="8"/>
       <c r="B135" s="8"/>
       <c r="C135" s="8"/>
-      <c r="D135" s="8"/>
+      <c r="D135" s="26"/>
       <c r="M135" s="6"/>
     </row>
     <row r="136" spans="1:13">
       <c r="A136" s="8"/>
       <c r="B136" s="8"/>
       <c r="C136" s="8"/>
-      <c r="D136" s="8"/>
+      <c r="D136" s="26"/>
       <c r="M136" s="6"/>
     </row>
     <row r="137" spans="1:13">
       <c r="A137" s="8"/>
       <c r="B137" s="8"/>
       <c r="C137" s="8"/>
-      <c r="D137" s="8"/>
+      <c r="D137" s="26"/>
       <c r="M137" s="6"/>
     </row>
     <row r="138" spans="1:13">
       <c r="A138" s="8"/>
       <c r="B138" s="8"/>
       <c r="C138" s="8"/>
-      <c r="D138" s="8"/>
+      <c r="D138" s="26"/>
       <c r="M138" s="6"/>
     </row>
     <row r="139" spans="1:13">
       <c r="A139" s="8"/>
       <c r="B139" s="8"/>
       <c r="C139" s="8"/>
-      <c r="D139" s="8"/>
+      <c r="D139" s="26"/>
       <c r="M139" s="6"/>
     </row>
     <row r="140" spans="1:13">
       <c r="A140" s="8"/>
       <c r="B140" s="8"/>
       <c r="C140" s="8"/>
-      <c r="D140" s="8"/>
+      <c r="D140" s="26"/>
       <c r="M140" s="6"/>
     </row>
     <row r="141" spans="1:13">
       <c r="A141" s="8"/>
       <c r="B141" s="8"/>
       <c r="C141" s="8"/>
-      <c r="D141" s="8"/>
+      <c r="D141" s="26"/>
       <c r="M141" s="6"/>
     </row>
     <row r="142" spans="1:13">
       <c r="A142" s="8"/>
       <c r="B142" s="8"/>
       <c r="C142" s="8"/>
-      <c r="D142" s="8"/>
+      <c r="D142" s="26"/>
       <c r="M142" s="6"/>
     </row>
     <row r="143" spans="1:13">
       <c r="A143" s="8"/>
       <c r="B143" s="8"/>
       <c r="C143" s="8"/>
-      <c r="D143" s="8"/>
+      <c r="D143" s="26"/>
       <c r="M143" s="6"/>
     </row>
     <row r="144" spans="1:13">
       <c r="A144" s="8"/>
       <c r="B144" s="8"/>
       <c r="C144" s="8"/>
-      <c r="D144" s="8"/>
+      <c r="D144" s="26"/>
       <c r="M144" s="6"/>
     </row>
     <row r="145" spans="1:13">
       <c r="A145" s="8"/>
       <c r="B145" s="8"/>
       <c r="C145" s="8"/>
-      <c r="D145" s="8"/>
+      <c r="D145" s="26"/>
       <c r="M145" s="6"/>
     </row>
     <row r="146" spans="1:13">
       <c r="A146" s="8"/>
       <c r="B146" s="8"/>
       <c r="C146" s="8"/>
-      <c r="D146" s="8"/>
+      <c r="D146" s="26"/>
       <c r="M146" s="6"/>
     </row>
     <row r="147" spans="1:13">
       <c r="A147" s="8"/>
       <c r="B147" s="8"/>
       <c r="C147" s="8"/>
-      <c r="D147" s="8"/>
+      <c r="D147" s="26"/>
       <c r="M147" s="6"/>
     </row>
     <row r="148" spans="1:13">
       <c r="A148" s="8"/>
       <c r="B148" s="8"/>
       <c r="C148" s="8"/>
-      <c r="D148" s="8"/>
+      <c r="D148" s="26"/>
       <c r="M148" s="6"/>
     </row>
     <row r="149" spans="1:13">
       <c r="A149" s="8"/>
       <c r="B149" s="8"/>
       <c r="C149" s="8"/>
-      <c r="D149" s="8"/>
+      <c r="D149" s="26"/>
       <c r="M149" s="6"/>
     </row>
     <row r="150" spans="1:13">
       <c r="A150" s="8"/>
       <c r="B150" s="8"/>
       <c r="C150" s="8"/>
-      <c r="D150" s="8"/>
+      <c r="D150" s="26"/>
       <c r="M150" s="6"/>
     </row>
     <row r="151" spans="1:13">
       <c r="A151" s="8"/>
       <c r="B151" s="8"/>
       <c r="C151" s="8"/>
-      <c r="D151" s="8"/>
+      <c r="D151" s="26"/>
       <c r="M151" s="6"/>
     </row>
     <row r="152" spans="1:13">
       <c r="A152" s="8"/>
       <c r="B152" s="8"/>
       <c r="C152" s="8"/>
-      <c r="D152" s="8"/>
+      <c r="D152" s="26"/>
       <c r="M152" s="6"/>
     </row>
     <row r="153" spans="1:13">
       <c r="A153" s="8"/>
       <c r="B153" s="8"/>
       <c r="C153" s="8"/>
-      <c r="D153" s="8"/>
+      <c r="D153" s="26"/>
       <c r="M153" s="6"/>
     </row>
     <row r="154" spans="1:13">
       <c r="A154" s="8"/>
       <c r="B154" s="8"/>
       <c r="C154" s="8"/>
-      <c r="D154" s="8"/>
+      <c r="D154" s="26"/>
       <c r="M154" s="6"/>
     </row>
     <row r="155" spans="1:13">
       <c r="A155" s="8"/>
       <c r="B155" s="8"/>
       <c r="C155" s="8"/>
-      <c r="D155" s="8"/>
+      <c r="D155" s="26"/>
       <c r="M155" s="6"/>
     </row>
     <row r="156" spans="1:13">
       <c r="A156" s="8"/>
       <c r="B156" s="8"/>
       <c r="C156" s="8"/>
-      <c r="D156" s="8"/>
+      <c r="D156" s="26"/>
       <c r="M156" s="6"/>
     </row>
     <row r="157" spans="1:13">
       <c r="A157" s="8"/>
       <c r="B157" s="8"/>
       <c r="C157" s="8"/>
-      <c r="D157" s="8"/>
+      <c r="D157" s="26"/>
       <c r="M157" s="6"/>
     </row>
     <row r="158" spans="1:13">
       <c r="A158" s="8"/>
       <c r="B158" s="8"/>
       <c r="C158" s="8"/>
-      <c r="D158" s="8"/>
+      <c r="D158" s="26"/>
       <c r="M158" s="6"/>
     </row>
     <row r="159" spans="1:13">
       <c r="A159" s="8"/>
       <c r="B159" s="8"/>
       <c r="C159" s="8"/>
-      <c r="D159" s="8"/>
+      <c r="D159" s="26"/>
       <c r="M159" s="6"/>
     </row>
     <row r="160" spans="1:13">
       <c r="A160" s="8"/>
       <c r="B160" s="8"/>
       <c r="C160" s="8"/>
-      <c r="D160" s="8"/>
+      <c r="D160" s="26"/>
       <c r="M160" s="6"/>
     </row>
     <row r="161" spans="1:13">
       <c r="A161" s="8"/>
       <c r="B161" s="8"/>
       <c r="C161" s="8"/>
-      <c r="D161" s="8"/>
+      <c r="D161" s="26"/>
       <c r="M161" s="6"/>
     </row>
     <row r="162" spans="1:13">
       <c r="A162" s="8"/>
       <c r="B162" s="8"/>
       <c r="C162" s="8"/>
-      <c r="D162" s="8"/>
+      <c r="D162" s="26"/>
       <c r="M162" s="6"/>
     </row>
     <row r="163" spans="1:13">
       <c r="A163" s="8"/>
       <c r="B163" s="8"/>
       <c r="C163" s="8"/>
-      <c r="D163" s="8"/>
+      <c r="D163" s="26"/>
       <c r="M163" s="6"/>
     </row>
     <row r="164" spans="1:13">
       <c r="A164" s="8"/>
       <c r="B164" s="8"/>
       <c r="C164" s="8"/>
-      <c r="D164" s="8"/>
+      <c r="D164" s="26"/>
       <c r="M164" s="6"/>
     </row>
     <row r="165" spans="1:13">
       <c r="A165" s="8"/>
       <c r="B165" s="8"/>
       <c r="C165" s="8"/>
-      <c r="D165" s="8"/>
+      <c r="D165" s="26"/>
       <c r="M165" s="6"/>
     </row>
     <row r="166" spans="1:13">
       <c r="A166" s="8"/>
       <c r="B166" s="8"/>
       <c r="C166" s="8"/>
-      <c r="D166" s="8"/>
+      <c r="D166" s="26"/>
       <c r="M166" s="6"/>
     </row>
     <row r="167" spans="1:13">
       <c r="B167" s="3"/>
-      <c r="D167" s="4"/>
+      <c r="D167" s="25"/>
       <c r="M167" s="6"/>
     </row>
     <row r="168" spans="1:13">
       <c r="A168" s="8"/>
       <c r="B168" s="8"/>
       <c r="C168" s="8"/>
-      <c r="D168" s="8"/>
+      <c r="D168" s="26"/>
       <c r="M168" s="6"/>
     </row>
     <row r="169" spans="1:13">
       <c r="B169" s="3"/>
-      <c r="D169" s="4"/>
+      <c r="D169" s="25"/>
       <c r="M169" s="6"/>
     </row>
     <row r="170" spans="1:13">
       <c r="A170" s="8"/>
       <c r="B170" s="8"/>
       <c r="C170" s="8"/>
-      <c r="D170" s="8"/>
+      <c r="D170" s="26"/>
       <c r="M170" s="6"/>
     </row>
     <row r="171" spans="1:13">
       <c r="A171" s="8"/>
       <c r="B171" s="8"/>
       <c r="C171" s="8"/>
-      <c r="D171" s="8"/>
+      <c r="D171" s="26"/>
       <c r="M171" s="6"/>
     </row>
     <row r="172" spans="1:13">
       <c r="A172" s="8"/>
       <c r="B172" s="8"/>
       <c r="C172" s="8"/>
-      <c r="D172" s="8"/>
+      <c r="D172" s="26"/>
       <c r="M172" s="6"/>
     </row>
     <row r="173" spans="1:13">
       <c r="A173" s="8"/>
       <c r="B173" s="8"/>
       <c r="C173" s="8"/>
-      <c r="D173" s="8"/>
+      <c r="D173" s="26"/>
       <c r="M173" s="6"/>
     </row>
     <row r="174" spans="1:13">
       <c r="A174" s="8"/>
       <c r="B174" s="8"/>
       <c r="C174" s="8"/>
-      <c r="D174" s="8"/>
+      <c r="D174" s="26"/>
       <c r="M174" s="6"/>
     </row>
     <row r="175" spans="1:13">
       <c r="A175" s="8"/>
       <c r="B175" s="8"/>
       <c r="C175" s="8"/>
-      <c r="D175" s="8"/>
+      <c r="D175" s="26"/>
       <c r="M175" s="6"/>
     </row>
     <row r="176" spans="1:13">
       <c r="A176" s="8"/>
       <c r="B176" s="8"/>
       <c r="C176" s="8"/>
-      <c r="D176" s="8"/>
+      <c r="D176" s="26"/>
       <c r="M176" s="6"/>
     </row>
     <row r="177" spans="1:13">
       <c r="A177" s="8"/>
       <c r="B177" s="8"/>
       <c r="C177" s="8"/>
-      <c r="D177" s="8"/>
+      <c r="D177" s="26"/>
       <c r="M177" s="6"/>
     </row>
     <row r="178" spans="1:13">
       <c r="A178" s="8"/>
       <c r="B178" s="8"/>
       <c r="C178" s="8"/>
-      <c r="D178" s="8"/>
+      <c r="D178" s="26"/>
       <c r="M178" s="6"/>
     </row>
     <row r="179" spans="1:13">
       <c r="B179" s="3"/>
-      <c r="D179" s="4"/>
+      <c r="D179" s="25"/>
       <c r="M179" s="6"/>
     </row>
     <row r="180" spans="1:13">
       <c r="A180" s="8"/>
       <c r="B180" s="8"/>
       <c r="C180" s="8"/>
-      <c r="D180" s="8"/>
+      <c r="D180" s="26"/>
       <c r="M180" s="6"/>
     </row>
     <row r="181" spans="1:13">
       <c r="A181" s="8"/>
       <c r="B181" s="8"/>
       <c r="C181" s="8"/>
-      <c r="D181" s="8"/>
+      <c r="D181" s="26"/>
       <c r="M181" s="6"/>
     </row>
     <row r="182" spans="1:13">
       <c r="A182" s="8"/>
       <c r="B182" s="8"/>
       <c r="C182" s="8"/>
-      <c r="D182" s="8"/>
+      <c r="D182" s="26"/>
       <c r="M182" s="6"/>
     </row>
     <row r="183" spans="1:13">
       <c r="A183" s="8"/>
       <c r="B183" s="8"/>
       <c r="C183" s="8"/>
-      <c r="D183" s="8"/>
+      <c r="D183" s="26"/>
       <c r="M183" s="6"/>
     </row>
     <row r="184" spans="1:13">
       <c r="A184" s="8"/>
       <c r="B184" s="8"/>
       <c r="C184" s="8"/>
-      <c r="D184" s="8"/>
+      <c r="D184" s="26"/>
       <c r="M184" s="6"/>
     </row>
     <row r="185" spans="1:13">
       <c r="A185" s="8"/>
       <c r="B185" s="8"/>
       <c r="C185" s="8"/>
-      <c r="D185" s="8"/>
+      <c r="D185" s="26"/>
       <c r="M185" s="6"/>
     </row>
     <row r="186" spans="1:13">
       <c r="A186" s="8"/>
       <c r="B186" s="8"/>
       <c r="C186" s="8"/>
-      <c r="D186" s="8"/>
+      <c r="D186" s="26"/>
       <c r="M186" s="6"/>
     </row>
     <row r="187" spans="1:13">
       <c r="A187" s="8"/>
       <c r="B187" s="8"/>
       <c r="C187" s="8"/>
-      <c r="D187" s="8"/>
+      <c r="D187" s="26"/>
       <c r="M187" s="6"/>
     </row>
     <row r="188" spans="1:13">
       <c r="B188" s="2"/>
-      <c r="D188" s="4"/>
+      <c r="D188" s="25"/>
       <c r="M188" s="6"/>
     </row>
     <row r="189" spans="1:13">
       <c r="A189" s="8"/>
       <c r="B189" s="8"/>
       <c r="C189" s="8"/>
-      <c r="D189" s="8"/>
+      <c r="D189" s="26"/>
       <c r="M189" s="6"/>
     </row>
     <row r="190" spans="1:13">
       <c r="A190" s="8"/>
       <c r="B190" s="8"/>
       <c r="C190" s="8"/>
-      <c r="D190" s="8"/>
+      <c r="D190" s="26"/>
       <c r="M190" s="6"/>
     </row>
     <row r="191" spans="1:13">
       <c r="A191" s="8"/>
       <c r="B191" s="8"/>
       <c r="C191" s="8"/>
-      <c r="D191" s="8"/>
+      <c r="D191" s="26"/>
       <c r="M191" s="6"/>
     </row>
     <row r="192" spans="1:13">
       <c r="A192" s="8"/>
       <c r="B192" s="8"/>
       <c r="C192" s="8"/>
-      <c r="D192" s="8"/>
+      <c r="D192" s="26"/>
       <c r="M192" s="6"/>
     </row>
     <row r="193" spans="1:13">
       <c r="A193" s="8"/>
       <c r="B193" s="8"/>
       <c r="C193" s="8"/>
-      <c r="D193" s="8"/>
+      <c r="D193" s="26"/>
       <c r="M193" s="6"/>
     </row>
     <row r="194" spans="1:13">
       <c r="A194" s="8"/>
       <c r="B194" s="8"/>
       <c r="C194" s="8"/>
-      <c r="D194" s="8"/>
+      <c r="D194" s="26"/>
       <c r="M194" s="6"/>
     </row>
     <row r="195" spans="1:13">
       <c r="A195" s="8"/>
       <c r="B195" s="8"/>
       <c r="C195" s="8"/>
-      <c r="D195" s="8"/>
+      <c r="D195" s="26"/>
       <c r="M195" s="6"/>
     </row>
     <row r="196" spans="1:13">
       <c r="A196" s="8"/>
       <c r="B196" s="8"/>
       <c r="C196" s="8"/>
-      <c r="D196" s="8"/>
+      <c r="D196" s="26"/>
       <c r="M196" s="6"/>
     </row>
     <row r="197" spans="1:13">
       <c r="A197" s="8"/>
       <c r="B197" s="8"/>
       <c r="C197" s="8"/>
-      <c r="D197" s="8"/>
+      <c r="D197" s="26"/>
       <c r="M197" s="6"/>
     </row>
     <row r="198" spans="1:13">
       <c r="B198" s="2"/>
-      <c r="D198" s="4"/>
+      <c r="D198" s="25"/>
       <c r="M198" s="6"/>
     </row>
     <row r="199" spans="1:13">
       <c r="A199" s="8"/>
       <c r="B199" s="8"/>
       <c r="C199" s="8"/>
-      <c r="D199" s="8"/>
+      <c r="D199" s="26"/>
       <c r="M199" s="6"/>
     </row>
     <row r="200" spans="1:13">
       <c r="A200" s="8"/>
       <c r="B200" s="8"/>
       <c r="C200" s="8"/>
-      <c r="D200" s="8"/>
+      <c r="D200" s="26"/>
       <c r="M200" s="6"/>
     </row>
     <row r="201" spans="1:13">
       <c r="A201" s="8"/>
       <c r="B201" s="8"/>
       <c r="C201" s="8"/>
-      <c r="D201" s="8"/>
+      <c r="D201" s="26"/>
       <c r="M201" s="6"/>
     </row>
     <row r="202" spans="1:13">
       <c r="A202" s="8"/>
       <c r="B202" s="8"/>
       <c r="C202" s="8"/>
-      <c r="D202" s="8"/>
+      <c r="D202" s="26"/>
       <c r="M202" s="6"/>
     </row>
     <row r="203" spans="1:13">
       <c r="A203" s="8"/>
       <c r="B203" s="8"/>
       <c r="C203" s="8"/>
-      <c r="D203" s="8"/>
+      <c r="D203" s="26"/>
       <c r="M203" s="6"/>
     </row>
     <row r="204" spans="1:13">
       <c r="A204" s="8"/>
       <c r="B204" s="8"/>
       <c r="C204" s="8"/>
-      <c r="D204" s="8"/>
+      <c r="D204" s="26"/>
       <c r="M204" s="6"/>
     </row>
     <row r="205" spans="1:13">
       <c r="B205" s="2"/>
-      <c r="D205" s="4"/>
+      <c r="D205" s="25"/>
       <c r="M205" s="6"/>
     </row>
     <row r="206" spans="1:13">
       <c r="A206" s="8"/>
       <c r="B206" s="8"/>
       <c r="C206" s="8"/>
-      <c r="D206" s="8"/>
+      <c r="D206" s="26"/>
       <c r="M206" s="6"/>
     </row>
     <row r="207" spans="1:13">
       <c r="A207" s="8"/>
       <c r="B207" s="8"/>
       <c r="C207" s="8"/>
-      <c r="D207" s="8"/>
+      <c r="D207" s="26"/>
       <c r="M207" s="6"/>
     </row>
     <row r="208" spans="1:13">
       <c r="B208" s="2"/>
-      <c r="D208" s="4"/>
+      <c r="D208" s="25"/>
       <c r="M208" s="6"/>
     </row>
     <row r="209" spans="1:13">
       <c r="A209" s="8"/>
       <c r="B209" s="8"/>
       <c r="C209" s="8"/>
-      <c r="D209" s="8"/>
+      <c r="D209" s="26"/>
       <c r="M209" s="6"/>
     </row>
     <row r="210" spans="1:13">
       <c r="A210" s="8"/>
       <c r="B210" s="8"/>
       <c r="C210" s="8"/>
-      <c r="D210" s="8"/>
+      <c r="D210" s="26"/>
       <c r="M210" s="6"/>
     </row>
     <row r="211" spans="1:13">
       <c r="A211" s="8"/>
       <c r="B211" s="8"/>
       <c r="C211" s="8"/>
-      <c r="D211" s="8"/>
+      <c r="D211" s="26"/>
       <c r="M211" s="6"/>
     </row>
     <row r="212" spans="1:13">
       <c r="A212" s="8"/>
       <c r="B212" s="8"/>
       <c r="C212" s="8"/>
-      <c r="D212" s="8"/>
+      <c r="D212" s="26"/>
       <c r="M212" s="6"/>
     </row>
     <row r="213" spans="1:13">
       <c r="A213" s="8"/>
       <c r="B213" s="8"/>
       <c r="C213" s="8"/>
-      <c r="D213" s="8"/>
+      <c r="D213" s="26"/>
       <c r="M213" s="6"/>
     </row>
     <row r="214" spans="1:13">
       <c r="A214" s="8"/>
       <c r="B214" s="8"/>
       <c r="C214" s="8"/>
-      <c r="D214" s="8"/>
+      <c r="D214" s="26"/>
       <c r="M214" s="6"/>
     </row>
     <row r="215" spans="1:13">
       <c r="A215" s="8"/>
       <c r="B215" s="8"/>
       <c r="C215" s="8"/>
-      <c r="D215" s="8"/>
+      <c r="D215" s="26"/>
       <c r="M215" s="6"/>
     </row>
     <row r="216" spans="1:13">
       <c r="A216" s="8"/>
       <c r="B216" s="8"/>
       <c r="C216" s="8"/>
-      <c r="D216" s="8"/>
+      <c r="D216" s="26"/>
       <c r="M216" s="6"/>
     </row>
     <row r="217" spans="1:13">
       <c r="A217" s="8"/>
       <c r="B217" s="8"/>
       <c r="C217" s="8"/>
-      <c r="D217" s="8"/>
+      <c r="D217" s="26"/>
       <c r="M217" s="6"/>
     </row>
     <row r="218" spans="1:13">
       <c r="A218" s="8"/>
       <c r="B218" s="8"/>
       <c r="C218" s="8"/>
-      <c r="D218" s="8"/>
+      <c r="D218" s="26"/>
       <c r="M218" s="6"/>
     </row>
     <row r="219" spans="1:13">
       <c r="A219" s="8"/>
       <c r="B219" s="8"/>
       <c r="C219" s="8"/>
-      <c r="D219" s="8"/>
+      <c r="D219" s="26"/>
       <c r="M219" s="6"/>
     </row>
     <row r="220" spans="1:13">
       <c r="A220" s="8"/>
       <c r="B220" s="8"/>
       <c r="C220" s="8"/>
-      <c r="D220" s="8"/>
+      <c r="D220" s="26"/>
       <c r="M220" s="6"/>
     </row>
     <row r="221" spans="1:13">
       <c r="A221" s="8"/>
       <c r="B221" s="8"/>
       <c r="C221" s="8"/>
-      <c r="D221" s="8"/>
+      <c r="D221" s="26"/>
       <c r="M221" s="6"/>
     </row>
     <row r="222" spans="1:13">
       <c r="A222" s="8"/>
       <c r="B222" s="8"/>
       <c r="C222" s="8"/>
-      <c r="D222" s="8"/>
+      <c r="D222" s="26"/>
       <c r="M222" s="6"/>
     </row>
     <row r="223" spans="1:13">
       <c r="A223" s="8"/>
       <c r="B223" s="8"/>
       <c r="C223" s="8"/>
-      <c r="D223" s="8"/>
+      <c r="D223" s="26"/>
       <c r="M223" s="6"/>
     </row>
     <row r="224" spans="1:13">
       <c r="A224" s="8"/>
       <c r="B224" s="8"/>
       <c r="C224" s="8"/>
-      <c r="D224" s="8"/>
+      <c r="D224" s="26"/>
       <c r="M224" s="6"/>
     </row>
     <row r="225" spans="1:13">
       <c r="A225" s="8"/>
       <c r="B225" s="8"/>
       <c r="C225" s="8"/>
-      <c r="D225" s="8"/>
+      <c r="D225" s="26"/>
       <c r="M225" s="6"/>
     </row>
     <row r="226" spans="1:13">
       <c r="A226" s="8"/>
       <c r="B226" s="8"/>
       <c r="C226" s="8"/>
-      <c r="D226" s="8"/>
+      <c r="D226" s="26"/>
       <c r="M226" s="6"/>
     </row>
     <row r="227" spans="1:13">
       <c r="A227" s="8"/>
       <c r="B227" s="8"/>
       <c r="C227" s="8"/>
-      <c r="D227" s="8"/>
+      <c r="D227" s="26"/>
       <c r="M227" s="6"/>
     </row>
     <row r="228" spans="1:13">
       <c r="A228" s="8"/>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
-      <c r="D228" s="8"/>
+      <c r="D228" s="26"/>
       <c r="M228" s="6"/>
     </row>
   </sheetData>

--- a/cw71012026.xlsx
+++ b/cw71012026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD359BC5-F077-E74B-9BC3-1216593DE0AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EEAA052-7201-1544-AEDD-0E6D0353FF88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="640" windowWidth="20680" windowHeight="17380" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
+    <workbookView xWindow="120" yWindow="600" windowWidth="20680" windowHeight="16960" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -480,7 +480,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -528,21 +528,17 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="6">
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -598,8 +594,8 @@
     <tableColumn id="4" xr3:uid="{248CFFC4-D566-4C47-A784-2D182108B777}" name="Quiz_1" dataDxfId="4"/>
     <tableColumn id="5" xr3:uid="{4A2A2B68-EF30-7742-9921-AE9C8CB19994}" name="Quiz_2" dataDxfId="3"/>
     <tableColumn id="6" xr3:uid="{F4845CBF-1A2D-6F4D-8189-BDA9FF51FC40}" name="Quiz_3" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{C50393AC-DA9E-B244-B444-966939E941DB}" name="Test_1" dataDxfId="0"/>
-    <tableColumn id="8" xr3:uid="{8357C7A6-F90C-A948-931D-7D4829EE9A20}" name="Test_2 " dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{C50393AC-DA9E-B244-B444-966939E941DB}" name="Test_1" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{8357C7A6-F90C-A948-931D-7D4829EE9A20}" name="Test_2 " dataDxfId="0"/>
     <tableColumn id="9" xr3:uid="{AF37A560-C5F8-4E49-A224-CE84A49E046A}" name="Test_3 "/>
     <tableColumn id="10" xr3:uid="{E7DCE493-9761-F446-9017-EFE5CA173E6F}" name="AS_1"/>
     <tableColumn id="11" xr3:uid="{22CC7E9A-51CA-274B-9C92-B1E8F88F4324}" name="AS_2 "/>
@@ -978,10 +974,10 @@
       </c>
     </row>
     <row r="2" spans="1:13" ht="20">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="13" t="s">
         <v>71</v>
       </c>
       <c r="C2" s="13" t="s">
@@ -1582,10 +1578,10 @@
       <c r="M22" s="6"/>
     </row>
     <row r="23" spans="1:13">
-      <c r="A23" s="29" t="s">
+      <c r="A23" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="B23" s="29" t="s">
+      <c r="B23" s="21" t="s">
         <v>96</v>
       </c>
       <c r="C23" t="s">
@@ -1666,10 +1662,10 @@
       <c r="M25" s="6"/>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="B26" s="30" t="s">
+      <c r="B26" s="9" t="s">
         <v>40</v>
       </c>
       <c r="C26" t="s">
@@ -1696,10 +1692,10 @@
       <c r="M26" s="6"/>
     </row>
     <row r="27" spans="1:13">
-      <c r="A27" s="31" t="s">
+      <c r="A27" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="B27" s="31" t="s">
+      <c r="B27" s="11" t="s">
         <v>55</v>
       </c>
       <c r="C27" s="11" t="s">
@@ -1723,10 +1719,10 @@
       <c r="M27" s="6"/>
     </row>
     <row r="28" spans="1:13" ht="20">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="B28" s="28" t="s">
+      <c r="B28" s="27" t="s">
         <v>74</v>
       </c>
       <c r="C28" s="13" t="s">
@@ -1750,10 +1746,10 @@
       <c r="M28" s="6"/>
     </row>
     <row r="29" spans="1:13">
-      <c r="A29" s="31" t="s">
+      <c r="A29" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="31" t="s">
+      <c r="B29" s="11" t="s">
         <v>57</v>
       </c>
       <c r="C29" s="11" t="s">
@@ -1975,7 +1971,9 @@
       <c r="G36" s="22">
         <v>0.53</v>
       </c>
-      <c r="H36" s="5"/>
+      <c r="H36" s="5">
+        <v>0.41</v>
+      </c>
       <c r="J36">
         <v>0.6</v>
       </c>
@@ -2000,7 +1998,9 @@
       <c r="G37" s="22">
         <v>0.51</v>
       </c>
-      <c r="H37" s="5"/>
+      <c r="H37" s="5">
+        <v>0.57999999999999996</v>
+      </c>
       <c r="J37">
         <v>0.73</v>
       </c>
@@ -2025,6 +2025,9 @@
       <c r="G38" s="22">
         <v>0.67</v>
       </c>
+      <c r="H38" s="4">
+        <v>0.49</v>
+      </c>
       <c r="J38">
         <v>0.75</v>
       </c>
@@ -2049,7 +2052,9 @@
       <c r="G39" s="22">
         <v>0.37</v>
       </c>
-      <c r="H39" s="5"/>
+      <c r="H39" s="5">
+        <v>0.47</v>
+      </c>
       <c r="J39">
         <v>0.61</v>
       </c>
@@ -2074,7 +2079,9 @@
       <c r="G40" s="22">
         <v>0.11</v>
       </c>
-      <c r="H40" s="5"/>
+      <c r="H40" s="5">
+        <v>0.1</v>
+      </c>
       <c r="J40">
         <v>0.57999999999999996</v>
       </c>
@@ -2099,6 +2106,9 @@
       <c r="G41" s="22">
         <v>0.28000000000000003</v>
       </c>
+      <c r="H41" s="4">
+        <v>0.36</v>
+      </c>
       <c r="J41">
         <v>0.82</v>
       </c>
@@ -2123,7 +2133,9 @@
       <c r="G42" s="22">
         <v>0.28000000000000003</v>
       </c>
-      <c r="H42" s="5"/>
+      <c r="H42" s="5">
+        <v>0.2</v>
+      </c>
       <c r="J42">
         <v>0.66</v>
       </c>
@@ -2148,7 +2160,9 @@
       <c r="G43" s="22">
         <v>0.49</v>
       </c>
-      <c r="H43" s="5"/>
+      <c r="H43" s="5">
+        <v>0.53</v>
+      </c>
       <c r="J43">
         <v>0.72</v>
       </c>

--- a/cw71012026.xlsx
+++ b/cw71012026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EEAA052-7201-1544-AEDD-0E6D0353FF88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{368C0EFF-C951-BE47-8647-5057ED0B652E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="120" yWindow="600" windowWidth="20680" windowHeight="16960" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -928,8 +928,14 @@
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="4" max="7" width="10.7109375" style="22"/>
-    <col min="8" max="8" width="10.7109375" style="4"/>
+    <col min="3" max="3" width="7.7109375" customWidth="1"/>
+    <col min="4" max="4" width="8.28515625" style="22" customWidth="1"/>
+    <col min="5" max="5" width="7.42578125" style="22" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" style="22" customWidth="1"/>
+    <col min="7" max="7" width="8.5703125" style="22" customWidth="1"/>
+    <col min="8" max="8" width="7.7109375" style="4" customWidth="1"/>
+    <col min="9" max="9" width="7.85546875" customWidth="1"/>
+    <col min="10" max="10" width="7.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -1055,6 +1061,9 @@
       <c r="H4" s="5">
         <v>0.67</v>
       </c>
+      <c r="J4">
+        <v>0.73</v>
+      </c>
       <c r="M4" s="10"/>
     </row>
     <row r="5" spans="1:13">
@@ -1082,6 +1091,9 @@
       <c r="H5" s="5">
         <v>0.59</v>
       </c>
+      <c r="J5">
+        <v>0.33</v>
+      </c>
       <c r="M5" s="10"/>
     </row>
     <row r="6" spans="1:13">
@@ -1651,7 +1663,7 @@
         <v>1</v>
       </c>
       <c r="F25" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" s="22">
         <v>0.39</v>
